--- a/development/abiraj_mini_aios_workbench/projects/PRJ-2026-026_amazon-keyword-gap-sync/evidence/final_outputs/REQ-30_amazon-keyword-gap-sync/REQ-30-D02_keyword_gap_report.xlsx
+++ b/development/abiraj_mini_aios_workbench/projects/PRJ-2026-026_amazon-keyword-gap-sync/evidence/final_outputs/REQ-30_amazon-keyword-gap-sync/REQ-30-D02_keyword_gap_report.xlsx
@@ -13,8 +13,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Field Reference" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Part A - No Content'!$A$1:$K$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Part B - Keyword Gaps'!$A$1:$M$145</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Part A - No Content'!$A$1:$K$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Part B - Keyword Gaps'!$A$1:$M$192</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Field Reference'!$A$1:$B$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -490,7 +490,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-19T11:34:56</t>
+          <t>2026-08-19T11:46:28</t>
         </is>
       </c>
     </row>
@@ -658,7 +658,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>18 listings with NO CONTENT — empty backend keyword field and/or no bullet points. Every keyword would show as 'missing' because there is nothing to search. These need a rewrite, not keyword edits (rule Q12).</t>
+          <t>21 listings with NO CONTENT — empty backend keyword field and/or no bullet points. Every keyword would show as 'missing' because there is nothing to search. These need a rewrite, not keyword edits (rule Q12).</t>
         </is>
       </c>
     </row>
@@ -670,7 +670,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>144 keyword rows across listings that DO have content — 115 real, actionable gaps.</t>
+          <t>191 keyword rows across listings that DO have content — 149 real, actionable gaps.</t>
         </is>
       </c>
     </row>
@@ -685,7 +685,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1211,17 +1211,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>LDMG95E274APK</t>
+          <t>LDMG95E274</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>B0D7MDP9XP</t>
+          <t>B093SS3HWN</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>LDMG95E274APK_DCVV</t>
+          <t>LDMG95E274 H_DCVV</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>DC VOLTAGE 10-Pack, LED Bayonet Light Bulb, BC G95 4W(40W Equivalent) Dimmable Warm White 2700K 450 Lumens LED Filament Amber Glass Retro Style Old Fashioned Decorative Energy Saving Bulb</t>
+          <t>DC VOLTAGE LED Vintage E27 Light Bulb, G95 4W (40W Equivalent) Dimmable Warm White 2700K 450 Lumens ES Screw LED Filament, Old Fashioned Retro Energy Saving Home Decorative Lighting</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1261,22 +1261,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>B09479HV6W</t>
+          <t>B0BLZFGY38</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>LDMG95E278</t>
+          <t>LDMG95E274</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>B0D4YG1QFJ</t>
+          <t>B0D7MDP9XP</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>LDMG95E2783PK_DCVV</t>
+          <t>LDMG95E274APK_DCVV</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1295,11 +1295,11 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>DC VOLTAGE Pack 3 | Vintage LED E27 Bulb, Edison G95 8W Screw Light Bulb, Dimmable LED Filament Warm White 2700K Amber Glass, 800 Lumen Retro Style Old Fashioned Bulb, 90% Energy Saving 220V</t>
+          <t>DC VOLTAGE 10-Pack, LED Bayonet Light Bulb, BC G95 4W(40W Equivalent) Dimmable Warm White 2700K 450 Lumens LED Filament Amber Glass Retro Style Old Fashioned Decorative Energy Saving Bulb</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>B09479HV6W</t>
+          <t>B09477YHK7</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1326,12 +1326,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>B0DH4M42LR</t>
+          <t>B0D4YG1QFJ</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>LDMG95E278_VDS</t>
+          <t>LDMG95E2783PK_DCVV</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>LEDSone E27 LED Vintage Light Bulb Screw 8W Edison LED Filament Bulb G95 Globe Edison Style Dimmable LED Bulbs Retro Amber Glass Decorative Light Bulbs Warm White 2700K</t>
+          <t>DC VOLTAGE Pack 3 | Vintage LED E27 Bulb, Edison G95 8W Screw Light Bulb, Dimmable LED Filament Warm White 2700K Amber Glass, 800 Lumen Retro Style Old Fashioned Bulb, 90% Energy Saving 220V</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>B09479HV6W</t>
+          <t>B09477YHK7</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1381,12 +1381,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>B0CNPZDQHZ</t>
+          <t>B0DH4M42LR</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>LDMG95E278-DC_DCVV</t>
+          <t>LDMG95E278_VDS</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>DC VOLTAGE G95 Globe E27 Screw Bulb,Led Edison Light Bulb, Dimmable Retro Bulb, 220V 8W 450 Lumen Warm White 2700K Led Filament Light Bulb,90% Energy Saving</t>
+          <t>LEDSone E27 LED Vintage Light Bulb Screw 8W Edison LED Filament Bulb G95 Globe Edison Style Dimmable LED Bulbs Retro Amber Glass Decorative Light Bulbs Warm White 2700K</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>B09479HV6W</t>
+          <t>B09477YHK7</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1436,12 +1436,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>B0D4Y9DKJD</t>
+          <t>B0CNPZDQHZ</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>LDMG95E2786PK_DCVV</t>
+          <t>LDMG95E278-DC_DCVV</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>DC VOLTAGE Vintage E27 LED Bulb, Edison G95 8W Screw Globe Dimmable LED Filament Bulb, 2700K Warm White Amber Glass, Retro Old Fashioned Light Bulb, 90% Energy Saving 220V - Pack of 6</t>
+          <t>DC VOLTAGE G95 Globe E27 Screw Bulb,Led Edison Light Bulb, Dimmable Retro Bulb, 220V 8W 450 Lumen Warm White 2700K Led Filament Light Bulb,90% Energy Saving</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1481,22 +1481,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>B0BLP1JSRK</t>
+          <t>B09477YHK7</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>LDMST64E278</t>
+          <t>LDMG95E278</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>B0BSGSLZMD</t>
+          <t>B0D4Y9DKJD</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>LDMST64E2786PK_DCVV</t>
+          <t>LDMG95E2786PK_DCVV</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1515,11 +1515,11 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>DC VOLTAGE Pack 6| LED Edison E27 Light Bulb, 8W (60W Equivalent) ST64 Dimmable 2700K Warm White Vintage Style Amber Glass LED Filament Energy Saving Bulb for Squirrel Cage Lamp &amp; Home Decoration</t>
+          <t>DC VOLTAGE Vintage E27 LED Bulb, Edison G95 8W Screw Globe Dimmable LED Filament Bulb, 2700K Warm White Amber Glass, Retro Old Fashioned Light Bulb, 90% Energy Saving 220V - Pack of 6</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>B0DDCGGFD5</t>
+          <t>B0BSGSLZMD</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>LDMST64E2783PK_VDS</t>
+          <t>LDMST64E2786PK_DCVV</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>LEDSone 3 Pcs Vintage LED Light Bulb E27 Edison Screw Bulb 8W Retro Amber Glass Lamp 2200K Warm White dimmable Antique Style Energy Saving LED ST64 Filament Lamp 220V</t>
+          <t>DC VOLTAGE Pack 6| LED Edison E27 Light Bulb, 8W (60W Equivalent) ST64 Dimmable 2700K Warm White Vintage Style Amber Glass LED Filament Energy Saving Bulb for Squirrel Cage Lamp &amp; Home Decoration</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>B08FYR2TFS</t>
+          <t>B0DDCGGFD5</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>LDMST64E278 A_DCVV</t>
+          <t>LDMST64E2783PK_VDS</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>DC VOLTAGE LED E27 Light Bulb, ST64 8W (60W Equivalent) Dimmable 2700K Warm White Amber Glass 806 Lumens Screw Base Vintage LED Filament Energy Saving Bulb for Squirrel Cage Lamp &amp; Home Decoration</t>
+          <t>LEDSone 3 Pcs Vintage LED Light Bulb E27 Edison Screw Bulb 8W Retro Amber Glass Lamp 2200K Warm White dimmable Antique Style Energy Saving LED ST64 Filament Lamp 220V</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1646,22 +1646,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>B0BL82M8SB</t>
+          <t>B0BLP1JSRK</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>LDMT185E274</t>
+          <t>LDMST64E278</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>B093ST24PN</t>
+          <t>B08FYR2TFS</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>LDMT185E274 H_DCVV</t>
+          <t>LDMST64E278 A_DCVV</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1680,11 +1680,11 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>DC VOLTAGE LED E27 Edison Light Bulb, T185 4W (40W Equivalent) Dimmable Warm White 2700K LED Filament Amber Glass 450 Lumens Tubular Screw Base Vintage Energy Saving Home Decorative Light Bulb</t>
+          <t>DC VOLTAGE LED E27 Light Bulb, ST64 8W (60W Equivalent) Dimmable 2700K Warm White Amber Glass 806 Lumens Screw Base Vintage LED Filament Energy Saving Bulb for Squirrel Cage Lamp &amp; Home Decoration</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1701,55 +1701,220 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
+          <t>B0BL82M8SB</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>LDMT185E274</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>B0BL82LFD7</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>LDMT185E274APK</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>zero_sales_6mo</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>backend keyword field empty</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Rewrite listing content (bullets + backend keywords)</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>LEDSone Vintage LED Edison Bulb, Dimmable 4W E27 2700K T185 Tubular LED Bulbs, Led Filament Bulbs, Antique Style Retro Amber Glass Screw Lamp 220V Pack of 10</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ledsone_uk</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>B0BL82M8SB</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>LDMT185E274</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>B093ST24PN</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>LDMT185E274 H_DCVV</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>zero_sales_6mo</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>backend keyword field empty; no bullet points; no description</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Rewrite listing content (bullets + backend keywords)</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>DC VOLTAGE LED E27 Edison Light Bulb, T185 4W (40W Equivalent) Dimmable Warm White 2700K LED Filament Amber Glass 450 Lumens Tubular Screw Base Vintage Energy Saving Home Decorative Light Bulb</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ledsone_uk</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
           <t>B0BL7LZR24</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>LDMT45E274</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>B0DJCWV93V</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>LDMT45E274_DCVV</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>zero_sales_6mo</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>zero_sales_6mo</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
         <is>
           <t>backend keyword field empty; no bullet points; no description</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>Rewrite listing content (bullets + backend keywords)</t>
         </is>
       </c>
-      <c r="I19" t="n">
+      <c r="I21" t="n">
         <v>11</v>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>DC VOLTAGE 1 Pack E27 LED 4W Vintage Edison Screw Bulb Equivalent to 40W Amber Glass Antique Light Bulb Warm White 2200K 450LM dimmable T45 Retro Filament Bulb</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ledsone_uk</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>B0DCDSZ719</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>LDSG95DIE274</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>B09JVSRK4Y</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>LDSG95DIE274APK_DCVV</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>zero_sales_6mo</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>backend keyword field empty; no bullet points; no description</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Rewrite listing content (bullets + backend keywords)</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>10</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>DC VOLTAGE Pack 10 | LED E27 Edison Decorative Bulbs, G95 Diamond Shape 4W (40W Equivalent), Non-Dimmable 2700K Warm White Amber Glass Vintage Spiral LED Filament 450 Lumens Energy Saving Light Bulbs</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K19"/>
+  <autoFilter ref="A1:K22"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1760,7 +1925,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M145"/>
+  <dimension ref="A1:M192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2763,22 +2928,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ledsone_uk</t>
+          <t>dcvoltage_uk</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>B0B8P9BKXB</t>
+          <t>B0CNRL871B</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>LDMG125E278</t>
+          <t>LDMST64E274</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>B0B8P75R4Y</t>
+          <t>B0DT9TL5DW</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2788,11 +2953,11 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>large screw light bulbs</t>
+          <t>outdoor light bulbs e27 dimmable</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>306</v>
+        <v>25</v>
       </c>
       <c r="H17" t="b">
         <v>0</v>
@@ -2824,22 +2989,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ledsone_uk</t>
+          <t>dcvoltage_uk</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>B0B8P9BKXB</t>
+          <t>B0CNRL871B</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>LDMG125E278</t>
+          <t>LDMST64E274</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>B0B8P75R4Y</t>
+          <t>B0DT9TL5DW</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2849,11 +3014,11 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>large light bulb</t>
+          <t>dc voltage vintage amber led bulb e27 edison screw st64 4w dimmable, 2700k warm glow, 40w equivalent, decorative retro light bulb for pendant lamps, wall sconces, indoor &amp; covered outdoor fixtures</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>192</v>
+        <v>2</v>
       </c>
       <c r="H18" t="b">
         <v>0</v>
@@ -2885,22 +3050,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ledsone_uk</t>
+          <t>dcvoltage_uk</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>B0B8P9BKXB</t>
+          <t>B0CNRL871B</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>LDMG125E278</t>
+          <t>LDMST64E274</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>B0B8P75R4Y</t>
+          <t>B0DT9TL5DW</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2910,11 +3075,11 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>e27 large globe bulb</t>
+          <t>dc voltage vintage amber led bulb e27 edison screw st64 4w dimmable,</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>128</v>
+        <v>1</v>
       </c>
       <c r="H19" t="b">
         <v>0</v>
@@ -2946,22 +3111,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ledsone_uk</t>
+          <t>dcvoltage_uk</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>B0B8P9BKXB</t>
+          <t>B0CNRL871B</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>LDMG125E278</t>
+          <t>LDMST64E274</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>B0B8P75R4Y</t>
+          <t>B0DT9TL5DW</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2971,31 +3136,31 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>e27 globe bulb</t>
+          <t>outdoor bulb for pendant light</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>91</v>
+        <v>1</v>
       </c>
       <c r="H20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>present</t>
+          <t>gap</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>pending_add</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -3032,11 +3197,11 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>large globe e27 edison screw led bulb</t>
+          <t>large screw light bulbs</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>55</v>
+        <v>306</v>
       </c>
       <c r="H21" t="b">
         <v>0</v>
@@ -3093,11 +3258,11 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>e27 large bulb</t>
+          <t>large light bulb</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>40</v>
+        <v>192</v>
       </c>
       <c r="H22" t="b">
         <v>0</v>
@@ -3154,11 +3319,11 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>large led bulb</t>
+          <t>e27 large globe bulb</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>23</v>
+        <v>128</v>
       </c>
       <c r="H23" t="b">
         <v>0</v>
@@ -3215,11 +3380,11 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>decorative bulbs bayonet</t>
+          <t>e27 globe bulb</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="H24" t="b">
         <v>1</v>
@@ -3276,17 +3441,17 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>es 8w led bulb</t>
+          <t>large globe e27 edison screw led bulb</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>14</v>
+        <v>55</v>
       </c>
       <c r="H25" t="b">
         <v>0</v>
       </c>
       <c r="I25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -3295,7 +3460,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>bullet</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -3337,31 +3502,31 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>g125 e27</t>
+          <t>e27 large bulb</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="H26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>present</t>
+          <t>gap</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>pending_add</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -3398,31 +3563,31 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>e27 g125 amber led filament globe bulb dimmable</t>
+          <t>large led bulb</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="H27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>present</t>
+          <t>gap</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>pending_add</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -3459,31 +3624,31 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>led e27 edison filament bulb light retro vintage screw globe lamp 8w</t>
+          <t>decorative bulbs bayonet</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="H28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" t="b">
         <v>1</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>gap</t>
+          <t>present</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>bullet</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>pending_add</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3520,17 +3685,17 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>e27 large bulb dimmable</t>
+          <t>es 8w led bulb</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H29" t="b">
         <v>0</v>
       </c>
       <c r="I29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -3539,7 +3704,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>bullet</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3581,31 +3746,31 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>led bulb light large 120 mm x 160mm</t>
+          <t>g125 e27</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>gap</t>
+          <t>present</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>pending_add</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -3642,11 +3807,11 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>led light bulb, e27</t>
+          <t>e27 g125 amber led filament globe bulb dimmable</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H31" t="b">
         <v>1</v>
@@ -3703,17 +3868,17 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>large e27 vintage light bulbs 14cm retro</t>
+          <t>led e27 edison filament bulb light retro vintage screw globe lamp 8w</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H32" t="b">
         <v>0</v>
       </c>
       <c r="I32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -3722,7 +3887,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>bullet</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3764,11 +3929,11 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>e27 xl bulb</t>
+          <t>e27 large bulb dimmable</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H33" t="b">
         <v>0</v>
@@ -3825,11 +3990,11 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>dimmable retro large 8w</t>
+          <t>led bulb light large 120 mm x 160mm</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H34" t="b">
         <v>0</v>
@@ -3886,31 +4051,31 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>vintage led e27 g125 8w dimmable, amber glass, 2700k, 806 lumen</t>
+          <t>led light bulb, e27</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>gap</t>
+          <t>present</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>pending_add</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3947,11 +4112,11 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>large bulb indoor e27 screw</t>
+          <t>large e27 vintage light bulbs 14cm retro</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H36" t="b">
         <v>0</v>
@@ -4008,17 +4173,17 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>e27 8w vintage light bulbs</t>
+          <t>e27 xl bulb</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H37" t="b">
         <v>0</v>
       </c>
       <c r="I37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -4027,7 +4192,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>bullet</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -4069,31 +4234,31 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>edison g125</t>
+          <t>dimmable retro large 8w</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>present</t>
+          <t>gap</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>pending_add</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -4130,31 +4295,31 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>e27 g125 vintage</t>
+          <t>vintage led e27 g125 8w dimmable, amber glass, 2700k, 806 lumen</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>present</t>
+          <t>gap</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>pending_add</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4191,11 +4356,11 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>g125 led filament bulb smoked e27 warm</t>
+          <t>large bulb indoor e27 screw</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H40" t="b">
         <v>0</v>
@@ -4252,11 +4417,11 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>led bulb dimmable filament amber e27 8w</t>
+          <t>e27 8w vintage light bulbs</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H41" t="b">
         <v>0</v>
@@ -4313,31 +4478,31 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>diall g125 e27 5.5w 470lm 330° amber globe warm white led filament light bulb</t>
+          <t>edison g125</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>gap</t>
+          <t>present</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>pending_add</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -4364,7 +4529,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>B0DQ8TM75J</t>
+          <t>B0B8P75R4Y</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -4374,31 +4539,31 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>large screw light bulbs</t>
+          <t>e27 g125 vintage</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>306</v>
+        <v>2</v>
       </c>
       <c r="H43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>gap</t>
+          <t>present</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>pending_add</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -4425,7 +4590,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>B0DQ8TM75J</t>
+          <t>B0B8P75R4Y</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -4435,11 +4600,11 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>large light bulb</t>
+          <t>g125 led filament bulb smoked e27 warm</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>192</v>
+        <v>2</v>
       </c>
       <c r="H44" t="b">
         <v>0</v>
@@ -4486,7 +4651,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>B0DQ8TM75J</t>
+          <t>B0B8P75R4Y</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -4496,17 +4661,17 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>e27 large globe bulb</t>
+          <t>led bulb dimmable filament amber e27 8w</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>128</v>
+        <v>1</v>
       </c>
       <c r="H45" t="b">
         <v>0</v>
       </c>
       <c r="I45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -4515,7 +4680,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>bullet</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4547,7 +4712,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>B0DQ8TM75J</t>
+          <t>B0B8P75R4Y</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4557,31 +4722,31 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>e27 globe bulb</t>
+          <t>diall g125 e27 5.5w 470lm 330° amber globe warm white led filament light bulb</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>91</v>
+        <v>1</v>
       </c>
       <c r="H46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>present</t>
+          <t>gap</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>pending_add</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4608,7 +4773,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>B0DQ8TM75J</t>
+          <t>B0BP2PVM3D</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -4618,14 +4783,14 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>large globe e27 edison screw led bulb</t>
+          <t>large screw light bulbs</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>55</v>
+        <v>306</v>
       </c>
       <c r="H47" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I47" t="b">
         <v>0</v>
@@ -4637,7 +4802,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>backend</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -4669,7 +4834,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>B0DQ8TM75J</t>
+          <t>B0BP2PVM3D</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -4679,14 +4844,14 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>e27 large bulb</t>
+          <t>large light bulb</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>40</v>
+        <v>192</v>
       </c>
       <c r="H48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I48" t="b">
         <v>0</v>
@@ -4698,7 +4863,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>backend</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -4730,7 +4895,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>B0DQ8TM75J</t>
+          <t>B0BP2PVM3D</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -4740,14 +4905,14 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>large led bulb</t>
+          <t>e27 large globe bulb</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>23</v>
+        <v>128</v>
       </c>
       <c r="H49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I49" t="b">
         <v>0</v>
@@ -4759,7 +4924,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>backend</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -4791,7 +4956,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>B0DQ8TM75J</t>
+          <t>B0BP2PVM3D</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -4801,31 +4966,31 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>decorative bulbs bayonet</t>
+          <t>e27 globe bulb</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="H50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>gap</t>
+          <t>present</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>pending_add</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -4852,7 +5017,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>B0DQ8TM75J</t>
+          <t>B0BP2PVM3D</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -4862,11 +5027,11 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>es 8w led bulb</t>
+          <t>large globe e27 edison screw led bulb</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>14</v>
+        <v>55</v>
       </c>
       <c r="H51" t="b">
         <v>1</v>
@@ -4913,7 +5078,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>B0DQ8TM75J</t>
+          <t>B0BP2PVM3D</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -4923,31 +5088,31 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>g125 e27</t>
+          <t>e27 large bulb</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="H52" t="b">
         <v>1</v>
       </c>
       <c r="I52" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>present</t>
+          <t>gap</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>backend</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>pending_add</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -4974,7 +5139,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>B0DQ8TM75J</t>
+          <t>B0BP2PVM3D</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -4984,31 +5149,31 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>e27 g125 amber led filament globe bulb dimmable</t>
+          <t>large led bulb</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="H53" t="b">
         <v>1</v>
       </c>
       <c r="I53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>present</t>
+          <t>gap</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>backend</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>pending_add</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -5035,7 +5200,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>B0DQ8TM75J</t>
+          <t>B0BP2PVM3D</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -5045,14 +5210,14 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>led e27 edison filament bulb light retro vintage screw globe lamp 8w</t>
+          <t>decorative bulbs bayonet</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="H54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I54" t="b">
         <v>0</v>
@@ -5064,7 +5229,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>backend</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -5096,7 +5261,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>B0DQ8TM75J</t>
+          <t>B0BP2PVM3D</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -5106,14 +5271,14 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>e27 large bulb dimmable</t>
+          <t>es 8w led bulb</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I55" t="b">
         <v>0</v>
@@ -5125,7 +5290,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>backend</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -5157,7 +5322,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>B0DQ8TM75J</t>
+          <t>B0BP2PVM3D</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -5167,31 +5332,31 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>led bulb light large 120 mm x 160mm</t>
+          <t>g125 e27</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>gap</t>
+          <t>present</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>pending_add</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -5218,7 +5383,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>B0DQ8TM75J</t>
+          <t>B0BP2PVM3D</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -5228,11 +5393,11 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>led light bulb, e27</t>
+          <t>e27 g125 amber led filament globe bulb dimmable</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H57" t="b">
         <v>1</v>
@@ -5279,7 +5444,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>B0DQ8TM75J</t>
+          <t>B0BP2PVM3D</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -5289,31 +5454,31 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>large e27 vintage light bulbs 14cm retro</t>
+          <t>led e27 edison filament bulb light retro vintage screw globe lamp 8w</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>gap</t>
+          <t>present</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>pending_add</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -5340,7 +5505,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>B0DQ8TM75J</t>
+          <t>B0BP2PVM3D</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -5350,14 +5515,14 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>e27 xl bulb</t>
+          <t>e27 large bulb dimmable</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I59" t="b">
         <v>0</v>
@@ -5369,7 +5534,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>backend</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -5401,7 +5566,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>B0DQ8TM75J</t>
+          <t>B0BP2PVM3D</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -5411,11 +5576,11 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>dimmable retro large 8w</t>
+          <t>led bulb light large 120 mm x 160mm</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H60" t="b">
         <v>0</v>
@@ -5462,7 +5627,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>B0DQ8TM75J</t>
+          <t>B0BP2PVM3D</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -5472,31 +5637,31 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>vintage led e27 g125 8w dimmable, amber glass, 2700k, 806 lumen</t>
+          <t>led light bulb, e27</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H61" t="b">
         <v>1</v>
       </c>
       <c r="I61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>gap</t>
+          <t>present</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>backend</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>pending_add</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -5523,7 +5688,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>B0DQ8TM75J</t>
+          <t>B0BP2PVM3D</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -5533,11 +5698,11 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>large bulb indoor e27 screw</t>
+          <t>large e27 vintage light bulbs 14cm retro</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H62" t="b">
         <v>0</v>
@@ -5584,7 +5749,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>B0DQ8TM75J</t>
+          <t>B0BP2PVM3D</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -5594,14 +5759,14 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>e27 8w vintage light bulbs</t>
+          <t>e27 xl bulb</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H63" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I63" t="b">
         <v>0</v>
@@ -5613,7 +5778,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>backend</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -5645,7 +5810,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>B0DQ8TM75J</t>
+          <t>B0BP2PVM3D</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -5655,31 +5820,31 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>edison g125</t>
+          <t>dimmable retro large 8w</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H64" t="b">
         <v>1</v>
       </c>
       <c r="I64" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>present</t>
+          <t>gap</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>backend</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>pending_add</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -5706,7 +5871,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>B0DQ8TM75J</t>
+          <t>B0BP2PVM3D</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -5716,31 +5881,31 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>e27 g125 vintage</t>
+          <t>vintage led e27 g125 8w dimmable, amber glass, 2700k, 806 lumen</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H65" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I65" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>present</t>
+          <t>gap</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>pending_add</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -5767,7 +5932,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>B0DQ8TM75J</t>
+          <t>B0BP2PVM3D</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -5777,14 +5942,14 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>g125 led filament bulb smoked e27 warm</t>
+          <t>large bulb indoor e27 screw</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I66" t="b">
         <v>0</v>
@@ -5796,7 +5961,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>backend</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -5828,7 +5993,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>B0DQ8TM75J</t>
+          <t>B0BP2PVM3D</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -5838,31 +6003,31 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>led bulb dimmable filament amber e27 8w</t>
+          <t>e27 8w vintage light bulbs</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H67" t="b">
         <v>1</v>
       </c>
       <c r="I67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>gap</t>
+          <t>present</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>backend</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>pending_add</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -5889,7 +6054,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>B0DQ8TM75J</t>
+          <t>B0BP2PVM3D</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -5899,31 +6064,31 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>diall g125 e27 5.5w 470lm 330° amber globe warm white led filament light bulb</t>
+          <t>edison g125</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H68" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I68" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>gap</t>
+          <t>present</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>pending_add</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -5940,17 +6105,17 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>B09479HV6W</t>
+          <t>B0B8P9BKXB</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>LDMG95E278</t>
+          <t>LDMG125E278</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>B0845ZBTJV</t>
+          <t>B0BP2PVM3D</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -5960,11 +6125,11 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>led bulbs</t>
+          <t>e27 g125 vintage</t>
         </is>
       </c>
       <c r="G69" t="n">
-        <v>2400</v>
+        <v>2</v>
       </c>
       <c r="H69" t="b">
         <v>1</v>
@@ -6001,17 +6166,17 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>B09479HV6W</t>
+          <t>B0B8P9BKXB</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>LDMG95E278</t>
+          <t>LDMG125E278</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>B0845ZBTJV</t>
+          <t>B0BP2PVM3D</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -6021,11 +6186,11 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>g95 e27 led filament large globe bulb</t>
+          <t>g125 led filament bulb smoked e27 warm</t>
         </is>
       </c>
       <c r="G70" t="n">
-        <v>64</v>
+        <v>2</v>
       </c>
       <c r="H70" t="b">
         <v>0</v>
@@ -6062,17 +6227,17 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>B09479HV6W</t>
+          <t>B0B8P9BKXB</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>LDMG95E278</t>
+          <t>LDMG125E278</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>B0845ZBTJV</t>
+          <t>B0BP2PVM3D</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -6082,31 +6247,31 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>large e27 vintage light bulbs</t>
+          <t>led bulb dimmable filament amber e27 8w</t>
         </is>
       </c>
       <c r="G71" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="H71" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I71" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>gap</t>
+          <t>present</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>pending_add</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -6123,17 +6288,17 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>B09479HV6W</t>
+          <t>B0B8P9BKXB</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>LDMG95E278</t>
+          <t>LDMG125E278</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>B0845ZBTJV</t>
+          <t>B0BP2PVM3D</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -6143,31 +6308,31 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>g95 e27 bulb</t>
+          <t>diall g125 e27 5.5w 470lm 330° amber globe warm white led filament light bulb</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="H72" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I72" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>present</t>
+          <t>gap</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>pending_add</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -6184,17 +6349,17 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>B09479HV6W</t>
+          <t>B0B8P9BKXB</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>LDMG95E278</t>
+          <t>LDMG125E278</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>B0845ZBTJV</t>
+          <t>B0DQ8TM75J</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -6204,17 +6369,17 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>e27 dimmable bulb vintage</t>
+          <t>large screw light bulbs</t>
         </is>
       </c>
       <c r="G73" t="n">
-        <v>14</v>
+        <v>306</v>
       </c>
       <c r="H73" t="b">
         <v>0</v>
       </c>
       <c r="I73" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -6223,7 +6388,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>bullet</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -6245,17 +6410,17 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>B09479HV6W</t>
+          <t>B0B8P9BKXB</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>LDMG95E278</t>
+          <t>LDMG125E278</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>B0845ZBTJV</t>
+          <t>B0DQ8TM75J</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -6265,31 +6430,31 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>dimmable antique light bulbs 8w</t>
+          <t>large light bulb</t>
         </is>
       </c>
       <c r="G74" t="n">
-        <v>6</v>
+        <v>192</v>
       </c>
       <c r="H74" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I74" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>present</t>
+          <t>gap</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>pending_add</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -6306,17 +6471,17 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>B09479HV6W</t>
+          <t>B0B8P9BKXB</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>LDMG95E278</t>
+          <t>LDMG125E278</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>B0845ZBTJV</t>
+          <t>B0DQ8TM75J</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -6326,31 +6491,31 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>g95</t>
+          <t>e27 large globe bulb</t>
         </is>
       </c>
       <c r="G75" t="n">
-        <v>6</v>
+        <v>128</v>
       </c>
       <c r="H75" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I75" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>present</t>
+          <t>gap</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>pending_add</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -6367,17 +6532,17 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>B09479HV6W</t>
+          <t>B0B8P9BKXB</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>LDMG95E278</t>
+          <t>LDMG125E278</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>B0845ZBTJV</t>
+          <t>B0DQ8TM75J</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -6387,31 +6552,31 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>9w led edison bulb</t>
+          <t>e27 globe bulb</t>
         </is>
       </c>
       <c r="G76" t="n">
-        <v>5</v>
+        <v>91</v>
       </c>
       <c r="H76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>gap</t>
+          <t>present</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>pending_add</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -6428,17 +6593,17 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>B09479HV6W</t>
+          <t>B0B8P9BKXB</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>LDMG95E278</t>
+          <t>LDMG125E278</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>B0845ZBTJV</t>
+          <t>B0DQ8TM75J</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -6448,17 +6613,17 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>e27 vintage bulb dimmable 8w</t>
+          <t>large globe e27 edison screw led bulb</t>
         </is>
       </c>
       <c r="G77" t="n">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="H77" t="b">
         <v>0</v>
       </c>
       <c r="I77" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
@@ -6467,7 +6632,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>bullet</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -6489,17 +6654,17 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>B09479HV6W</t>
+          <t>B0B8P9BKXB</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>LDMG95E278</t>
+          <t>LDMG125E278</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>B0845ZBTJV</t>
+          <t>B0DQ8TM75J</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -6509,31 +6674,31 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>led e27 g95</t>
+          <t>e27 large bulb</t>
         </is>
       </c>
       <c r="G78" t="n">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="H78" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I78" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>present</t>
+          <t>gap</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>pending_add</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -6550,17 +6715,17 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>B09479HV6W</t>
+          <t>B0B8P9BKXB</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>LDMG95E278</t>
+          <t>LDMG125E278</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>B0845ZBTJV</t>
+          <t>B0DQ8TM75J</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -6570,31 +6735,31 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>e27 dimmable led globe</t>
+          <t>large led bulb</t>
         </is>
       </c>
       <c r="G79" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="H79" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I79" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>present</t>
+          <t>gap</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>pending_add</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -6611,17 +6776,17 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>B09479HV6W</t>
+          <t>B0B8P9BKXB</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>LDMG95E278</t>
+          <t>LDMG125E278</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>B0845ZBTJV</t>
+          <t>B0DQ8TM75J</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -6631,11 +6796,11 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>dimmable 8w e27 screw lamps</t>
+          <t>decorative bulbs bayonet</t>
         </is>
       </c>
       <c r="G80" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="H80" t="b">
         <v>0</v>
@@ -6672,17 +6837,17 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>B0BLP1JSRK</t>
+          <t>B0B8P9BKXB</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>LDMST64E278</t>
+          <t>LDMG125E278</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>B0BLNZS78D</t>
+          <t>B0DQ8TM75J</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -6692,11 +6857,11 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>e27 vintage bulb 60w</t>
+          <t>es 8w led bulb</t>
         </is>
       </c>
       <c r="G81" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H81" t="b">
         <v>1</v>
@@ -6733,17 +6898,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>B0BLP1JSRK</t>
+          <t>B0B8P9BKXB</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>LDMST64E278</t>
+          <t>LDMG125E278</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>B0BLNZS78D</t>
+          <t>B0DQ8TM75J</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -6753,31 +6918,31 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>e27 es dimmable bulb 8w squirrel cage</t>
+          <t>g125 e27</t>
         </is>
       </c>
       <c r="G82" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="H82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>gap</t>
+          <t>present</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>pending_add</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -6794,17 +6959,17 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>B0BLP1JSRK</t>
+          <t>B0B8P9BKXB</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>LDMST64E278</t>
+          <t>LDMG125E278</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>B0BLNZS78D</t>
+          <t>B0DQ8TM75J</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -6814,31 +6979,31 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>bravo lighting bulbs 8w dimmable</t>
+          <t>e27 g125 amber led filament globe bulb dimmable</t>
         </is>
       </c>
       <c r="G83" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H83" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I83" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>gap</t>
+          <t>present</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>pending_add</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -6855,17 +7020,17 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>B0BLP1JSRK</t>
+          <t>B0B8P9BKXB</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>LDMST64E278</t>
+          <t>LDMG125E278</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>B0BLNZS78D</t>
+          <t>B0DQ8TM75J</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -6875,14 +7040,14 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>ledsone pack 3 | vintage led edison e27 light bulb, 8w (equivalent 60w) st64 dimmable 2700k warm white amber glass screw 806 lumens| energy saving bulb for squirrel cage lamp 220v [energy class a]</t>
+          <t>led e27 edison filament bulb light retro vintage screw globe lamp 8w</t>
         </is>
       </c>
       <c r="G84" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H84" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I84" t="b">
         <v>0</v>
@@ -6894,7 +7059,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>backend</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -6916,17 +7081,17 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>B0BLP1JSRK</t>
+          <t>B0B8P9BKXB</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>LDMST64E278</t>
+          <t>LDMG125E278</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>B0BLNZS78D</t>
+          <t>B0DQ8TM75J</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -6936,14 +7101,14 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>e27 8w vintage light bulbs</t>
+          <t>e27 large bulb dimmable</t>
         </is>
       </c>
       <c r="G85" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H85" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I85" t="b">
         <v>0</v>
@@ -6955,7 +7120,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>backend</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -6977,17 +7142,17 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>B0BLP1JSRK</t>
+          <t>B0B8P9BKXB</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>LDMST64E278</t>
+          <t>LDMG125E278</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>B0BLNZS78D</t>
+          <t>B0DQ8TM75J</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -6997,11 +7162,11 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>squirrel led cage dimmable</t>
+          <t>led bulb light large 120 mm x 160mm</t>
         </is>
       </c>
       <c r="G86" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H86" t="b">
         <v>0</v>
@@ -7038,17 +7203,17 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>B0BLP1JSRK</t>
+          <t>B0B8P9BKXB</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>LDMST64E278</t>
+          <t>LDMG125E278</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>B0BLNZS78D</t>
+          <t>B0DQ8TM75J</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -7058,31 +7223,31 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>bul-e27-rus-w1 bulb</t>
+          <t>led light bulb, e27</t>
         </is>
       </c>
       <c r="G87" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H87" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I87" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>gap</t>
+          <t>present</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>pending_add</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -7099,17 +7264,17 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>B0BLP1JSRK</t>
+          <t>B0B8P9BKXB</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>LDMST64E278</t>
+          <t>LDMG125E278</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>B0BLNZS78D</t>
+          <t>B0DQ8TM75J</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -7119,11 +7284,11 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>e27 8w 2200k 720lumen</t>
+          <t>large e27 vintage light bulbs 14cm retro</t>
         </is>
       </c>
       <c r="G88" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H88" t="b">
         <v>0</v>
@@ -7160,17 +7325,17 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>B0BLP1JSRK</t>
+          <t>B0B8P9BKXB</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>LDMST64E278</t>
+          <t>LDMG125E278</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>B0BLNZS78D</t>
+          <t>B0DQ8TM75J</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -7180,11 +7345,11 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>e27 dimmable bulb pack of six</t>
+          <t>e27 xl bulb</t>
         </is>
       </c>
       <c r="G89" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H89" t="b">
         <v>0</v>
@@ -7221,17 +7386,17 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>B0BLP1JSRK</t>
+          <t>B0B8P9BKXB</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>LDMST64E278</t>
+          <t>LDMG125E278</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>B0BLNZS78D</t>
+          <t>B0DQ8TM75J</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -7241,11 +7406,11 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>light bulbs screv wintage 8w</t>
+          <t>dimmable retro large 8w</t>
         </is>
       </c>
       <c r="G90" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H90" t="b">
         <v>0</v>
@@ -7282,17 +7447,17 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>B0BLP1JSRK</t>
+          <t>B0B8P9BKXB</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>LDMST64E278</t>
+          <t>LDMG125E278</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>B0BLNZS78D</t>
+          <t>B0DQ8TM75J</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -7302,11 +7467,11 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>e27 2700k dimmable 8w amber 6 pack</t>
+          <t>vintage led e27 g125 8w dimmable, amber glass, 2700k, 806 lumen</t>
         </is>
       </c>
       <c r="G91" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H91" t="b">
         <v>1</v>
@@ -7343,17 +7508,17 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>B0BLP1JSRK</t>
+          <t>B0B8P9BKXB</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>LDMST64E278</t>
+          <t>LDMG125E278</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>B0BLNZS78D</t>
+          <t>B0DQ8TM75J</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -7363,11 +7528,11 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>bulb warm yellliw pack 6</t>
+          <t>large bulb indoor e27 screw</t>
         </is>
       </c>
       <c r="G92" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H92" t="b">
         <v>0</v>
@@ -7404,17 +7569,17 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>B0BLP1JSRK</t>
+          <t>B0B8P9BKXB</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>LDMST64E278</t>
+          <t>LDMG125E278</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>B0BLNZS78D</t>
+          <t>B0DQ8TM75J</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -7424,14 +7589,14 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>squirrel cage vintage edison e27 screw bulb 8w clear</t>
+          <t>e27 8w vintage light bulbs</t>
         </is>
       </c>
       <c r="G93" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H93" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I93" t="b">
         <v>0</v>
@@ -7443,7 +7608,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>backend</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -7465,17 +7630,17 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>B0BLP1JSRK</t>
+          <t>B0B8P9BKXB</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>LDMST64E278</t>
+          <t>LDMG125E278</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>B0BLNZS78D</t>
+          <t>B0DQ8TM75J</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -7485,31 +7650,31 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>6 led e27 st64 8w 60 w dimmable warm white 2700k</t>
+          <t>edison g125</t>
         </is>
       </c>
       <c r="G94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H94" t="b">
         <v>1</v>
       </c>
       <c r="I94" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>gap</t>
+          <t>present</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>backend</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>pending_add</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -7526,17 +7691,17 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>B0BLP1JSRK</t>
+          <t>B0B8P9BKXB</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>LDMST64E278</t>
+          <t>LDMG125E278</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>B0BLNZS78D</t>
+          <t>B0DQ8TM75J</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -7546,31 +7711,31 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>vintage 60w es bulb pack not dimmable</t>
+          <t>e27 g125 vintage</t>
         </is>
       </c>
       <c r="G95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H95" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I95" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>gap</t>
+          <t>present</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>pending_add</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -7587,17 +7752,17 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>B0BLP1JSRK</t>
+          <t>B0B8P9BKXB</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>LDMST64E278</t>
+          <t>LDMG125E278</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>B0BLP1LN2C</t>
+          <t>B0DQ8TM75J</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -7607,14 +7772,14 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>e27 vintage bulb 60w</t>
+          <t>g125 led filament bulb smoked e27 warm</t>
         </is>
       </c>
       <c r="G96" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="H96" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I96" t="b">
         <v>0</v>
@@ -7626,7 +7791,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>backend</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -7648,17 +7813,17 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>B0BLP1JSRK</t>
+          <t>B0B8P9BKXB</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>LDMST64E278</t>
+          <t>LDMG125E278</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>B0BLP1LN2C</t>
+          <t>B0DQ8TM75J</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -7668,14 +7833,14 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>e27 es dimmable bulb 8w squirrel cage</t>
+          <t>led bulb dimmable filament amber e27 8w</t>
         </is>
       </c>
       <c r="G97" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H97" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I97" t="b">
         <v>0</v>
@@ -7687,7 +7852,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>backend</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -7709,17 +7874,17 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>B0BLP1JSRK</t>
+          <t>B0B8P9BKXB</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>LDMST64E278</t>
+          <t>LDMG125E278</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>B0BLP1LN2C</t>
+          <t>B0DQ8TM75J</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -7729,11 +7894,11 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>bravo lighting bulbs 8w dimmable</t>
+          <t>diall g125 e27 5.5w 470lm 330° amber globe warm white led filament light bulb</t>
         </is>
       </c>
       <c r="G98" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H98" t="b">
         <v>0</v>
@@ -7770,17 +7935,17 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>B0BLP1JSRK</t>
+          <t>B09477YHK7</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>LDMST64E278</t>
+          <t>LDMG95E278</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>B0BLP1LN2C</t>
+          <t>B0845ZBTJV</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -7790,31 +7955,31 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>ledsone pack 3 | vintage led edison e27 light bulb, 8w (equivalent 60w) st64 dimmable 2700k warm white amber glass screw 806 lumens| energy saving bulb for squirrel cage lamp 220v [energy class a]</t>
+          <t>e27 screw bulb</t>
         </is>
       </c>
       <c r="G99" t="n">
-        <v>4</v>
+        <v>11481</v>
       </c>
       <c r="H99" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I99" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>gap</t>
+          <t>present</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>pending_add</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -7831,17 +7996,17 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>B0BLP1JSRK</t>
+          <t>B09477YHK7</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>LDMST64E278</t>
+          <t>LDMG95E278</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>B0BLP1LN2C</t>
+          <t>B0845ZBTJV</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -7851,31 +8016,31 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>e27 8w vintage light bulbs</t>
+          <t>e27 dimmable bulb</t>
         </is>
       </c>
       <c r="G100" t="n">
-        <v>4</v>
+        <v>722</v>
       </c>
       <c r="H100" t="b">
         <v>1</v>
       </c>
       <c r="I100" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>gap</t>
+          <t>present</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>backend</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>pending_add</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -7892,17 +8057,17 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>B0BLP1JSRK</t>
+          <t>B09477YHK7</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>LDMST64E278</t>
+          <t>LDMG95E278</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>B0BLP1LN2C</t>
+          <t>B0845ZBTJV</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -7912,31 +8077,31 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>squirrel led cage dimmable</t>
+          <t>e27 edison screw bulb</t>
         </is>
       </c>
       <c r="G101" t="n">
-        <v>3</v>
+        <v>380</v>
       </c>
       <c r="H101" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I101" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>gap</t>
+          <t>present</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>pending_add</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -7953,17 +8118,17 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>B0BLP1JSRK</t>
+          <t>B09477YHK7</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>LDMST64E278</t>
+          <t>LDMG95E278</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>B0BLP1LN2C</t>
+          <t>B0845ZBTJV</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -7973,11 +8138,11 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>bul-e27-rus-w1 bulb</t>
+          <t>e27 bulb 60w</t>
         </is>
       </c>
       <c r="G102" t="n">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="H102" t="b">
         <v>0</v>
@@ -8014,17 +8179,17 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>B0BLP1JSRK</t>
+          <t>B09477YHK7</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>LDMST64E278</t>
+          <t>LDMG95E278</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>B0BLP1LN2C</t>
+          <t>B0845ZBTJV</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -8034,31 +8199,31 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>e27 8w 2200k 720lumen</t>
+          <t>g95 bulbs</t>
         </is>
       </c>
       <c r="G103" t="n">
-        <v>2</v>
+        <v>55</v>
       </c>
       <c r="H103" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I103" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>gap</t>
+          <t>present</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>pending_add</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -8075,17 +8240,17 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>B0BLP1JSRK</t>
+          <t>B09477YHK7</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>LDMST64E278</t>
+          <t>LDMG95E278</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>B0BLP1LN2C</t>
+          <t>B0845ZBTJV</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -8095,11 +8260,11 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>e27 dimmable bulb pack of six</t>
+          <t>4000k e27 bulb</t>
         </is>
       </c>
       <c r="G104" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="H104" t="b">
         <v>0</v>
@@ -8136,17 +8301,17 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>B0BLP1JSRK</t>
+          <t>B09477YHK7</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>LDMST64E278</t>
+          <t>LDMG95E278</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>B0BLP1LN2C</t>
+          <t>B0845ZBTJV</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -8156,17 +8321,17 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>light bulbs screv wintage 8w</t>
+          <t>e27 dimmable bulb warm white vintage</t>
         </is>
       </c>
       <c r="G105" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H105" t="b">
         <v>0</v>
       </c>
       <c r="I105" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
@@ -8175,7 +8340,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>bullet</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -8197,17 +8362,17 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>B0BLP1JSRK</t>
+          <t>B09477YHK7</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>LDMST64E278</t>
+          <t>LDMG95E278</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>B0BLP1LN2C</t>
+          <t>B0845ZBTJV</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -8217,14 +8382,14 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>e27 2700k dimmable 8w amber 6 pack</t>
+          <t>sklum e27 g95</t>
         </is>
       </c>
       <c r="G106" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H106" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I106" t="b">
         <v>0</v>
@@ -8236,7 +8401,7 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>backend</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -8258,17 +8423,17 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>B0BLP1JSRK</t>
+          <t>B09477YHK7</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>LDMST64E278</t>
+          <t>LDMG95E278</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>B0BLP1LN2C</t>
+          <t>B0845ZBTJV</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -8278,11 +8443,11 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>bulb warm yellliw pack 6</t>
+          <t>pack of 6 e27 globe bulbs</t>
         </is>
       </c>
       <c r="G107" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H107" t="b">
         <v>0</v>
@@ -8319,17 +8484,17 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>B0BLP1JSRK</t>
+          <t>B09477YHK7</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>LDMST64E278</t>
+          <t>LDMG95E278</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>B0BLP1LN2C</t>
+          <t>B0845ZBTJV</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -8339,31 +8504,31 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>squirrel cage vintage edison e27 screw bulb 8w clear</t>
+          <t>e27 globe dimmable led</t>
         </is>
       </c>
       <c r="G108" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H108" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I108" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>gap</t>
+          <t>present</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>pending_add</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -8380,17 +8545,17 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>B0BLP1JSRK</t>
+          <t>B09477YHK7</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>LDMST64E278</t>
+          <t>LDMG95E278</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>B0BLP1LN2C</t>
+          <t>B0845ZBTJV</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -8400,14 +8565,14 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>6 led e27 st64 8w 60 w dimmable warm white 2700k</t>
+          <t>philips 8w / 806 lumens / 2700k / e27</t>
         </is>
       </c>
       <c r="G109" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H109" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I109" t="b">
         <v>0</v>
@@ -8419,7 +8584,7 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>backend</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -8441,17 +8606,17 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>B0BLP1JSRK</t>
+          <t>B09477YHK7</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>LDMST64E278</t>
+          <t>LDMG95E278</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>B0BLP1LN2C</t>
+          <t>B0845ZBTJV</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -8461,11 +8626,11 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>vintage 60w es bulb pack not dimmable</t>
+          <t>95mm amber glass e27</t>
         </is>
       </c>
       <c r="G110" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H110" t="b">
         <v>0</v>
@@ -8512,7 +8677,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>B0D7HPWK2P</t>
+          <t>B0BLNZS78D</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -8529,7 +8694,7 @@
         <v>11</v>
       </c>
       <c r="H111" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I111" t="b">
         <v>0</v>
@@ -8541,7 +8706,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>backend</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -8573,7 +8738,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>B0D7HPWK2P</t>
+          <t>B0BLNZS78D</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -8634,7 +8799,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>B0D7HPWK2P</t>
+          <t>B0BLNZS78D</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -8695,7 +8860,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>B0D7HPWK2P</t>
+          <t>B0BLNZS78D</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -8756,7 +8921,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>B0D7HPWK2P</t>
+          <t>B0BLNZS78D</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -8817,7 +8982,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>B0D7HPWK2P</t>
+          <t>B0BLNZS78D</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -8837,7 +9002,7 @@
         <v>0</v>
       </c>
       <c r="I116" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J116" t="inlineStr">
         <is>
@@ -8846,7 +9011,7 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>bullet</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -8878,7 +9043,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>B0D7HPWK2P</t>
+          <t>B0BLNZS78D</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -8939,7 +9104,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>B0D7HPWK2P</t>
+          <t>B0BLNZS78D</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -9000,7 +9165,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>B0D7HPWK2P</t>
+          <t>B0BLNZS78D</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -9061,7 +9226,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>B0D7HPWK2P</t>
+          <t>B0BLNZS78D</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -9122,7 +9287,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>B0D7HPWK2P</t>
+          <t>B0BLNZS78D</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -9183,7 +9348,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>B0D7HPWK2P</t>
+          <t>B0BLNZS78D</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -9244,7 +9409,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>B0D7HPWK2P</t>
+          <t>B0BLNZS78D</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -9305,7 +9470,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>B0D7HPWK2P</t>
+          <t>B0BLNZS78D</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -9322,7 +9487,7 @@
         <v>1</v>
       </c>
       <c r="H124" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I124" t="b">
         <v>0</v>
@@ -9334,7 +9499,7 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>backend</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -9366,7 +9531,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>B0D7HPWK2P</t>
+          <t>B0BLNZS78D</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -9417,51 +9582,51 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>B0DCDSZ719</t>
+          <t>B0BLP1JSRK</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>LDSG95DIE274</t>
+          <t>LDMST64E278</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>B0DCFP1CX8</t>
+          <t>B0BLP1LN2C</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>sales_drop_3mo</t>
+          <t>zero_sales_6mo</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>vintage light bulb</t>
+          <t>e27 vintage bulb 60w</t>
         </is>
       </c>
       <c r="G126" t="n">
-        <v>394</v>
+        <v>11</v>
       </c>
       <c r="H126" t="b">
         <v>1</v>
       </c>
       <c r="I126" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>present</t>
+          <t>gap</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>backend</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>pending_add</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -9478,34 +9643,34 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>B0DCDSZ719</t>
+          <t>B0BLP1JSRK</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>LDSG95DIE274</t>
+          <t>LDMST64E278</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>B0DCFP1CX8</t>
+          <t>B0BLP1LN2C</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>sales_drop_3mo</t>
+          <t>zero_sales_6mo</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>decorative light bulbs</t>
+          <t>e27 es dimmable bulb 8w squirrel cage</t>
         </is>
       </c>
       <c r="G127" t="n">
-        <v>213</v>
+        <v>4</v>
       </c>
       <c r="H127" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I127" t="b">
         <v>0</v>
@@ -9517,7 +9682,7 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>backend</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -9539,34 +9704,34 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>B0DCDSZ719</t>
+          <t>B0BLP1JSRK</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>LDSG95DIE274</t>
+          <t>LDMST64E278</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>B0DCFP1CX8</t>
+          <t>B0BLP1LN2C</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>sales_drop_3mo</t>
+          <t>zero_sales_6mo</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>e27 vintage light bulbs</t>
+          <t>bravo lighting bulbs 8w dimmable</t>
         </is>
       </c>
       <c r="G128" t="n">
-        <v>177</v>
+        <v>4</v>
       </c>
       <c r="H128" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I128" t="b">
         <v>0</v>
@@ -9578,7 +9743,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>backend</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -9600,31 +9765,31 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>B0DCDSZ719</t>
+          <t>B0BLP1JSRK</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>LDSG95DIE274</t>
+          <t>LDMST64E278</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>B0DCFP1CX8</t>
+          <t>B0BLP1LN2C</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>sales_drop_3mo</t>
+          <t>zero_sales_6mo</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>e14 vintage bulb</t>
+          <t>ledsone pack 3 | vintage led edison e27 light bulb, 8w (equivalent 60w) st64 dimmable 2700k warm white amber glass screw 806 lumens| energy saving bulb for squirrel cage lamp 220v [energy class a]</t>
         </is>
       </c>
       <c r="G129" t="n">
-        <v>132</v>
+        <v>4</v>
       </c>
       <c r="H129" t="b">
         <v>0</v>
@@ -9661,34 +9826,34 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>B0DCDSZ719</t>
+          <t>B0BLP1JSRK</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>LDSG95DIE274</t>
+          <t>LDMST64E278</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>B0DCFP1CX8</t>
+          <t>B0BLP1LN2C</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>sales_drop_3mo</t>
+          <t>zero_sales_6mo</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>fancy light bulbs</t>
+          <t>e27 8w vintage light bulbs</t>
         </is>
       </c>
       <c r="G130" t="n">
-        <v>64</v>
+        <v>4</v>
       </c>
       <c r="H130" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I130" t="b">
         <v>0</v>
@@ -9700,7 +9865,7 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>backend</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -9722,51 +9887,51 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>B0DCDSZ719</t>
+          <t>B0BLP1JSRK</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>LDSG95DIE274</t>
+          <t>LDMST64E278</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>B0DCFP1CX8</t>
+          <t>B0BLP1LN2C</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>sales_drop_3mo</t>
+          <t>zero_sales_6mo</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>dimmable led vintage</t>
+          <t>squirrel led cage dimmable</t>
         </is>
       </c>
       <c r="G131" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="H131" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I131" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>present</t>
+          <t>gap</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>pending_add</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -9783,31 +9948,31 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>B0DCDSZ719</t>
+          <t>B0BLP1JSRK</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>LDSG95DIE274</t>
+          <t>LDMST64E278</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>B0DCFP1CX8</t>
+          <t>B0BLP1LN2C</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>sales_drop_3mo</t>
+          <t>zero_sales_6mo</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>e14 2w diamond shaped bulb</t>
+          <t>bul-e27-rus-w1 bulb</t>
         </is>
       </c>
       <c r="G132" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="H132" t="b">
         <v>0</v>
@@ -9844,31 +10009,31 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>B0DCDSZ719</t>
+          <t>B0BLP1JSRK</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>LDSG95DIE274</t>
+          <t>LDMST64E278</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>B0DCFP1CX8</t>
+          <t>B0BLP1LN2C</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>sales_drop_3mo</t>
+          <t>zero_sales_6mo</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>fancy lightbulbs</t>
+          <t>e27 8w 2200k 720lumen</t>
         </is>
       </c>
       <c r="G133" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H133" t="b">
         <v>0</v>
@@ -9905,31 +10070,31 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>B0DCDSZ719</t>
+          <t>B0BLP1JSRK</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>LDSG95DIE274</t>
+          <t>LDMST64E278</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>B0DCFP1CX8</t>
+          <t>B0BLP1LN2C</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>sales_drop_3mo</t>
+          <t>zero_sales_6mo</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>e17 warm light bulb</t>
+          <t>e27 dimmable bulb pack of six</t>
         </is>
       </c>
       <c r="G134" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H134" t="b">
         <v>0</v>
@@ -9966,31 +10131,31 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>B0DCDSZ719</t>
+          <t>B0BLP1JSRK</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>LDSG95DIE274</t>
+          <t>LDMST64E278</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>B0DCFP1CX8</t>
+          <t>B0BLP1LN2C</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>sales_drop_3mo</t>
+          <t>zero_sales_6mo</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>decorative led bulb xxl</t>
+          <t>light bulbs screv wintage 8w</t>
         </is>
       </c>
       <c r="G135" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H135" t="b">
         <v>0</v>
@@ -10027,17 +10192,17 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>B0DCDSZ719</t>
+          <t>B0BLP1JSRK</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>LDSG95DIE274</t>
+          <t>LDMST64E278</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>B0DR1XY3R6</t>
+          <t>B0BLP1LN2C</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -10047,31 +10212,31 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>vintage light bulb</t>
+          <t>e27 2700k dimmable 8w amber 6 pack</t>
         </is>
       </c>
       <c r="G136" t="n">
-        <v>394</v>
+        <v>1</v>
       </c>
       <c r="H136" t="b">
         <v>1</v>
       </c>
       <c r="I136" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>present</t>
+          <t>gap</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>backend</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>pending_add</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
@@ -10088,17 +10253,17 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>B0DCDSZ719</t>
+          <t>B0BLP1JSRK</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>LDSG95DIE274</t>
+          <t>LDMST64E278</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>B0DR1XY3R6</t>
+          <t>B0BLP1LN2C</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -10108,31 +10273,31 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>decorative light bulbs</t>
+          <t>bulb warm yellliw pack 6</t>
         </is>
       </c>
       <c r="G137" t="n">
-        <v>213</v>
+        <v>1</v>
       </c>
       <c r="H137" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I137" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>present</t>
+          <t>gap</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>pending_add</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
@@ -10149,17 +10314,17 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>B0DCDSZ719</t>
+          <t>B0BLP1JSRK</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>LDSG95DIE274</t>
+          <t>LDMST64E278</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>B0DR1XY3R6</t>
+          <t>B0BLP1LN2C</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -10169,31 +10334,31 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>e27 vintage light bulbs</t>
+          <t>squirrel cage vintage edison e27 screw bulb 8w clear</t>
         </is>
       </c>
       <c r="G138" t="n">
-        <v>177</v>
+        <v>1</v>
       </c>
       <c r="H138" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I138" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>present</t>
+          <t>gap</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>pending_add</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
@@ -10210,17 +10375,17 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>B0DCDSZ719</t>
+          <t>B0BLP1JSRK</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>LDSG95DIE274</t>
+          <t>LDMST64E278</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>B0DR1XY3R6</t>
+          <t>B0BLP1LN2C</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -10230,14 +10395,14 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>e14 vintage bulb</t>
+          <t>6 led e27 st64 8w 60 w dimmable warm white 2700k</t>
         </is>
       </c>
       <c r="G139" t="n">
-        <v>132</v>
+        <v>1</v>
       </c>
       <c r="H139" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I139" t="b">
         <v>0</v>
@@ -10249,7 +10414,7 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>backend</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -10271,17 +10436,17 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>B0DCDSZ719</t>
+          <t>B0BLP1JSRK</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>LDSG95DIE274</t>
+          <t>LDMST64E278</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>B0DR1XY3R6</t>
+          <t>B0BLP1LN2C</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -10291,31 +10456,31 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>fancy light bulbs</t>
+          <t>vintage 60w es bulb pack not dimmable</t>
         </is>
       </c>
       <c r="G140" t="n">
-        <v>64</v>
+        <v>1</v>
       </c>
       <c r="H140" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I140" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>present</t>
+          <t>gap</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>pending_add</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
@@ -10332,17 +10497,17 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>B0DCDSZ719</t>
+          <t>B0BLP1JSRK</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>LDSG95DIE274</t>
+          <t>LDMST64E278</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>B0DR1XY3R6</t>
+          <t>B0D7HPWK2P</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -10352,31 +10517,31 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>dimmable led vintage</t>
+          <t>e27 vintage bulb 60w</t>
         </is>
       </c>
       <c r="G141" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H141" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I141" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>present</t>
+          <t>gap</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>pending_add</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
@@ -10393,17 +10558,17 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>B0DCDSZ719</t>
+          <t>B0BLP1JSRK</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>LDSG95DIE274</t>
+          <t>LDMST64E278</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>B0DR1XY3R6</t>
+          <t>B0D7HPWK2P</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -10413,11 +10578,11 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>e14 2w diamond shaped bulb</t>
+          <t>e27 es dimmable bulb 8w squirrel cage</t>
         </is>
       </c>
       <c r="G142" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="H142" t="b">
         <v>0</v>
@@ -10454,17 +10619,17 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>B0DCDSZ719</t>
+          <t>B0BLP1JSRK</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>LDSG95DIE274</t>
+          <t>LDMST64E278</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>B0DR1XY3R6</t>
+          <t>B0D7HPWK2P</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -10474,11 +10639,11 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>fancy lightbulbs</t>
+          <t>bravo lighting bulbs 8w dimmable</t>
         </is>
       </c>
       <c r="G143" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H143" t="b">
         <v>0</v>
@@ -10515,17 +10680,17 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>B0DCDSZ719</t>
+          <t>B0BLP1JSRK</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>LDSG95DIE274</t>
+          <t>LDMST64E278</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>B0DR1XY3R6</t>
+          <t>B0D7HPWK2P</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -10535,7 +10700,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>e17 warm light bulb</t>
+          <t>ledsone pack 3 | vintage led edison e27 light bulb, 8w (equivalent 60w) st64 dimmable 2700k warm white amber glass screw 806 lumens| energy saving bulb for squirrel cage lamp 220v [energy class a]</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -10545,7 +10710,7 @@
         <v>0</v>
       </c>
       <c r="I144" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J144" t="inlineStr">
         <is>
@@ -10554,7 +10719,7 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>bullet</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
@@ -10576,61 +10741,2928 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
+          <t>B0BLP1JSRK</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>LDMST64E278</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>B0D7HPWK2P</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>zero_sales_6mo</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>e27 8w vintage light bulbs</t>
+        </is>
+      </c>
+      <c r="G145" t="n">
+        <v>4</v>
+      </c>
+      <c r="H145" t="b">
+        <v>1</v>
+      </c>
+      <c r="I145" t="b">
+        <v>0</v>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>pending_add</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>ledsone_uk</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>B0BLP1JSRK</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>LDMST64E278</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>B0D7HPWK2P</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>zero_sales_6mo</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>squirrel led cage dimmable</t>
+        </is>
+      </c>
+      <c r="G146" t="n">
+        <v>3</v>
+      </c>
+      <c r="H146" t="b">
+        <v>0</v>
+      </c>
+      <c r="I146" t="b">
+        <v>1</v>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>bullet</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>pending_add</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>ledsone_uk</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>B0BLP1JSRK</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>LDMST64E278</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>B0D7HPWK2P</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>zero_sales_6mo</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>bul-e27-rus-w1 bulb</t>
+        </is>
+      </c>
+      <c r="G147" t="n">
+        <v>3</v>
+      </c>
+      <c r="H147" t="b">
+        <v>0</v>
+      </c>
+      <c r="I147" t="b">
+        <v>0</v>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>backend_and_bullet</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>pending_add</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>ledsone_uk</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>B0BLP1JSRK</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>LDMST64E278</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>B0D7HPWK2P</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>zero_sales_6mo</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>e27 8w 2200k 720lumen</t>
+        </is>
+      </c>
+      <c r="G148" t="n">
+        <v>2</v>
+      </c>
+      <c r="H148" t="b">
+        <v>0</v>
+      </c>
+      <c r="I148" t="b">
+        <v>0</v>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>backend_and_bullet</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>pending_add</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>ledsone_uk</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>B0BLP1JSRK</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>LDMST64E278</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>B0D7HPWK2P</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>zero_sales_6mo</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>e27 dimmable bulb pack of six</t>
+        </is>
+      </c>
+      <c r="G149" t="n">
+        <v>2</v>
+      </c>
+      <c r="H149" t="b">
+        <v>0</v>
+      </c>
+      <c r="I149" t="b">
+        <v>0</v>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>backend_and_bullet</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>pending_add</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>ledsone_uk</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>B0BLP1JSRK</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>LDMST64E278</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>B0D7HPWK2P</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>zero_sales_6mo</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>light bulbs screv wintage 8w</t>
+        </is>
+      </c>
+      <c r="G150" t="n">
+        <v>2</v>
+      </c>
+      <c r="H150" t="b">
+        <v>0</v>
+      </c>
+      <c r="I150" t="b">
+        <v>0</v>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>backend_and_bullet</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>pending_add</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>ledsone_uk</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>B0BLP1JSRK</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>LDMST64E278</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>B0D7HPWK2P</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>zero_sales_6mo</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>e27 2700k dimmable 8w amber 6 pack</t>
+        </is>
+      </c>
+      <c r="G151" t="n">
+        <v>1</v>
+      </c>
+      <c r="H151" t="b">
+        <v>1</v>
+      </c>
+      <c r="I151" t="b">
+        <v>0</v>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>pending_add</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>ledsone_uk</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>B0BLP1JSRK</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>LDMST64E278</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>B0D7HPWK2P</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>zero_sales_6mo</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>bulb warm yellliw pack 6</t>
+        </is>
+      </c>
+      <c r="G152" t="n">
+        <v>1</v>
+      </c>
+      <c r="H152" t="b">
+        <v>0</v>
+      </c>
+      <c r="I152" t="b">
+        <v>0</v>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>backend_and_bullet</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>pending_add</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>ledsone_uk</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>B0BLP1JSRK</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>LDMST64E278</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>B0D7HPWK2P</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>zero_sales_6mo</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>squirrel cage vintage edison e27 screw bulb 8w clear</t>
+        </is>
+      </c>
+      <c r="G153" t="n">
+        <v>1</v>
+      </c>
+      <c r="H153" t="b">
+        <v>0</v>
+      </c>
+      <c r="I153" t="b">
+        <v>0</v>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>backend_and_bullet</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>pending_add</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>ledsone_uk</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>B0BLP1JSRK</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>LDMST64E278</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>B0D7HPWK2P</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>zero_sales_6mo</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>6 led e27 st64 8w 60 w dimmable warm white 2700k</t>
+        </is>
+      </c>
+      <c r="G154" t="n">
+        <v>1</v>
+      </c>
+      <c r="H154" t="b">
+        <v>0</v>
+      </c>
+      <c r="I154" t="b">
+        <v>0</v>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>backend_and_bullet</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>pending_add</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>ledsone_uk</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>B0BLP1JSRK</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>LDMST64E278</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>B0D7HPWK2P</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>zero_sales_6mo</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>vintage 60w es bulb pack not dimmable</t>
+        </is>
+      </c>
+      <c r="G155" t="n">
+        <v>1</v>
+      </c>
+      <c r="H155" t="b">
+        <v>0</v>
+      </c>
+      <c r="I155" t="b">
+        <v>0</v>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>backend_and_bullet</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>pending_add</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>ledsone_uk</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>B09JM3PLLH</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>LDSG125LOE274</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>B0DBTNQT8Z</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>zero_sales_6mo</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>large e27 vintage light bulbs</t>
+        </is>
+      </c>
+      <c r="G156" t="n">
+        <v>150</v>
+      </c>
+      <c r="H156" t="b">
+        <v>0</v>
+      </c>
+      <c r="I156" t="b">
+        <v>0</v>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>backend_and_bullet</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>pending_add</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>ledsone_uk</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>B09JM3PLLH</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>LDSG125LOE274</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>B0DBTNQT8Z</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>zero_sales_6mo</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>edison bulb</t>
+        </is>
+      </c>
+      <c r="G157" t="n">
+        <v>133</v>
+      </c>
+      <c r="H157" t="b">
+        <v>1</v>
+      </c>
+      <c r="I157" t="b">
+        <v>1</v>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>present</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>ledsone_uk</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>B09JM3PLLH</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>LDSG125LOE274</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>B0DBTNQT8Z</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>zero_sales_6mo</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>love light bulb</t>
+        </is>
+      </c>
+      <c r="G158" t="n">
+        <v>74</v>
+      </c>
+      <c r="H158" t="b">
+        <v>1</v>
+      </c>
+      <c r="I158" t="b">
+        <v>1</v>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>present</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>ledsone_uk</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>B09JM3PLLH</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>LDSG125LOE274</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>B0DBTNQT8Z</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>zero_sales_6mo</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>e27 screw bulb decorative</t>
+        </is>
+      </c>
+      <c r="G159" t="n">
+        <v>55</v>
+      </c>
+      <c r="H159" t="b">
+        <v>1</v>
+      </c>
+      <c r="I159" t="b">
+        <v>0</v>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>pending_add</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>ledsone_uk</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>B09JM3PLLH</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>LDSG125LOE274</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>B0DBTNQT8Z</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>zero_sales_6mo</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>e27 large globe bulb</t>
+        </is>
+      </c>
+      <c r="G160" t="n">
+        <v>50</v>
+      </c>
+      <c r="H160" t="b">
+        <v>0</v>
+      </c>
+      <c r="I160" t="b">
+        <v>0</v>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>backend_and_bullet</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>pending_add</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>ledsone_uk</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>B09JM3PLLH</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>LDSG125LOE274</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>B0DBTNQT8Z</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>zero_sales_6mo</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>extra large edison bulb</t>
+        </is>
+      </c>
+      <c r="G161" t="n">
+        <v>40</v>
+      </c>
+      <c r="H161" t="b">
+        <v>0</v>
+      </c>
+      <c r="I161" t="b">
+        <v>0</v>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>backend_and_bullet</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>pending_add</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>ledsone_uk</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>B09JM3PLLH</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>LDSG125LOE274</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>B0DBTNQT8Z</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>zero_sales_6mo</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>big bulb</t>
+        </is>
+      </c>
+      <c r="G162" t="n">
+        <v>20</v>
+      </c>
+      <c r="H162" t="b">
+        <v>0</v>
+      </c>
+      <c r="I162" t="b">
+        <v>1</v>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>bullet</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>pending_add</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>ledsone_uk</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>B09JM3PLLH</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>LDSG125LOE274</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>B0DBTNQT8Z</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>zero_sales_6mo</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>e27 screw bulb spiral</t>
+        </is>
+      </c>
+      <c r="G163" t="n">
+        <v>17</v>
+      </c>
+      <c r="H163" t="b">
+        <v>0</v>
+      </c>
+      <c r="I163" t="b">
+        <v>0</v>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>backend_and_bullet</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>pending_add</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>ledsone_uk</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>B09JM3PLLH</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>LDSG125LOE274</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>B0DBTNQT8Z</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>zero_sales_6mo</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>warm white large screw light bulbs</t>
+        </is>
+      </c>
+      <c r="G164" t="n">
+        <v>16</v>
+      </c>
+      <c r="H164" t="b">
+        <v>0</v>
+      </c>
+      <c r="I164" t="b">
+        <v>0</v>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>backend_and_bullet</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>pending_add</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>ledsone_uk</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>B09JM3PLLH</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>LDSG125LOE274</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>B0DBTNQT8Z</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>zero_sales_6mo</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>love bulb</t>
+        </is>
+      </c>
+      <c r="G165" t="n">
+        <v>14</v>
+      </c>
+      <c r="H165" t="b">
+        <v>1</v>
+      </c>
+      <c r="I165" t="b">
+        <v>1</v>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>present</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>ledsone_uk</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>B09JM3PLLH</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>LDSG125LOE274</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>B0DBTNQT8Z</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>zero_sales_6mo</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>g125 led bulb</t>
+        </is>
+      </c>
+      <c r="G166" t="n">
+        <v>6</v>
+      </c>
+      <c r="H166" t="b">
+        <v>1</v>
+      </c>
+      <c r="I166" t="b">
+        <v>1</v>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>present</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>ledsone_uk</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>B09JM3PLLH</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>LDSG125LOE274</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>B0DBTNQT8Z</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>zero_sales_6mo</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>screw e27 led light bulb, 4w globe large screw vintage edison led bulbs</t>
+        </is>
+      </c>
+      <c r="G167" t="n">
+        <v>6</v>
+      </c>
+      <c r="H167" t="b">
+        <v>0</v>
+      </c>
+      <c r="I167" t="b">
+        <v>0</v>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>backend_and_bullet</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>pending_add</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>ledsone_uk</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>B09JM3PLLH</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>LDSG125LOE274</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>B0DBTNQT8Z</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>zero_sales_6mo</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>large edison screw bulb warm white</t>
+        </is>
+      </c>
+      <c r="G168" t="n">
+        <v>5</v>
+      </c>
+      <c r="H168" t="b">
+        <v>0</v>
+      </c>
+      <c r="I168" t="b">
+        <v>0</v>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>backend_and_bullet</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>pending_add</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>ledsone_uk</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>B09JM3PLLH</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>LDSG125LOE274</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>B0DBTNQT8Z</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>zero_sales_6mo</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>light bulb with amber love</t>
+        </is>
+      </c>
+      <c r="G169" t="n">
+        <v>5</v>
+      </c>
+      <c r="H169" t="b">
+        <v>1</v>
+      </c>
+      <c r="I169" t="b">
+        <v>0</v>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>pending_add</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>ledsone_uk</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>B09JM3PLLH</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>LDSG125LOE274</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>B0DBTNQT8Z</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>zero_sales_6mo</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>es love light bulb</t>
+        </is>
+      </c>
+      <c r="G170" t="n">
+        <v>3</v>
+      </c>
+      <c r="H170" t="b">
+        <v>1</v>
+      </c>
+      <c r="I170" t="b">
+        <v>1</v>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>present</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>ledsone_uk</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>B09JM3PLLH</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>LDSG125LOE274</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>B0DBTNQT8Z</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>zero_sales_6mo</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>e27 love light balb</t>
+        </is>
+      </c>
+      <c r="G171" t="n">
+        <v>2</v>
+      </c>
+      <c r="H171" t="b">
+        <v>0</v>
+      </c>
+      <c r="I171" t="b">
+        <v>0</v>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>backend_and_bullet</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>pending_add</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>ledsone_uk</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>B09JM3PLLH</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>LDSG125LOE274</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>B0DBTNQT8Z</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>zero_sales_6mo</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>bulb writing</t>
+        </is>
+      </c>
+      <c r="G172" t="n">
+        <v>1</v>
+      </c>
+      <c r="H172" t="b">
+        <v>0</v>
+      </c>
+      <c r="I172" t="b">
+        <v>0</v>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>backend_and_bullet</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>pending_add</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>ledsone_uk</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
           <t>B0DCDSZ719</t>
         </is>
       </c>
-      <c r="C145" t="inlineStr">
+      <c r="C173" t="inlineStr">
         <is>
           <t>LDSG95DIE274</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr">
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>B0DCFP1CX8</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>sales_drop_3mo</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>vintage light bulb</t>
+        </is>
+      </c>
+      <c r="G173" t="n">
+        <v>394</v>
+      </c>
+      <c r="H173" t="b">
+        <v>1</v>
+      </c>
+      <c r="I173" t="b">
+        <v>1</v>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>present</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>ledsone_uk</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>B0DCDSZ719</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>LDSG95DIE274</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>B0DCFP1CX8</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>sales_drop_3mo</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>decorative light bulbs</t>
+        </is>
+      </c>
+      <c r="G174" t="n">
+        <v>213</v>
+      </c>
+      <c r="H174" t="b">
+        <v>1</v>
+      </c>
+      <c r="I174" t="b">
+        <v>0</v>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>pending_add</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>ledsone_uk</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>B0DCDSZ719</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>LDSG95DIE274</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>B0DCFP1CX8</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>sales_drop_3mo</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>e27 vintage light bulbs</t>
+        </is>
+      </c>
+      <c r="G175" t="n">
+        <v>177</v>
+      </c>
+      <c r="H175" t="b">
+        <v>1</v>
+      </c>
+      <c r="I175" t="b">
+        <v>0</v>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>pending_add</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>ledsone_uk</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>B0DCDSZ719</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>LDSG95DIE274</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>B0DCFP1CX8</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>sales_drop_3mo</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>e14 vintage bulb</t>
+        </is>
+      </c>
+      <c r="G176" t="n">
+        <v>132</v>
+      </c>
+      <c r="H176" t="b">
+        <v>0</v>
+      </c>
+      <c r="I176" t="b">
+        <v>0</v>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>backend_and_bullet</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>pending_add</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>ledsone_uk</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>B0DCDSZ719</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>LDSG95DIE274</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>B0DCFP1CX8</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>sales_drop_3mo</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>fancy light bulbs</t>
+        </is>
+      </c>
+      <c r="G177" t="n">
+        <v>64</v>
+      </c>
+      <c r="H177" t="b">
+        <v>0</v>
+      </c>
+      <c r="I177" t="b">
+        <v>0</v>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>backend_and_bullet</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>pending_add</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>ledsone_uk</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>B0DCDSZ719</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>LDSG95DIE274</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>B0DCFP1CX8</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>sales_drop_3mo</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>dimmable led vintage</t>
+        </is>
+      </c>
+      <c r="G178" t="n">
+        <v>16</v>
+      </c>
+      <c r="H178" t="b">
+        <v>1</v>
+      </c>
+      <c r="I178" t="b">
+        <v>1</v>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>present</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>ledsone_uk</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>B0DCDSZ719</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>LDSG95DIE274</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>B0DCFP1CX8</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>sales_drop_3mo</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>e14 2w diamond shaped bulb</t>
+        </is>
+      </c>
+      <c r="G179" t="n">
+        <v>11</v>
+      </c>
+      <c r="H179" t="b">
+        <v>0</v>
+      </c>
+      <c r="I179" t="b">
+        <v>0</v>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>backend_and_bullet</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>pending_add</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>ledsone_uk</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>B0DCDSZ719</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>LDSG95DIE274</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>B0DCFP1CX8</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>sales_drop_3mo</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>fancy lightbulbs</t>
+        </is>
+      </c>
+      <c r="G180" t="n">
+        <v>10</v>
+      </c>
+      <c r="H180" t="b">
+        <v>0</v>
+      </c>
+      <c r="I180" t="b">
+        <v>0</v>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>backend_and_bullet</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>pending_add</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>ledsone_uk</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>B0DCDSZ719</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>LDSG95DIE274</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>B0DCFP1CX8</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>sales_drop_3mo</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>e17 warm light bulb</t>
+        </is>
+      </c>
+      <c r="G181" t="n">
+        <v>4</v>
+      </c>
+      <c r="H181" t="b">
+        <v>0</v>
+      </c>
+      <c r="I181" t="b">
+        <v>0</v>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>backend_and_bullet</t>
+        </is>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>pending_add</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>ledsone_uk</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>B0DCDSZ719</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>LDSG95DIE274</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>B0DCFP1CX8</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>sales_drop_3mo</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>decorative led bulb xxl</t>
+        </is>
+      </c>
+      <c r="G182" t="n">
+        <v>3</v>
+      </c>
+      <c r="H182" t="b">
+        <v>0</v>
+      </c>
+      <c r="I182" t="b">
+        <v>0</v>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>backend_and_bullet</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>pending_add</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>ledsone_uk</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>B0DCDSZ719</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>LDSG95DIE274</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
         <is>
           <t>B0DR1XY3R6</t>
         </is>
       </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>zero_sales_6mo</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>zero_sales_6mo</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>vintage light bulb</t>
+        </is>
+      </c>
+      <c r="G183" t="n">
+        <v>394</v>
+      </c>
+      <c r="H183" t="b">
+        <v>1</v>
+      </c>
+      <c r="I183" t="b">
+        <v>1</v>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>present</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>ledsone_uk</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>B0DCDSZ719</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>LDSG95DIE274</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>B0DR1XY3R6</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>zero_sales_6mo</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>decorative light bulbs</t>
+        </is>
+      </c>
+      <c r="G184" t="n">
+        <v>213</v>
+      </c>
+      <c r="H184" t="b">
+        <v>1</v>
+      </c>
+      <c r="I184" t="b">
+        <v>1</v>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>present</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>ledsone_uk</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>B0DCDSZ719</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>LDSG95DIE274</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>B0DR1XY3R6</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>zero_sales_6mo</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>e27 vintage light bulbs</t>
+        </is>
+      </c>
+      <c r="G185" t="n">
+        <v>177</v>
+      </c>
+      <c r="H185" t="b">
+        <v>1</v>
+      </c>
+      <c r="I185" t="b">
+        <v>1</v>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>present</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>ledsone_uk</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>B0DCDSZ719</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>LDSG95DIE274</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>B0DR1XY3R6</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>zero_sales_6mo</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>e14 vintage bulb</t>
+        </is>
+      </c>
+      <c r="G186" t="n">
+        <v>132</v>
+      </c>
+      <c r="H186" t="b">
+        <v>0</v>
+      </c>
+      <c r="I186" t="b">
+        <v>0</v>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>backend_and_bullet</t>
+        </is>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>pending_add</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>ledsone_uk</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>B0DCDSZ719</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>LDSG95DIE274</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>B0DR1XY3R6</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>zero_sales_6mo</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>fancy light bulbs</t>
+        </is>
+      </c>
+      <c r="G187" t="n">
+        <v>64</v>
+      </c>
+      <c r="H187" t="b">
+        <v>1</v>
+      </c>
+      <c r="I187" t="b">
+        <v>1</v>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>present</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>ledsone_uk</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>B0DCDSZ719</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>LDSG95DIE274</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>B0DR1XY3R6</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>zero_sales_6mo</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>dimmable led vintage</t>
+        </is>
+      </c>
+      <c r="G188" t="n">
+        <v>16</v>
+      </c>
+      <c r="H188" t="b">
+        <v>1</v>
+      </c>
+      <c r="I188" t="b">
+        <v>1</v>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>present</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>ledsone_uk</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>B0DCDSZ719</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>LDSG95DIE274</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>B0DR1XY3R6</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>zero_sales_6mo</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>e14 2w diamond shaped bulb</t>
+        </is>
+      </c>
+      <c r="G189" t="n">
+        <v>11</v>
+      </c>
+      <c r="H189" t="b">
+        <v>0</v>
+      </c>
+      <c r="I189" t="b">
+        <v>0</v>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>backend_and_bullet</t>
+        </is>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>pending_add</t>
+        </is>
+      </c>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>ledsone_uk</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>B0DCDSZ719</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>LDSG95DIE274</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>B0DR1XY3R6</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>zero_sales_6mo</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>fancy lightbulbs</t>
+        </is>
+      </c>
+      <c r="G190" t="n">
+        <v>10</v>
+      </c>
+      <c r="H190" t="b">
+        <v>0</v>
+      </c>
+      <c r="I190" t="b">
+        <v>0</v>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>backend_and_bullet</t>
+        </is>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>pending_add</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>ledsone_uk</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>B0DCDSZ719</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>LDSG95DIE274</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>B0DR1XY3R6</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>zero_sales_6mo</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>e17 warm light bulb</t>
+        </is>
+      </c>
+      <c r="G191" t="n">
+        <v>4</v>
+      </c>
+      <c r="H191" t="b">
+        <v>0</v>
+      </c>
+      <c r="I191" t="b">
+        <v>1</v>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>bullet</t>
+        </is>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>pending_add</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>ledsone_uk</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>B0DCDSZ719</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>LDSG95DIE274</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>B0DR1XY3R6</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>zero_sales_6mo</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
         <is>
           <t>decorative led bulb xxl</t>
         </is>
       </c>
-      <c r="G145" t="n">
+      <c r="G192" t="n">
         <v>3</v>
       </c>
-      <c r="H145" t="b">
-        <v>0</v>
-      </c>
-      <c r="I145" t="b">
-        <v>0</v>
-      </c>
-      <c r="J145" t="inlineStr">
-        <is>
-          <t>gap</t>
-        </is>
-      </c>
-      <c r="K145" t="inlineStr">
+      <c r="H192" t="b">
+        <v>0</v>
+      </c>
+      <c r="I192" t="b">
+        <v>0</v>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
         <is>
           <t>backend_and_bullet</t>
         </is>
       </c>
-      <c r="L145" t="inlineStr">
-        <is>
-          <t>pending_add</t>
-        </is>
-      </c>
-      <c r="M145" t="inlineStr">
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>pending_add</t>
+        </is>
+      </c>
+      <c r="M192" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M145"/>
+  <autoFilter ref="A1:M192"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/development/abiraj_mini_aios_workbench/projects/PRJ-2026-026_amazon-keyword-gap-sync/evidence/final_outputs/REQ-30_amazon-keyword-gap-sync/REQ-30-D02_keyword_gap_report.xlsx
+++ b/development/abiraj_mini_aios_workbench/projects/PRJ-2026-026_amazon-keyword-gap-sync/evidence/final_outputs/REQ-30_amazon-keyword-gap-sync/REQ-30-D02_keyword_gap_report.xlsx
@@ -10,12 +10,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes &amp; Method" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Part A - No Content" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Part B - Keyword Gaps" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Field Reference" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Part C - SKU mismatch" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Field Reference" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Part A - No Content'!$A$1:$K$22</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Part B - Keyword Gaps'!$A$1:$M$192</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Field Reference'!$A$1:$B$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Part A - No Content'!$A$1:$K$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Part B - Keyword Gaps'!$A$1:$M$151</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Part C - SKU mismatch'!$A$1:$L$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Field Reference'!$A$1:$B$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -444,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -490,7 +492,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-19T11:46:28</t>
+          <t>2026-08-19T11:52:27</t>
         </is>
       </c>
     </row>
@@ -634,7 +636,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>1_account_separation=PASS; 3_one_place_is_enough=PASS; 4_dual_method_independent=PASS; 5_directional_add_logic=PASS; 6_zero_manual_lookup=PASS; 7_monthly_cadence=PASS</t>
+          <t>1_account_separation=PASS; 2_sku_mismatch_never_paired=PASS; 3_one_place_is_enough=PASS; 4_dual_method_independent=PASS; 5_directional_add_logic=PASS; 6_zero_manual_lookup=PASS; 7_monthly_cadence=PASS</t>
         </is>
       </c>
     </row>
@@ -658,19 +660,31 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>21 listings with NO CONTENT — empty backend keyword field and/or no bullet points. Every keyword would show as 'missing' because there is nothing to search. These need a rewrite, not keyword edits (rule Q12).</t>
+          <t>20 listings with NO CONTENT — empty backend keyword field and/or no bullet points. Every keyword would show as 'missing' because there is nothing to search. These need a rewrite, not keyword edits (rule Q12).</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>Part C</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>3 pairs REJECTED — same base SKU but the two listings state different wattage, so the stored SKU is wrong. Not keyword-checked; the SKU needs correcting first.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
           <t>Part B</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>191 keyword rows across listings that DO have content — 149 real, actionable gaps.</t>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>150 keyword rows across listings that DO have content — 115 real, actionable gaps.</t>
         </is>
       </c>
     </row>
@@ -685,7 +699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -876,22 +890,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>B09Z6P8H29</t>
+          <t>B0B8P9BKXB</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>LDCWB223</t>
+          <t>LDMG125E278</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>B0D5CMBXK6</t>
+          <t>B08G4YZDH5</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>LDCWB2236PK</t>
+          <t>LDMG125E278_VDS</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -901,7 +915,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>backend keyword field empty</t>
+          <t>backend keyword field empty; no bullet points; no description</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -910,11 +924,11 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>LEDSone B22 Bayonet LED Light Bulb, GLS B22 LED Bulbs Cool White 6000K, Energy Saver Bulb, 80lm/W Lumen, Non-Dimmable (6 Pack, 3W)</t>
+          <t>LEDSone Vintage LED G125 Globe 8W E27 Screw Bulb Retro e27 Edison Light Bulbs Lamp Dimmable LED Filament Ampoule Warm Yellow Bulbs</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -941,12 +955,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>B08G4YZDH5</t>
+          <t>B09M42QJCS</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>LDMG125E278_VDS</t>
+          <t>LDMG125E2785PK_DCVV</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -969,7 +983,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>LEDSone Vintage LED G125 Globe 8W E27 Screw Bulb Retro e27 Edison Light Bulbs Lamp Dimmable LED Filament Ampoule Warm Yellow Bulbs</t>
+          <t>DC VOLTAGE Pack 5 | Vintage LED Screw E27 Bulb,Edison G125 8W LED Filament Dimmable Bulb Warm White 2700K Amber Glass 800 Lumen LED Bulb CRI&gt;90, 90% Energy Saving- 220V</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -996,12 +1010,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>B09M42QJCS</t>
+          <t>B0CNQ1Q3BJ</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>LDMG125E2785PK_DCVV</t>
+          <t>LDMG125E278-DC_DCVV</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1024,7 +1038,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>DC VOLTAGE Pack 5 | Vintage LED Screw E27 Bulb,Edison G125 8W LED Filament Dimmable Bulb Warm White 2700K Amber Glass 800 Lumen LED Bulb CRI&gt;90, 90% Energy Saving- 220V</t>
+          <t>Vintage LED E27 Bulb, Edison G125 8W Dimmable Screw Bulb, LED Filament Warm White 2700K Amber Glass Light 806 Lumen Large Globe , Retro Style Old Fashioned Bulb, 220V CRI&gt;90, ,90% Energy Saving</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1051,12 +1065,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>B0CNQ1Q3BJ</t>
+          <t>B09M42FP91</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>LDMG125E278-DC_DCVV</t>
+          <t>LDMG125E2783PK_DCVV</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1079,7 +1093,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Vintage LED E27 Bulb, Edison G125 8W Dimmable Screw Bulb, LED Filament Warm White 2700K Amber Glass Light 806 Lumen Large Globe , Retro Style Old Fashioned Bulb, 220V CRI&gt;90, ,90% Energy Saving</t>
+          <t>Pack 3 | LED Vintage Globe E27 Light Bulb , G125 8W (Equivalent 60W) Dimmable 2700K Warm White 806 Lumens ES Screw Base Amber Glass | Old Fashioned Large giant Energy Saving Bulb for Decoration</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1106,12 +1120,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>B09M42FP91</t>
+          <t>B0B8SRVWSP</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>LDMG125E2783PK_DCVV</t>
+          <t>LDMG125E2783PK_SM</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1134,7 +1148,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Pack 3 | LED Vintage Globe E27 Light Bulb , G125 8W (Equivalent 60W) Dimmable 2700K Warm White 806 Lumens ES Screw Base Amber Glass | Old Fashioned Large giant Energy Saving Bulb for Decoration</t>
+          <t>LEDSone 3 Pack Vintage LED Dimmable Amber Bulb E27 Edison Screw 8W Equivalent G125 Globe LED Filament Bulbs 450LM 2700K Warm White Old Fashioned Bulbs</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1151,22 +1165,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>B0B8P9BKXB</t>
+          <t>B0BLZFGY38</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>LDMG125E278</t>
+          <t>LDMG95E274</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>B0B8SRVWSP</t>
+          <t>B093SS3HWN</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>LDMG125E2783PK_SM</t>
+          <t>LDMG95E274 H_DCVV</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1185,11 +1199,11 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>LEDSone 3 Pack Vintage LED Dimmable Amber Bulb E27 Edison Screw 8W Equivalent G125 Globe LED Filament Bulbs 450LM 2700K Warm White Old Fashioned Bulbs</t>
+          <t>DC VOLTAGE LED Vintage E27 Light Bulb, G95 4W (40W Equivalent) Dimmable Warm White 2700K 450 Lumens ES Screw LED Filament, Old Fashioned Retro Energy Saving Home Decorative Lighting</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1216,12 +1230,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>B093SS3HWN</t>
+          <t>B0D7MDP9XP</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>LDMG95E274 H_DCVV</t>
+          <t>LDMG95E274APK_DCVV</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1244,7 +1258,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>DC VOLTAGE LED Vintage E27 Light Bulb, G95 4W (40W Equivalent) Dimmable Warm White 2700K 450 Lumens ES Screw LED Filament, Old Fashioned Retro Energy Saving Home Decorative Lighting</t>
+          <t>DC VOLTAGE 10-Pack, LED Bayonet Light Bulb, BC G95 4W(40W Equivalent) Dimmable Warm White 2700K 450 Lumens LED Filament Amber Glass Retro Style Old Fashioned Decorative Energy Saving Bulb</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1261,22 +1275,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>B0BLZFGY38</t>
+          <t>B09477YHK7</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>LDMG95E274</t>
+          <t>LDMG95E278</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>B0D7MDP9XP</t>
+          <t>B0D4YG1QFJ</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>LDMG95E274APK_DCVV</t>
+          <t>LDMG95E2783PK_DCVV</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1295,11 +1309,11 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>DC VOLTAGE 10-Pack, LED Bayonet Light Bulb, BC G95 4W(40W Equivalent) Dimmable Warm White 2700K 450 Lumens LED Filament Amber Glass Retro Style Old Fashioned Decorative Energy Saving Bulb</t>
+          <t>DC VOLTAGE Pack 3 | Vintage LED E27 Bulb, Edison G95 8W Screw Light Bulb, Dimmable LED Filament Warm White 2700K Amber Glass, 800 Lumen Retro Style Old Fashioned Bulb, 90% Energy Saving 220V</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1326,12 +1340,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>B0D4YG1QFJ</t>
+          <t>B0DH4M42LR</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>LDMG95E2783PK_DCVV</t>
+          <t>LDMG95E278_VDS</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1354,7 +1368,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>DC VOLTAGE Pack 3 | Vintage LED E27 Bulb, Edison G95 8W Screw Light Bulb, Dimmable LED Filament Warm White 2700K Amber Glass, 800 Lumen Retro Style Old Fashioned Bulb, 90% Energy Saving 220V</t>
+          <t>LEDSone E27 LED Vintage Light Bulb Screw 8W Edison LED Filament Bulb G95 Globe Edison Style Dimmable LED Bulbs Retro Amber Glass Decorative Light Bulbs Warm White 2700K</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1381,12 +1395,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>B0DH4M42LR</t>
+          <t>B0CNPZDQHZ</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>LDMG95E278_VDS</t>
+          <t>LDMG95E278-DC_DCVV</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1409,7 +1423,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>LEDSone E27 LED Vintage Light Bulb Screw 8W Edison LED Filament Bulb G95 Globe Edison Style Dimmable LED Bulbs Retro Amber Glass Decorative Light Bulbs Warm White 2700K</t>
+          <t>DC VOLTAGE G95 Globe E27 Screw Bulb,Led Edison Light Bulb, Dimmable Retro Bulb, 220V 8W 450 Lumen Warm White 2700K Led Filament Light Bulb,90% Energy Saving</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1436,12 +1450,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>B0CNPZDQHZ</t>
+          <t>B0D4Y9DKJD</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>LDMG95E278-DC_DCVV</t>
+          <t>LDMG95E2786PK_DCVV</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1464,7 +1478,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>DC VOLTAGE G95 Globe E27 Screw Bulb,Led Edison Light Bulb, Dimmable Retro Bulb, 220V 8W 450 Lumen Warm White 2700K Led Filament Light Bulb,90% Energy Saving</t>
+          <t>DC VOLTAGE Vintage E27 LED Bulb, Edison G95 8W Screw Globe Dimmable LED Filament Bulb, 2700K Warm White Amber Glass, Retro Old Fashioned Light Bulb, 90% Energy Saving 220V - Pack of 6</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1481,22 +1495,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>B09477YHK7</t>
+          <t>B0BLP1JSRK</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>LDMG95E278</t>
+          <t>LDMST64E278</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>B0D4Y9DKJD</t>
+          <t>B0BSGSLZMD</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>LDMG95E2786PK_DCVV</t>
+          <t>LDMST64E2786PK_DCVV</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1515,11 +1529,11 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>DC VOLTAGE Vintage E27 LED Bulb, Edison G95 8W Screw Globe Dimmable LED Filament Bulb, 2700K Warm White Amber Glass, Retro Old Fashioned Light Bulb, 90% Energy Saving 220V - Pack of 6</t>
+          <t>DC VOLTAGE Pack 6| LED Edison E27 Light Bulb, 8W (60W Equivalent) ST64 Dimmable 2700K Warm White Vintage Style Amber Glass LED Filament Energy Saving Bulb for Squirrel Cage Lamp &amp; Home Decoration</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1546,12 +1560,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>B0BSGSLZMD</t>
+          <t>B0DDCGGFD5</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>LDMST64E2786PK_DCVV</t>
+          <t>LDMST64E2783PK_VDS</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1574,7 +1588,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>DC VOLTAGE Pack 6| LED Edison E27 Light Bulb, 8W (60W Equivalent) ST64 Dimmable 2700K Warm White Vintage Style Amber Glass LED Filament Energy Saving Bulb for Squirrel Cage Lamp &amp; Home Decoration</t>
+          <t>LEDSone 3 Pcs Vintage LED Light Bulb E27 Edison Screw Bulb 8W Retro Amber Glass Lamp 2200K Warm White dimmable Antique Style Energy Saving LED ST64 Filament Lamp 220V</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1601,12 +1615,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>B0DDCGGFD5</t>
+          <t>B08FYR2TFS</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>LDMST64E2783PK_VDS</t>
+          <t>LDMST64E278 A_DCVV</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1629,7 +1643,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>LEDSone 3 Pcs Vintage LED Light Bulb E27 Edison Screw Bulb 8W Retro Amber Glass Lamp 2200K Warm White dimmable Antique Style Energy Saving LED ST64 Filament Lamp 220V</t>
+          <t>DC VOLTAGE LED E27 Light Bulb, ST64 8W (60W Equivalent) Dimmable 2700K Warm White Amber Glass 806 Lumens Screw Base Vintage LED Filament Energy Saving Bulb for Squirrel Cage Lamp &amp; Home Decoration</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1646,22 +1660,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>B0BLP1JSRK</t>
+          <t>B0BL82M8SB</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>LDMST64E278</t>
+          <t>LDMT185E274</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>B08FYR2TFS</t>
+          <t>B0BL82LFD7</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>LDMST64E278 A_DCVV</t>
+          <t>LDMT185E274APK</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1671,7 +1685,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>backend keyword field empty; no bullet points; no description</t>
+          <t>backend keyword field empty</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1680,11 +1694,11 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>DC VOLTAGE LED E27 Light Bulb, ST64 8W (60W Equivalent) Dimmable 2700K Warm White Amber Glass 806 Lumens Screw Base Vintage LED Filament Energy Saving Bulb for Squirrel Cage Lamp &amp; Home Decoration</t>
+          <t>LEDSone Vintage LED Edison Bulb, Dimmable 4W E27 2700K T185 Tubular LED Bulbs, Led Filament Bulbs, Antique Style Retro Amber Glass Screw Lamp 220V Pack of 10</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1711,12 +1725,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>B0BL82LFD7</t>
+          <t>B093ST24PN</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>LDMT185E274APK</t>
+          <t>LDMT185E274 H_DCVV</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1726,7 +1740,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>backend keyword field empty</t>
+          <t>backend keyword field empty; no bullet points; no description</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1739,7 +1753,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>LEDSone Vintage LED Edison Bulb, Dimmable 4W E27 2700K T185 Tubular LED Bulbs, Led Filament Bulbs, Antique Style Retro Amber Glass Screw Lamp 220V Pack of 10</t>
+          <t>DC VOLTAGE LED E27 Edison Light Bulb, T185 4W (40W Equivalent) Dimmable Warm White 2700K LED Filament Amber Glass 450 Lumens Tubular Screw Base Vintage Energy Saving Home Decorative Light Bulb</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1756,22 +1770,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>B0BL82M8SB</t>
+          <t>B0BL7LZR24</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>LDMT185E274</t>
+          <t>LDMT45E274</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>B093ST24PN</t>
+          <t>B0DJCWV93V</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>LDMT185E274 H_DCVV</t>
+          <t>LDMT45E274_DCVV</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1790,11 +1804,11 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>DC VOLTAGE LED E27 Edison Light Bulb, T185 4W (40W Equivalent) Dimmable Warm White 2700K LED Filament Amber Glass 450 Lumens Tubular Screw Base Vintage Energy Saving Home Decorative Light Bulb</t>
+          <t>DC VOLTAGE 1 Pack E27 LED 4W Vintage Edison Screw Bulb Equivalent to 40W Amber Glass Antique Light Bulb Warm White 2200K 450LM dimmable T45 Retro Filament Bulb</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1811,22 +1825,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>B0BL7LZR24</t>
+          <t>B0DCDSZ719</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>LDMT45E274</t>
+          <t>LDSG95DIE274</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>B0DJCWV93V</t>
+          <t>B09JVSRK4Y</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>LDMT45E274_DCVV</t>
+          <t>LDSG95DIE274APK_DCVV</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1845,11 +1859,11 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>DC VOLTAGE 1 Pack E27 LED 4W Vintage Edison Screw Bulb Equivalent to 40W Amber Glass Antique Light Bulb Warm White 2200K 450LM dimmable T45 Retro Filament Bulb</t>
+          <t>DC VOLTAGE Pack 10 | LED E27 Edison Decorative Bulbs, G95 Diamond Shape 4W (40W Equivalent), Non-Dimmable 2700K Warm White Amber Glass Vintage Spiral LED Filament 450 Lumens Energy Saving Light Bulbs</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1858,63 +1872,8 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>ledsone_uk</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>B0DCDSZ719</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>LDSG95DIE274</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>B09JVSRK4Y</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>LDSG95DIE274APK_DCVV</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>zero_sales_6mo</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>backend keyword field empty; no bullet points; no description</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Rewrite listing content (bullets + backend keywords)</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>10</v>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>DC VOLTAGE Pack 10 | LED E27 Edison Decorative Bulbs, G95 Diamond Shape 4W (40W Equivalent), Non-Dimmable 2700K Warm White Amber Glass Vintage Spiral LED Filament 450 Lumens Energy Saving Light Bulbs</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:K22"/>
+  <autoFilter ref="A1:K21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1925,7 +1884,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M192"/>
+  <dimension ref="A1:M151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3187,7 +3146,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>B0B8P75R4Y</t>
+          <t>B0BP2PVM3D</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -3204,7 +3163,7 @@
         <v>306</v>
       </c>
       <c r="H21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" t="b">
         <v>0</v>
@@ -3216,7 +3175,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>backend</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -3248,7 +3207,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>B0B8P75R4Y</t>
+          <t>B0BP2PVM3D</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -3265,7 +3224,7 @@
         <v>192</v>
       </c>
       <c r="H22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22" t="b">
         <v>0</v>
@@ -3277,7 +3236,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>backend</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -3309,7 +3268,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>B0B8P75R4Y</t>
+          <t>B0BP2PVM3D</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -3326,7 +3285,7 @@
         <v>128</v>
       </c>
       <c r="H23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23" t="b">
         <v>0</v>
@@ -3338,7 +3297,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>backend</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -3370,7 +3329,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>B0B8P75R4Y</t>
+          <t>B0BP2PVM3D</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -3431,7 +3390,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>B0B8P75R4Y</t>
+          <t>B0BP2PVM3D</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -3448,7 +3407,7 @@
         <v>55</v>
       </c>
       <c r="H25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25" t="b">
         <v>0</v>
@@ -3460,7 +3419,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>backend</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -3492,7 +3451,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>B0B8P75R4Y</t>
+          <t>B0BP2PVM3D</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -3509,7 +3468,7 @@
         <v>40</v>
       </c>
       <c r="H26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26" t="b">
         <v>0</v>
@@ -3521,7 +3480,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>backend</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -3553,7 +3512,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>B0B8P75R4Y</t>
+          <t>B0BP2PVM3D</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3570,7 +3529,7 @@
         <v>23</v>
       </c>
       <c r="H27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27" t="b">
         <v>0</v>
@@ -3582,7 +3541,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>backend</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -3614,7 +3573,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>B0B8P75R4Y</t>
+          <t>B0BP2PVM3D</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3631,24 +3590,24 @@
         <v>20</v>
       </c>
       <c r="H28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>present</t>
+          <t>gap</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>pending_add</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3675,7 +3634,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>B0B8P75R4Y</t>
+          <t>B0BP2PVM3D</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3692,10 +3651,10 @@
         <v>14</v>
       </c>
       <c r="H29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -3704,7 +3663,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>bullet</t>
+          <t>backend</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3736,7 +3695,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>B0B8P75R4Y</t>
+          <t>B0BP2PVM3D</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3797,7 +3756,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>B0B8P75R4Y</t>
+          <t>B0BP2PVM3D</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3858,7 +3817,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>B0B8P75R4Y</t>
+          <t>B0BP2PVM3D</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3875,24 +3834,24 @@
         <v>9</v>
       </c>
       <c r="H32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I32" t="b">
         <v>1</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>gap</t>
+          <t>present</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>bullet</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>pending_add</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3919,7 +3878,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>B0B8P75R4Y</t>
+          <t>B0BP2PVM3D</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3936,7 +3895,7 @@
         <v>8</v>
       </c>
       <c r="H33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I33" t="b">
         <v>0</v>
@@ -3948,7 +3907,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>backend</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3980,7 +3939,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>B0B8P75R4Y</t>
+          <t>B0BP2PVM3D</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -4041,7 +4000,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>B0B8P75R4Y</t>
+          <t>B0BP2PVM3D</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -4102,7 +4061,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>B0B8P75R4Y</t>
+          <t>B0BP2PVM3D</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -4163,7 +4122,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>B0B8P75R4Y</t>
+          <t>B0BP2PVM3D</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -4224,7 +4183,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>B0B8P75R4Y</t>
+          <t>B0BP2PVM3D</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -4241,7 +4200,7 @@
         <v>5</v>
       </c>
       <c r="H38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I38" t="b">
         <v>0</v>
@@ -4253,7 +4212,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>backend</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -4285,7 +4244,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>B0B8P75R4Y</t>
+          <t>B0BP2PVM3D</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -4346,7 +4305,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>B0B8P75R4Y</t>
+          <t>B0BP2PVM3D</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -4363,7 +4322,7 @@
         <v>4</v>
       </c>
       <c r="H40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I40" t="b">
         <v>0</v>
@@ -4375,7 +4334,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>backend</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -4407,7 +4366,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>B0B8P75R4Y</t>
+          <t>B0BP2PVM3D</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -4424,24 +4383,24 @@
         <v>4</v>
       </c>
       <c r="H41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I41" t="b">
         <v>1</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>gap</t>
+          <t>present</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>bullet</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>pending_add</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -4468,7 +4427,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>B0B8P75R4Y</t>
+          <t>B0BP2PVM3D</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -4529,7 +4488,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>B0B8P75R4Y</t>
+          <t>B0BP2PVM3D</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -4590,7 +4549,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>B0B8P75R4Y</t>
+          <t>B0BP2PVM3D</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -4651,7 +4610,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>B0B8P75R4Y</t>
+          <t>B0BP2PVM3D</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -4668,24 +4627,24 @@
         <v>1</v>
       </c>
       <c r="H45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I45" t="b">
         <v>1</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>gap</t>
+          <t>present</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>bullet</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>pending_add</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -4712,7 +4671,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>B0B8P75R4Y</t>
+          <t>B0BP2PVM3D</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4773,7 +4732,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>B0BP2PVM3D</t>
+          <t>B0DQ8TM75J</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -4790,7 +4749,7 @@
         <v>306</v>
       </c>
       <c r="H47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I47" t="b">
         <v>0</v>
@@ -4802,7 +4761,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>backend</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -4834,7 +4793,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>B0BP2PVM3D</t>
+          <t>B0DQ8TM75J</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -4851,7 +4810,7 @@
         <v>192</v>
       </c>
       <c r="H48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I48" t="b">
         <v>0</v>
@@ -4863,7 +4822,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>backend</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -4895,7 +4854,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>B0BP2PVM3D</t>
+          <t>B0DQ8TM75J</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -4912,7 +4871,7 @@
         <v>128</v>
       </c>
       <c r="H49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I49" t="b">
         <v>0</v>
@@ -4924,7 +4883,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>backend</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -4956,7 +4915,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>B0BP2PVM3D</t>
+          <t>B0DQ8TM75J</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -5017,7 +4976,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>B0BP2PVM3D</t>
+          <t>B0DQ8TM75J</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -5034,7 +4993,7 @@
         <v>55</v>
       </c>
       <c r="H51" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I51" t="b">
         <v>0</v>
@@ -5046,7 +5005,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>backend</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -5078,7 +5037,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>B0BP2PVM3D</t>
+          <t>B0DQ8TM75J</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -5095,7 +5054,7 @@
         <v>40</v>
       </c>
       <c r="H52" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I52" t="b">
         <v>0</v>
@@ -5107,7 +5066,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>backend</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -5139,7 +5098,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>B0BP2PVM3D</t>
+          <t>B0DQ8TM75J</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -5156,7 +5115,7 @@
         <v>23</v>
       </c>
       <c r="H53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I53" t="b">
         <v>0</v>
@@ -5168,7 +5127,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>backend</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -5200,7 +5159,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>B0BP2PVM3D</t>
+          <t>B0DQ8TM75J</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -5261,7 +5220,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>B0BP2PVM3D</t>
+          <t>B0DQ8TM75J</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -5322,7 +5281,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>B0BP2PVM3D</t>
+          <t>B0DQ8TM75J</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -5383,7 +5342,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>B0BP2PVM3D</t>
+          <t>B0DQ8TM75J</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -5444,7 +5403,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>B0BP2PVM3D</t>
+          <t>B0DQ8TM75J</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -5464,21 +5423,21 @@
         <v>1</v>
       </c>
       <c r="I58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>present</t>
+          <t>gap</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>backend</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>pending_add</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -5505,7 +5464,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>B0BP2PVM3D</t>
+          <t>B0DQ8TM75J</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -5522,7 +5481,7 @@
         <v>8</v>
       </c>
       <c r="H59" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I59" t="b">
         <v>0</v>
@@ -5534,7 +5493,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>backend</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -5566,7 +5525,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>B0BP2PVM3D</t>
+          <t>B0DQ8TM75J</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -5627,7 +5586,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>B0BP2PVM3D</t>
+          <t>B0DQ8TM75J</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -5688,7 +5647,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>B0BP2PVM3D</t>
+          <t>B0DQ8TM75J</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -5749,7 +5708,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>B0BP2PVM3D</t>
+          <t>B0DQ8TM75J</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -5810,7 +5769,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>B0BP2PVM3D</t>
+          <t>B0DQ8TM75J</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -5827,7 +5786,7 @@
         <v>5</v>
       </c>
       <c r="H64" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I64" t="b">
         <v>0</v>
@@ -5839,7 +5798,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>backend</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -5871,7 +5830,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>B0BP2PVM3D</t>
+          <t>B0DQ8TM75J</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -5888,7 +5847,7 @@
         <v>5</v>
       </c>
       <c r="H65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I65" t="b">
         <v>0</v>
@@ -5900,7 +5859,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>backend</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -5932,7 +5891,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>B0BP2PVM3D</t>
+          <t>B0DQ8TM75J</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -5949,7 +5908,7 @@
         <v>4</v>
       </c>
       <c r="H66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I66" t="b">
         <v>0</v>
@@ -5961,7 +5920,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>backend</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -5993,7 +5952,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>B0BP2PVM3D</t>
+          <t>B0DQ8TM75J</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -6013,21 +5972,21 @@
         <v>1</v>
       </c>
       <c r="I67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>present</t>
+          <t>gap</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>backend</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>pending_add</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -6054,7 +6013,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>B0BP2PVM3D</t>
+          <t>B0DQ8TM75J</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -6115,7 +6074,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>B0BP2PVM3D</t>
+          <t>B0DQ8TM75J</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -6176,7 +6135,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>B0BP2PVM3D</t>
+          <t>B0DQ8TM75J</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -6237,7 +6196,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>B0BP2PVM3D</t>
+          <t>B0DQ8TM75J</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -6257,21 +6216,21 @@
         <v>1</v>
       </c>
       <c r="I71" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>present</t>
+          <t>gap</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>backend</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>pending_add</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -6298,7 +6257,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>B0BP2PVM3D</t>
+          <t>B0DQ8TM75J</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -6349,17 +6308,17 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>B0B8P9BKXB</t>
+          <t>B09477YHK7</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>LDMG125E278</t>
+          <t>LDMG95E278</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>B0DQ8TM75J</t>
+          <t>B0845ZBTJV</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -6369,31 +6328,31 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>large screw light bulbs</t>
+          <t>e27 screw bulb</t>
         </is>
       </c>
       <c r="G73" t="n">
-        <v>306</v>
+        <v>11481</v>
       </c>
       <c r="H73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>gap</t>
+          <t>present</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>pending_add</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -6410,17 +6369,17 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>B0B8P9BKXB</t>
+          <t>B09477YHK7</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>LDMG125E278</t>
+          <t>LDMG95E278</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>B0DQ8TM75J</t>
+          <t>B0845ZBTJV</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -6430,31 +6389,31 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>large light bulb</t>
+          <t>e27 dimmable bulb</t>
         </is>
       </c>
       <c r="G74" t="n">
-        <v>192</v>
+        <v>722</v>
       </c>
       <c r="H74" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I74" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>gap</t>
+          <t>present</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>pending_add</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -6471,17 +6430,17 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>B0B8P9BKXB</t>
+          <t>B09477YHK7</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>LDMG125E278</t>
+          <t>LDMG95E278</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>B0DQ8TM75J</t>
+          <t>B0845ZBTJV</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -6491,31 +6450,31 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>e27 large globe bulb</t>
+          <t>e27 edison screw bulb</t>
         </is>
       </c>
       <c r="G75" t="n">
-        <v>128</v>
+        <v>380</v>
       </c>
       <c r="H75" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I75" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>gap</t>
+          <t>present</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>pending_add</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -6532,17 +6491,17 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>B0B8P9BKXB</t>
+          <t>B09477YHK7</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>LDMG125E278</t>
+          <t>LDMG95E278</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>B0DQ8TM75J</t>
+          <t>B0845ZBTJV</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -6552,31 +6511,31 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>e27 globe bulb</t>
+          <t>e27 bulb 60w</t>
         </is>
       </c>
       <c r="G76" t="n">
-        <v>91</v>
+        <v>70</v>
       </c>
       <c r="H76" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I76" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>present</t>
+          <t>gap</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>pending_add</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -6593,17 +6552,17 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>B0B8P9BKXB</t>
+          <t>B09477YHK7</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>LDMG125E278</t>
+          <t>LDMG95E278</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>B0DQ8TM75J</t>
+          <t>B0845ZBTJV</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -6613,31 +6572,31 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>large globe e27 edison screw led bulb</t>
+          <t>g95 bulbs</t>
         </is>
       </c>
       <c r="G77" t="n">
         <v>55</v>
       </c>
       <c r="H77" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I77" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>gap</t>
+          <t>present</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>pending_add</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -6654,17 +6613,17 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>B0B8P9BKXB</t>
+          <t>B09477YHK7</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>LDMG125E278</t>
+          <t>LDMG95E278</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>B0DQ8TM75J</t>
+          <t>B0845ZBTJV</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -6674,11 +6633,11 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>e27 large bulb</t>
+          <t>4000k e27 bulb</t>
         </is>
       </c>
       <c r="G78" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H78" t="b">
         <v>0</v>
@@ -6715,17 +6674,17 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>B0B8P9BKXB</t>
+          <t>B09477YHK7</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>LDMG125E278</t>
+          <t>LDMG95E278</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>B0DQ8TM75J</t>
+          <t>B0845ZBTJV</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -6735,17 +6694,17 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>large led bulb</t>
+          <t>e27 dimmable bulb warm white vintage</t>
         </is>
       </c>
       <c r="G79" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="H79" t="b">
         <v>0</v>
       </c>
       <c r="I79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
@@ -6754,7 +6713,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>bullet</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -6776,17 +6735,17 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>B0B8P9BKXB</t>
+          <t>B09477YHK7</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>LDMG125E278</t>
+          <t>LDMG95E278</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>B0DQ8TM75J</t>
+          <t>B0845ZBTJV</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -6796,11 +6755,11 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>decorative bulbs bayonet</t>
+          <t>sklum e27 g95</t>
         </is>
       </c>
       <c r="G80" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="H80" t="b">
         <v>0</v>
@@ -6837,17 +6796,17 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>B0B8P9BKXB</t>
+          <t>B09477YHK7</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>LDMG125E278</t>
+          <t>LDMG95E278</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>B0DQ8TM75J</t>
+          <t>B0845ZBTJV</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -6857,14 +6816,14 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>es 8w led bulb</t>
+          <t>pack of 6 e27 globe bulbs</t>
         </is>
       </c>
       <c r="G81" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="H81" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I81" t="b">
         <v>0</v>
@@ -6876,7 +6835,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>backend</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -6898,17 +6857,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>B0B8P9BKXB</t>
+          <t>B09477YHK7</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>LDMG125E278</t>
+          <t>LDMG95E278</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>B0DQ8TM75J</t>
+          <t>B0845ZBTJV</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -6918,11 +6877,11 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>g125 e27</t>
+          <t>e27 globe dimmable led</t>
         </is>
       </c>
       <c r="G82" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="H82" t="b">
         <v>1</v>
@@ -6959,17 +6918,17 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>B0B8P9BKXB</t>
+          <t>B09477YHK7</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>LDMG125E278</t>
+          <t>LDMG95E278</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>B0DQ8TM75J</t>
+          <t>B0845ZBTJV</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -6979,31 +6938,31 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>e27 g125 amber led filament globe bulb dimmable</t>
+          <t>philips 8w / 806 lumens / 2700k / e27</t>
         </is>
       </c>
       <c r="G83" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="H83" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I83" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>present</t>
+          <t>gap</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>pending_add</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -7020,17 +6979,17 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>B0B8P9BKXB</t>
+          <t>B09477YHK7</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>LDMG125E278</t>
+          <t>LDMG95E278</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>B0DQ8TM75J</t>
+          <t>B0845ZBTJV</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -7040,14 +6999,14 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>led e27 edison filament bulb light retro vintage screw globe lamp 8w</t>
+          <t>95mm amber glass e27</t>
         </is>
       </c>
       <c r="G84" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H84" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I84" t="b">
         <v>0</v>
@@ -7059,7 +7018,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>backend</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -7081,17 +7040,17 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>B0B8P9BKXB</t>
+          <t>B0BLP1JSRK</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>LDMG125E278</t>
+          <t>LDMST64E278</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>B0DQ8TM75J</t>
+          <t>B0BLNZS78D</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -7101,14 +7060,14 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>e27 large bulb dimmable</t>
+          <t>e27 vintage bulb 60w</t>
         </is>
       </c>
       <c r="G85" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H85" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I85" t="b">
         <v>0</v>
@@ -7120,7 +7079,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>backend</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -7142,17 +7101,17 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>B0B8P9BKXB</t>
+          <t>B0BLP1JSRK</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>LDMG125E278</t>
+          <t>LDMST64E278</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>B0DQ8TM75J</t>
+          <t>B0BLNZS78D</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -7162,11 +7121,11 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>led bulb light large 120 mm x 160mm</t>
+          <t>e27 es dimmable bulb 8w squirrel cage</t>
         </is>
       </c>
       <c r="G86" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H86" t="b">
         <v>0</v>
@@ -7203,17 +7162,17 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>B0B8P9BKXB</t>
+          <t>B0BLP1JSRK</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>LDMG125E278</t>
+          <t>LDMST64E278</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>B0DQ8TM75J</t>
+          <t>B0BLNZS78D</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -7223,31 +7182,31 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>led light bulb, e27</t>
+          <t>bravo lighting bulbs 8w dimmable</t>
         </is>
       </c>
       <c r="G87" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H87" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I87" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>present</t>
+          <t>gap</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>pending_add</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -7264,17 +7223,17 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>B0B8P9BKXB</t>
+          <t>B0BLP1JSRK</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>LDMG125E278</t>
+          <t>LDMST64E278</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>B0DQ8TM75J</t>
+          <t>B0BLNZS78D</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -7284,11 +7243,11 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>large e27 vintage light bulbs 14cm retro</t>
+          <t>ledsone pack 3 | vintage led edison e27 light bulb, 8w (equivalent 60w) st64 dimmable 2700k warm white amber glass screw 806 lumens| energy saving bulb for squirrel cage lamp 220v [energy class a]</t>
         </is>
       </c>
       <c r="G88" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H88" t="b">
         <v>0</v>
@@ -7325,17 +7284,17 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>B0B8P9BKXB</t>
+          <t>B0BLP1JSRK</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>LDMG125E278</t>
+          <t>LDMST64E278</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>B0DQ8TM75J</t>
+          <t>B0BLNZS78D</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -7345,14 +7304,14 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>e27 xl bulb</t>
+          <t>e27 8w vintage light bulbs</t>
         </is>
       </c>
       <c r="G89" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H89" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I89" t="b">
         <v>0</v>
@@ -7364,7 +7323,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>backend</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -7386,17 +7345,17 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>B0B8P9BKXB</t>
+          <t>B0BLP1JSRK</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>LDMG125E278</t>
+          <t>LDMST64E278</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>B0DQ8TM75J</t>
+          <t>B0BLNZS78D</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -7406,11 +7365,11 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>dimmable retro large 8w</t>
+          <t>squirrel led cage dimmable</t>
         </is>
       </c>
       <c r="G90" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H90" t="b">
         <v>0</v>
@@ -7447,17 +7406,17 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>B0B8P9BKXB</t>
+          <t>B0BLP1JSRK</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>LDMG125E278</t>
+          <t>LDMST64E278</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>B0DQ8TM75J</t>
+          <t>B0BLNZS78D</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -7467,14 +7426,14 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>vintage led e27 g125 8w dimmable, amber glass, 2700k, 806 lumen</t>
+          <t>bul-e27-rus-w1 bulb</t>
         </is>
       </c>
       <c r="G91" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H91" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I91" t="b">
         <v>0</v>
@@ -7486,7 +7445,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>backend</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -7508,17 +7467,17 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>B0B8P9BKXB</t>
+          <t>B0BLP1JSRK</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>LDMG125E278</t>
+          <t>LDMST64E278</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>B0DQ8TM75J</t>
+          <t>B0BLNZS78D</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -7528,11 +7487,11 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>large bulb indoor e27 screw</t>
+          <t>e27 8w 2200k 720lumen</t>
         </is>
       </c>
       <c r="G92" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H92" t="b">
         <v>0</v>
@@ -7569,17 +7528,17 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>B0B8P9BKXB</t>
+          <t>B0BLP1JSRK</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>LDMG125E278</t>
+          <t>LDMST64E278</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>B0DQ8TM75J</t>
+          <t>B0BLNZS78D</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -7589,14 +7548,14 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>e27 8w vintage light bulbs</t>
+          <t>e27 dimmable bulb pack of six</t>
         </is>
       </c>
       <c r="G93" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H93" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I93" t="b">
         <v>0</v>
@@ -7608,7 +7567,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>backend</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -7630,17 +7589,17 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>B0B8P9BKXB</t>
+          <t>B0BLP1JSRK</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>LDMG125E278</t>
+          <t>LDMST64E278</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>B0DQ8TM75J</t>
+          <t>B0BLNZS78D</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -7650,31 +7609,31 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>edison g125</t>
+          <t>light bulbs screv wintage 8w</t>
         </is>
       </c>
       <c r="G94" t="n">
         <v>2</v>
       </c>
       <c r="H94" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I94" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>present</t>
+          <t>gap</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>pending_add</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -7691,17 +7650,17 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>B0B8P9BKXB</t>
+          <t>B0BLP1JSRK</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>LDMG125E278</t>
+          <t>LDMST64E278</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>B0DQ8TM75J</t>
+          <t>B0BLNZS78D</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -7711,31 +7670,31 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>e27 g125 vintage</t>
+          <t>e27 2700k dimmable 8w amber 6 pack</t>
         </is>
       </c>
       <c r="G95" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H95" t="b">
         <v>1</v>
       </c>
       <c r="I95" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>present</t>
+          <t>gap</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>backend</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>pending_add</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -7752,17 +7711,17 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>B0B8P9BKXB</t>
+          <t>B0BLP1JSRK</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>LDMG125E278</t>
+          <t>LDMST64E278</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>B0DQ8TM75J</t>
+          <t>B0BLNZS78D</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -7772,11 +7731,11 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>g125 led filament bulb smoked e27 warm</t>
+          <t>bulb warm yellliw pack 6</t>
         </is>
       </c>
       <c r="G96" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H96" t="b">
         <v>0</v>
@@ -7813,17 +7772,17 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>B0B8P9BKXB</t>
+          <t>B0BLP1JSRK</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>LDMG125E278</t>
+          <t>LDMST64E278</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>B0DQ8TM75J</t>
+          <t>B0BLNZS78D</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -7833,14 +7792,14 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>led bulb dimmable filament amber e27 8w</t>
+          <t>squirrel cage vintage edison e27 screw bulb 8w clear</t>
         </is>
       </c>
       <c r="G97" t="n">
         <v>1</v>
       </c>
       <c r="H97" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I97" t="b">
         <v>0</v>
@@ -7852,7 +7811,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>backend</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -7874,17 +7833,17 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>B0B8P9BKXB</t>
+          <t>B0BLP1JSRK</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>LDMG125E278</t>
+          <t>LDMST64E278</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>B0DQ8TM75J</t>
+          <t>B0BLNZS78D</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -7894,14 +7853,14 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>diall g125 e27 5.5w 470lm 330° amber globe warm white led filament light bulb</t>
+          <t>6 led e27 st64 8w 60 w dimmable warm white 2700k</t>
         </is>
       </c>
       <c r="G98" t="n">
         <v>1</v>
       </c>
       <c r="H98" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I98" t="b">
         <v>0</v>
@@ -7913,7 +7872,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>backend</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -7935,17 +7894,17 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>B09477YHK7</t>
+          <t>B0BLP1JSRK</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>LDMG95E278</t>
+          <t>LDMST64E278</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>B0845ZBTJV</t>
+          <t>B0BLNZS78D</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -7955,31 +7914,31 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>e27 screw bulb</t>
+          <t>vintage 60w es bulb pack not dimmable</t>
         </is>
       </c>
       <c r="G99" t="n">
-        <v>11481</v>
+        <v>1</v>
       </c>
       <c r="H99" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I99" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>present</t>
+          <t>gap</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>pending_add</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -7996,17 +7955,17 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>B09477YHK7</t>
+          <t>B0BLP1JSRK</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>LDMG95E278</t>
+          <t>LDMST64E278</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>B0845ZBTJV</t>
+          <t>B0BLP1LN2C</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -8016,31 +7975,31 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>e27 dimmable bulb</t>
+          <t>e27 vintage bulb 60w</t>
         </is>
       </c>
       <c r="G100" t="n">
-        <v>722</v>
+        <v>11</v>
       </c>
       <c r="H100" t="b">
         <v>1</v>
       </c>
       <c r="I100" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>present</t>
+          <t>gap</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>backend</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>pending_add</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -8057,17 +8016,17 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>B09477YHK7</t>
+          <t>B0BLP1JSRK</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>LDMG95E278</t>
+          <t>LDMST64E278</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>B0845ZBTJV</t>
+          <t>B0BLP1LN2C</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -8077,31 +8036,31 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>e27 edison screw bulb</t>
+          <t>e27 es dimmable bulb 8w squirrel cage</t>
         </is>
       </c>
       <c r="G101" t="n">
-        <v>380</v>
+        <v>4</v>
       </c>
       <c r="H101" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I101" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>present</t>
+          <t>gap</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>pending_add</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -8118,17 +8077,17 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>B09477YHK7</t>
+          <t>B0BLP1JSRK</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>LDMG95E278</t>
+          <t>LDMST64E278</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>B0845ZBTJV</t>
+          <t>B0BLP1LN2C</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -8138,11 +8097,11 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>e27 bulb 60w</t>
+          <t>bravo lighting bulbs 8w dimmable</t>
         </is>
       </c>
       <c r="G102" t="n">
-        <v>70</v>
+        <v>4</v>
       </c>
       <c r="H102" t="b">
         <v>0</v>
@@ -8179,17 +8138,17 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>B09477YHK7</t>
+          <t>B0BLP1JSRK</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>LDMG95E278</t>
+          <t>LDMST64E278</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>B0845ZBTJV</t>
+          <t>B0BLP1LN2C</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -8199,31 +8158,31 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>g95 bulbs</t>
+          <t>ledsone pack 3 | vintage led edison e27 light bulb, 8w (equivalent 60w) st64 dimmable 2700k warm white amber glass screw 806 lumens| energy saving bulb for squirrel cage lamp 220v [energy class a]</t>
         </is>
       </c>
       <c r="G103" t="n">
-        <v>55</v>
+        <v>4</v>
       </c>
       <c r="H103" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I103" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>present</t>
+          <t>gap</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>pending_add</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -8240,17 +8199,17 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>B09477YHK7</t>
+          <t>B0BLP1JSRK</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>LDMG95E278</t>
+          <t>LDMST64E278</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>B0845ZBTJV</t>
+          <t>B0BLP1LN2C</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -8260,14 +8219,14 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>4000k e27 bulb</t>
+          <t>e27 8w vintage light bulbs</t>
         </is>
       </c>
       <c r="G104" t="n">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="H104" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I104" t="b">
         <v>0</v>
@@ -8279,7 +8238,7 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>backend</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -8301,17 +8260,17 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>B09477YHK7</t>
+          <t>B0BLP1JSRK</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>LDMG95E278</t>
+          <t>LDMST64E278</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>B0845ZBTJV</t>
+          <t>B0BLP1LN2C</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -8321,17 +8280,17 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>e27 dimmable bulb warm white vintage</t>
+          <t>squirrel led cage dimmable</t>
         </is>
       </c>
       <c r="G105" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H105" t="b">
         <v>0</v>
       </c>
       <c r="I105" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
@@ -8340,7 +8299,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>bullet</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -8362,17 +8321,17 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>B09477YHK7</t>
+          <t>B0BLP1JSRK</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>LDMG95E278</t>
+          <t>LDMST64E278</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>B0845ZBTJV</t>
+          <t>B0BLP1LN2C</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -8382,11 +8341,11 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>sklum e27 g95</t>
+          <t>bul-e27-rus-w1 bulb</t>
         </is>
       </c>
       <c r="G106" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H106" t="b">
         <v>0</v>
@@ -8423,17 +8382,17 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>B09477YHK7</t>
+          <t>B0BLP1JSRK</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>LDMG95E278</t>
+          <t>LDMST64E278</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>B0845ZBTJV</t>
+          <t>B0BLP1LN2C</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -8443,11 +8402,11 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>pack of 6 e27 globe bulbs</t>
+          <t>e27 8w 2200k 720lumen</t>
         </is>
       </c>
       <c r="G107" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H107" t="b">
         <v>0</v>
@@ -8484,17 +8443,17 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>B09477YHK7</t>
+          <t>B0BLP1JSRK</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>LDMG95E278</t>
+          <t>LDMST64E278</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>B0845ZBTJV</t>
+          <t>B0BLP1LN2C</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -8504,31 +8463,31 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>e27 globe dimmable led</t>
+          <t>e27 dimmable bulb pack of six</t>
         </is>
       </c>
       <c r="G108" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H108" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I108" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>present</t>
+          <t>gap</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>pending_add</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -8545,17 +8504,17 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>B09477YHK7</t>
+          <t>B0BLP1JSRK</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>LDMG95E278</t>
+          <t>LDMST64E278</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>B0845ZBTJV</t>
+          <t>B0BLP1LN2C</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -8565,11 +8524,11 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>philips 8w / 806 lumens / 2700k / e27</t>
+          <t>light bulbs screv wintage 8w</t>
         </is>
       </c>
       <c r="G109" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H109" t="b">
         <v>0</v>
@@ -8606,17 +8565,17 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>B09477YHK7</t>
+          <t>B0BLP1JSRK</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>LDMG95E278</t>
+          <t>LDMST64E278</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>B0845ZBTJV</t>
+          <t>B0BLP1LN2C</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -8626,14 +8585,14 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>95mm amber glass e27</t>
+          <t>e27 2700k dimmable 8w amber 6 pack</t>
         </is>
       </c>
       <c r="G110" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H110" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I110" t="b">
         <v>0</v>
@@ -8645,7 +8604,7 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>backend</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -8677,7 +8636,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>B0BLNZS78D</t>
+          <t>B0BLP1LN2C</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -8687,14 +8646,14 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>e27 vintage bulb 60w</t>
+          <t>bulb warm yellliw pack 6</t>
         </is>
       </c>
       <c r="G111" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="H111" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I111" t="b">
         <v>0</v>
@@ -8706,7 +8665,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>backend</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -8738,7 +8697,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>B0BLNZS78D</t>
+          <t>B0BLP1LN2C</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -8748,11 +8707,11 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>e27 es dimmable bulb 8w squirrel cage</t>
+          <t>squirrel cage vintage edison e27 screw bulb 8w clear</t>
         </is>
       </c>
       <c r="G112" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H112" t="b">
         <v>0</v>
@@ -8799,7 +8758,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>B0BLNZS78D</t>
+          <t>B0BLP1LN2C</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -8809,14 +8768,14 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>bravo lighting bulbs 8w dimmable</t>
+          <t>6 led e27 st64 8w 60 w dimmable warm white 2700k</t>
         </is>
       </c>
       <c r="G113" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H113" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I113" t="b">
         <v>0</v>
@@ -8828,7 +8787,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>backend</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -8860,7 +8819,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>B0BLNZS78D</t>
+          <t>B0BLP1LN2C</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -8870,11 +8829,11 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>ledsone pack 3 | vintage led edison e27 light bulb, 8w (equivalent 60w) st64 dimmable 2700k warm white amber glass screw 806 lumens| energy saving bulb for squirrel cage lamp 220v [energy class a]</t>
+          <t>vintage 60w es bulb pack not dimmable</t>
         </is>
       </c>
       <c r="G114" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H114" t="b">
         <v>0</v>
@@ -8911,17 +8870,17 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>B0BLP1JSRK</t>
+          <t>B09JM3PLLH</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>LDMST64E278</t>
+          <t>LDSG125LOE274</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>B0BLNZS78D</t>
+          <t>B0DBTNQT8Z</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -8931,14 +8890,14 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>e27 8w vintage light bulbs</t>
+          <t>large e27 vintage light bulbs</t>
         </is>
       </c>
       <c r="G115" t="n">
-        <v>4</v>
+        <v>150</v>
       </c>
       <c r="H115" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I115" t="b">
         <v>0</v>
@@ -8950,7 +8909,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>backend</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -8972,17 +8931,17 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>B0BLP1JSRK</t>
+          <t>B09JM3PLLH</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>LDMST64E278</t>
+          <t>LDSG125LOE274</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>B0BLNZS78D</t>
+          <t>B0DBTNQT8Z</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -8992,31 +8951,31 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>squirrel led cage dimmable</t>
+          <t>edison bulb</t>
         </is>
       </c>
       <c r="G116" t="n">
-        <v>3</v>
+        <v>133</v>
       </c>
       <c r="H116" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I116" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>gap</t>
+          <t>present</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>pending_add</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
@@ -9033,17 +8992,17 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>B0BLP1JSRK</t>
+          <t>B09JM3PLLH</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>LDMST64E278</t>
+          <t>LDSG125LOE274</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>B0BLNZS78D</t>
+          <t>B0DBTNQT8Z</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -9053,31 +9012,31 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>bul-e27-rus-w1 bulb</t>
+          <t>love light bulb</t>
         </is>
       </c>
       <c r="G117" t="n">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="H117" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I117" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>gap</t>
+          <t>present</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>pending_add</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
@@ -9094,17 +9053,17 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>B0BLP1JSRK</t>
+          <t>B09JM3PLLH</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>LDMST64E278</t>
+          <t>LDSG125LOE274</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>B0BLNZS78D</t>
+          <t>B0DBTNQT8Z</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -9114,14 +9073,14 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>e27 8w 2200k 720lumen</t>
+          <t>e27 screw bulb decorative</t>
         </is>
       </c>
       <c r="G118" t="n">
-        <v>2</v>
+        <v>55</v>
       </c>
       <c r="H118" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I118" t="b">
         <v>0</v>
@@ -9133,7 +9092,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>backend</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -9155,17 +9114,17 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>B0BLP1JSRK</t>
+          <t>B09JM3PLLH</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>LDMST64E278</t>
+          <t>LDSG125LOE274</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>B0BLNZS78D</t>
+          <t>B0DBTNQT8Z</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -9175,11 +9134,11 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>e27 dimmable bulb pack of six</t>
+          <t>e27 large globe bulb</t>
         </is>
       </c>
       <c r="G119" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="H119" t="b">
         <v>0</v>
@@ -9216,17 +9175,17 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>B0BLP1JSRK</t>
+          <t>B09JM3PLLH</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>LDMST64E278</t>
+          <t>LDSG125LOE274</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>B0BLNZS78D</t>
+          <t>B0DBTNQT8Z</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -9236,11 +9195,11 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>light bulbs screv wintage 8w</t>
+          <t>extra large edison bulb</t>
         </is>
       </c>
       <c r="G120" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="H120" t="b">
         <v>0</v>
@@ -9277,17 +9236,17 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>B0BLP1JSRK</t>
+          <t>B09JM3PLLH</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>LDMST64E278</t>
+          <t>LDSG125LOE274</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>B0BLNZS78D</t>
+          <t>B0DBTNQT8Z</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -9297,17 +9256,17 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>e27 2700k dimmable 8w amber 6 pack</t>
+          <t>big bulb</t>
         </is>
       </c>
       <c r="G121" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="H121" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I121" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J121" t="inlineStr">
         <is>
@@ -9316,7 +9275,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>backend</t>
+          <t>bullet</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -9338,17 +9297,17 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>B0BLP1JSRK</t>
+          <t>B09JM3PLLH</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>LDMST64E278</t>
+          <t>LDSG125LOE274</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>B0BLNZS78D</t>
+          <t>B0DBTNQT8Z</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -9358,11 +9317,11 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>bulb warm yellliw pack 6</t>
+          <t>e27 screw bulb spiral</t>
         </is>
       </c>
       <c r="G122" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="H122" t="b">
         <v>0</v>
@@ -9399,17 +9358,17 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>B0BLP1JSRK</t>
+          <t>B09JM3PLLH</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>LDMST64E278</t>
+          <t>LDSG125LOE274</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>B0BLNZS78D</t>
+          <t>B0DBTNQT8Z</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -9419,11 +9378,11 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>squirrel cage vintage edison e27 screw bulb 8w clear</t>
+          <t>warm white large screw light bulbs</t>
         </is>
       </c>
       <c r="G123" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="H123" t="b">
         <v>0</v>
@@ -9460,17 +9419,17 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>B0BLP1JSRK</t>
+          <t>B09JM3PLLH</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>LDMST64E278</t>
+          <t>LDSG125LOE274</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>B0BLNZS78D</t>
+          <t>B0DBTNQT8Z</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -9480,31 +9439,31 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>6 led e27 st64 8w 60 w dimmable warm white 2700k</t>
+          <t>love bulb</t>
         </is>
       </c>
       <c r="G124" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="H124" t="b">
         <v>1</v>
       </c>
       <c r="I124" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>gap</t>
+          <t>present</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>backend</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>pending_add</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -9521,17 +9480,17 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>B0BLP1JSRK</t>
+          <t>B09JM3PLLH</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>LDMST64E278</t>
+          <t>LDSG125LOE274</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>B0BLNZS78D</t>
+          <t>B0DBTNQT8Z</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -9541,31 +9500,31 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>vintage 60w es bulb pack not dimmable</t>
+          <t>g125 led bulb</t>
         </is>
       </c>
       <c r="G125" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H125" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I125" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>gap</t>
+          <t>present</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>pending_add</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -9582,17 +9541,17 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>B0BLP1JSRK</t>
+          <t>B09JM3PLLH</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>LDMST64E278</t>
+          <t>LDSG125LOE274</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>B0BLP1LN2C</t>
+          <t>B0DBTNQT8Z</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -9602,14 +9561,14 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>e27 vintage bulb 60w</t>
+          <t>screw e27 led light bulb, 4w globe large screw vintage edison led bulbs</t>
         </is>
       </c>
       <c r="G126" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="H126" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I126" t="b">
         <v>0</v>
@@ -9621,7 +9580,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>backend</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -9643,17 +9602,17 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>B0BLP1JSRK</t>
+          <t>B09JM3PLLH</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>LDMST64E278</t>
+          <t>LDSG125LOE274</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>B0BLP1LN2C</t>
+          <t>B0DBTNQT8Z</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -9663,11 +9622,11 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>e27 es dimmable bulb 8w squirrel cage</t>
+          <t>large edison screw bulb warm white</t>
         </is>
       </c>
       <c r="G127" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H127" t="b">
         <v>0</v>
@@ -9704,17 +9663,17 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>B0BLP1JSRK</t>
+          <t>B09JM3PLLH</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>LDMST64E278</t>
+          <t>LDSG125LOE274</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>B0BLP1LN2C</t>
+          <t>B0DBTNQT8Z</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -9724,14 +9683,14 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>bravo lighting bulbs 8w dimmable</t>
+          <t>light bulb with amber love</t>
         </is>
       </c>
       <c r="G128" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H128" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I128" t="b">
         <v>0</v>
@@ -9743,7 +9702,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>backend</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -9765,17 +9724,17 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>B0BLP1JSRK</t>
+          <t>B09JM3PLLH</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>LDMST64E278</t>
+          <t>LDSG125LOE274</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>B0BLP1LN2C</t>
+          <t>B0DBTNQT8Z</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -9785,31 +9744,31 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>ledsone pack 3 | vintage led edison e27 light bulb, 8w (equivalent 60w) st64 dimmable 2700k warm white amber glass screw 806 lumens| energy saving bulb for squirrel cage lamp 220v [energy class a]</t>
+          <t>es love light bulb</t>
         </is>
       </c>
       <c r="G129" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H129" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I129" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>gap</t>
+          <t>present</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>pending_add</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -9826,17 +9785,17 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>B0BLP1JSRK</t>
+          <t>B09JM3PLLH</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>LDMST64E278</t>
+          <t>LDSG125LOE274</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>B0BLP1LN2C</t>
+          <t>B0DBTNQT8Z</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -9846,14 +9805,14 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>e27 8w vintage light bulbs</t>
+          <t>e27 love light balb</t>
         </is>
       </c>
       <c r="G130" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H130" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I130" t="b">
         <v>0</v>
@@ -9865,7 +9824,7 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>backend</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -9887,17 +9846,17 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>B0BLP1JSRK</t>
+          <t>B09JM3PLLH</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>LDMST64E278</t>
+          <t>LDSG125LOE274</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>B0BLP1LN2C</t>
+          <t>B0DBTNQT8Z</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -9907,11 +9866,11 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>squirrel led cage dimmable</t>
+          <t>bulb writing</t>
         </is>
       </c>
       <c r="G131" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H131" t="b">
         <v>0</v>
@@ -9948,51 +9907,51 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>B0BLP1JSRK</t>
+          <t>B0DCDSZ719</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>LDMST64E278</t>
+          <t>LDSG95DIE274</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>B0BLP1LN2C</t>
+          <t>B0DCFP1CX8</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>zero_sales_6mo</t>
+          <t>sales_drop_3mo</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>bul-e27-rus-w1 bulb</t>
+          <t>vintage light bulb</t>
         </is>
       </c>
       <c r="G132" t="n">
-        <v>3</v>
+        <v>394</v>
       </c>
       <c r="H132" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I132" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>gap</t>
+          <t>present</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>pending_add</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -10009,34 +9968,34 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>B0BLP1JSRK</t>
+          <t>B0DCDSZ719</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>LDMST64E278</t>
+          <t>LDSG95DIE274</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>B0BLP1LN2C</t>
+          <t>B0DCFP1CX8</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>zero_sales_6mo</t>
+          <t>sales_drop_3mo</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>e27 8w 2200k 720lumen</t>
+          <t>decorative light bulbs</t>
         </is>
       </c>
       <c r="G133" t="n">
-        <v>2</v>
+        <v>213</v>
       </c>
       <c r="H133" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I133" t="b">
         <v>0</v>
@@ -10048,7 +10007,7 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>backend</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -10070,34 +10029,34 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>B0BLP1JSRK</t>
+          <t>B0DCDSZ719</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>LDMST64E278</t>
+          <t>LDSG95DIE274</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>B0BLP1LN2C</t>
+          <t>B0DCFP1CX8</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>zero_sales_6mo</t>
+          <t>sales_drop_3mo</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>e27 dimmable bulb pack of six</t>
+          <t>e27 vintage light bulbs</t>
         </is>
       </c>
       <c r="G134" t="n">
-        <v>2</v>
+        <v>177</v>
       </c>
       <c r="H134" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I134" t="b">
         <v>0</v>
@@ -10109,7 +10068,7 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>backend</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -10131,31 +10090,31 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>B0BLP1JSRK</t>
+          <t>B0DCDSZ719</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>LDMST64E278</t>
+          <t>LDSG95DIE274</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>B0BLP1LN2C</t>
+          <t>B0DCFP1CX8</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>zero_sales_6mo</t>
+          <t>sales_drop_3mo</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>light bulbs screv wintage 8w</t>
+          <t>e14 vintage bulb</t>
         </is>
       </c>
       <c r="G135" t="n">
-        <v>2</v>
+        <v>132</v>
       </c>
       <c r="H135" t="b">
         <v>0</v>
@@ -10192,34 +10151,34 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>B0BLP1JSRK</t>
+          <t>B0DCDSZ719</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>LDMST64E278</t>
+          <t>LDSG95DIE274</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>B0BLP1LN2C</t>
+          <t>B0DCFP1CX8</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>zero_sales_6mo</t>
+          <t>sales_drop_3mo</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>e27 2700k dimmable 8w amber 6 pack</t>
+          <t>fancy light bulbs</t>
         </is>
       </c>
       <c r="G136" t="n">
-        <v>1</v>
+        <v>64</v>
       </c>
       <c r="H136" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I136" t="b">
         <v>0</v>
@@ -10231,7 +10190,7 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>backend</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -10253,51 +10212,51 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>B0BLP1JSRK</t>
+          <t>B0DCDSZ719</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>LDMST64E278</t>
+          <t>LDSG95DIE274</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>B0BLP1LN2C</t>
+          <t>B0DCFP1CX8</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>zero_sales_6mo</t>
+          <t>sales_drop_3mo</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>bulb warm yellliw pack 6</t>
+          <t>dimmable led vintage</t>
         </is>
       </c>
       <c r="G137" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="H137" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I137" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>gap</t>
+          <t>present</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>pending_add</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
@@ -10314,31 +10273,31 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>B0BLP1JSRK</t>
+          <t>B0DCDSZ719</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>LDMST64E278</t>
+          <t>LDSG95DIE274</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>B0BLP1LN2C</t>
+          <t>B0DCFP1CX8</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>zero_sales_6mo</t>
+          <t>sales_drop_3mo</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>squirrel cage vintage edison e27 screw bulb 8w clear</t>
+          <t>e14 2w diamond shaped bulb</t>
         </is>
       </c>
       <c r="G138" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="H138" t="b">
         <v>0</v>
@@ -10375,34 +10334,34 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>B0BLP1JSRK</t>
+          <t>B0DCDSZ719</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>LDMST64E278</t>
+          <t>LDSG95DIE274</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>B0BLP1LN2C</t>
+          <t>B0DCFP1CX8</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>zero_sales_6mo</t>
+          <t>sales_drop_3mo</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>6 led e27 st64 8w 60 w dimmable warm white 2700k</t>
+          <t>fancy lightbulbs</t>
         </is>
       </c>
       <c r="G139" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H139" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I139" t="b">
         <v>0</v>
@@ -10414,7 +10373,7 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>backend</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -10436,31 +10395,31 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>B0BLP1JSRK</t>
+          <t>B0DCDSZ719</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>LDMST64E278</t>
+          <t>LDSG95DIE274</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>B0BLP1LN2C</t>
+          <t>B0DCFP1CX8</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>zero_sales_6mo</t>
+          <t>sales_drop_3mo</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>vintage 60w es bulb pack not dimmable</t>
+          <t>e17 warm light bulb</t>
         </is>
       </c>
       <c r="G140" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H140" t="b">
         <v>0</v>
@@ -10497,31 +10456,31 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>B0BLP1JSRK</t>
+          <t>B0DCDSZ719</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>LDMST64E278</t>
+          <t>LDSG95DIE274</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>B0D7HPWK2P</t>
+          <t>B0DCFP1CX8</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>zero_sales_6mo</t>
+          <t>sales_drop_3mo</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>e27 vintage bulb 60w</t>
+          <t>decorative led bulb xxl</t>
         </is>
       </c>
       <c r="G141" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="H141" t="b">
         <v>0</v>
@@ -10558,17 +10517,17 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>B0BLP1JSRK</t>
+          <t>B0DCDSZ719</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>LDMST64E278</t>
+          <t>LDSG95DIE274</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>B0D7HPWK2P</t>
+          <t>B0DR1XY3R6</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -10578,31 +10537,31 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>e27 es dimmable bulb 8w squirrel cage</t>
+          <t>vintage light bulb</t>
         </is>
       </c>
       <c r="G142" t="n">
-        <v>4</v>
+        <v>394</v>
       </c>
       <c r="H142" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I142" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>gap</t>
+          <t>present</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>pending_add</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
@@ -10619,17 +10578,17 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>B0BLP1JSRK</t>
+          <t>B0DCDSZ719</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>LDMST64E278</t>
+          <t>LDSG95DIE274</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>B0D7HPWK2P</t>
+          <t>B0DR1XY3R6</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -10639,31 +10598,31 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>bravo lighting bulbs 8w dimmable</t>
+          <t>decorative light bulbs</t>
         </is>
       </c>
       <c r="G143" t="n">
-        <v>4</v>
+        <v>213</v>
       </c>
       <c r="H143" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I143" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>gap</t>
+          <t>present</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>pending_add</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
@@ -10680,17 +10639,17 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>B0BLP1JSRK</t>
+          <t>B0DCDSZ719</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>LDMST64E278</t>
+          <t>LDSG95DIE274</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>B0D7HPWK2P</t>
+          <t>B0DR1XY3R6</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -10700,31 +10659,31 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>ledsone pack 3 | vintage led edison e27 light bulb, 8w (equivalent 60w) st64 dimmable 2700k warm white amber glass screw 806 lumens| energy saving bulb for squirrel cage lamp 220v [energy class a]</t>
+          <t>e27 vintage light bulbs</t>
         </is>
       </c>
       <c r="G144" t="n">
-        <v>4</v>
+        <v>177</v>
       </c>
       <c r="H144" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I144" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>gap</t>
+          <t>present</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>pending_add</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -10741,17 +10700,17 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>B0BLP1JSRK</t>
+          <t>B0DCDSZ719</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>LDMST64E278</t>
+          <t>LDSG95DIE274</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>B0D7HPWK2P</t>
+          <t>B0DR1XY3R6</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -10761,14 +10720,14 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>e27 8w vintage light bulbs</t>
+          <t>e14 vintage bulb</t>
         </is>
       </c>
       <c r="G145" t="n">
-        <v>4</v>
+        <v>132</v>
       </c>
       <c r="H145" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I145" t="b">
         <v>0</v>
@@ -10780,7 +10739,7 @@
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>backend</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -10802,17 +10761,17 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>B0BLP1JSRK</t>
+          <t>B0DCDSZ719</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>LDMST64E278</t>
+          <t>LDSG95DIE274</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>B0D7HPWK2P</t>
+          <t>B0DR1XY3R6</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -10822,31 +10781,31 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>squirrel led cage dimmable</t>
+          <t>fancy light bulbs</t>
         </is>
       </c>
       <c r="G146" t="n">
-        <v>3</v>
+        <v>64</v>
       </c>
       <c r="H146" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I146" t="b">
         <v>1</v>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>gap</t>
+          <t>present</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>bullet</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>pending_add</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
@@ -10863,17 +10822,17 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>B0BLP1JSRK</t>
+          <t>B0DCDSZ719</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>LDMST64E278</t>
+          <t>LDSG95DIE274</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>B0D7HPWK2P</t>
+          <t>B0DR1XY3R6</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -10883,31 +10842,31 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>bul-e27-rus-w1 bulb</t>
+          <t>dimmable led vintage</t>
         </is>
       </c>
       <c r="G147" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="H147" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I147" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>gap</t>
+          <t>present</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>pending_add</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
@@ -10924,17 +10883,17 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>B0BLP1JSRK</t>
+          <t>B0DCDSZ719</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>LDMST64E278</t>
+          <t>LDSG95DIE274</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>B0D7HPWK2P</t>
+          <t>B0DR1XY3R6</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -10944,11 +10903,11 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>e27 8w 2200k 720lumen</t>
+          <t>e14 2w diamond shaped bulb</t>
         </is>
       </c>
       <c r="G148" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="H148" t="b">
         <v>0</v>
@@ -10985,17 +10944,17 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>B0BLP1JSRK</t>
+          <t>B0DCDSZ719</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>LDMST64E278</t>
+          <t>LDSG95DIE274</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>B0D7HPWK2P</t>
+          <t>B0DR1XY3R6</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -11005,11 +10964,11 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>e27 dimmable bulb pack of six</t>
+          <t>fancy lightbulbs</t>
         </is>
       </c>
       <c r="G149" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H149" t="b">
         <v>0</v>
@@ -11046,17 +11005,17 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>B0BLP1JSRK</t>
+          <t>B0DCDSZ719</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>LDMST64E278</t>
+          <t>LDSG95DIE274</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>B0D7HPWK2P</t>
+          <t>B0DR1XY3R6</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -11066,17 +11025,17 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>light bulbs screv wintage 8w</t>
+          <t>e17 warm light bulb</t>
         </is>
       </c>
       <c r="G150" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H150" t="b">
         <v>0</v>
       </c>
       <c r="I150" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J150" t="inlineStr">
         <is>
@@ -11085,7 +11044,7 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>bullet</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -11107,17 +11066,17 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>B0BLP1JSRK</t>
+          <t>B0DCDSZ719</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>LDMST64E278</t>
+          <t>LDSG95DIE274</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>B0D7HPWK2P</t>
+          <t>B0DR1XY3R6</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -11127,14 +11086,14 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>e27 2700k dimmable 8w amber 6 pack</t>
+          <t>decorative led bulb xxl</t>
         </is>
       </c>
       <c r="G151" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H151" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I151" t="b">
         <v>0</v>
@@ -11146,7 +11105,7 @@
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>backend</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -11160,2514 +11119,278 @@
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>ledsone_uk</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>B0BLP1JSRK</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>LDMST64E278</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>B0D7HPWK2P</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>zero_sales_6mo</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>bulb warm yellliw pack 6</t>
-        </is>
-      </c>
-      <c r="G152" t="n">
-        <v>1</v>
-      </c>
-      <c r="H152" t="b">
-        <v>0</v>
-      </c>
-      <c r="I152" t="b">
-        <v>0</v>
-      </c>
-      <c r="J152" t="inlineStr">
-        <is>
-          <t>gap</t>
-        </is>
-      </c>
-      <c r="K152" t="inlineStr">
-        <is>
-          <t>backend_and_bullet</t>
-        </is>
-      </c>
-      <c r="L152" t="inlineStr">
-        <is>
-          <t>pending_add</t>
-        </is>
-      </c>
-      <c r="M152" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>ledsone_uk</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>B0BLP1JSRK</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>LDMST64E278</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>B0D7HPWK2P</t>
-        </is>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>zero_sales_6mo</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>squirrel cage vintage edison e27 screw bulb 8w clear</t>
-        </is>
-      </c>
-      <c r="G153" t="n">
-        <v>1</v>
-      </c>
-      <c r="H153" t="b">
-        <v>0</v>
-      </c>
-      <c r="I153" t="b">
-        <v>0</v>
-      </c>
-      <c r="J153" t="inlineStr">
-        <is>
-          <t>gap</t>
-        </is>
-      </c>
-      <c r="K153" t="inlineStr">
-        <is>
-          <t>backend_and_bullet</t>
-        </is>
-      </c>
-      <c r="L153" t="inlineStr">
-        <is>
-          <t>pending_add</t>
-        </is>
-      </c>
-      <c r="M153" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>ledsone_uk</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>B0BLP1JSRK</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>LDMST64E278</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>B0D7HPWK2P</t>
-        </is>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>zero_sales_6mo</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>6 led e27 st64 8w 60 w dimmable warm white 2700k</t>
-        </is>
-      </c>
-      <c r="G154" t="n">
-        <v>1</v>
-      </c>
-      <c r="H154" t="b">
-        <v>0</v>
-      </c>
-      <c r="I154" t="b">
-        <v>0</v>
-      </c>
-      <c r="J154" t="inlineStr">
-        <is>
-          <t>gap</t>
-        </is>
-      </c>
-      <c r="K154" t="inlineStr">
-        <is>
-          <t>backend_and_bullet</t>
-        </is>
-      </c>
-      <c r="L154" t="inlineStr">
-        <is>
-          <t>pending_add</t>
-        </is>
-      </c>
-      <c r="M154" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>ledsone_uk</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>B0BLP1JSRK</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>LDMST64E278</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>B0D7HPWK2P</t>
-        </is>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>zero_sales_6mo</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>vintage 60w es bulb pack not dimmable</t>
-        </is>
-      </c>
-      <c r="G155" t="n">
-        <v>1</v>
-      </c>
-      <c r="H155" t="b">
-        <v>0</v>
-      </c>
-      <c r="I155" t="b">
-        <v>0</v>
-      </c>
-      <c r="J155" t="inlineStr">
-        <is>
-          <t>gap</t>
-        </is>
-      </c>
-      <c r="K155" t="inlineStr">
-        <is>
-          <t>backend_and_bullet</t>
-        </is>
-      </c>
-      <c r="L155" t="inlineStr">
-        <is>
-          <t>pending_add</t>
-        </is>
-      </c>
-      <c r="M155" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>ledsone_uk</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>B09JM3PLLH</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>LDSG125LOE274</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>B0DBTNQT8Z</t>
-        </is>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>zero_sales_6mo</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>large e27 vintage light bulbs</t>
-        </is>
-      </c>
-      <c r="G156" t="n">
-        <v>150</v>
-      </c>
-      <c r="H156" t="b">
-        <v>0</v>
-      </c>
-      <c r="I156" t="b">
-        <v>0</v>
-      </c>
-      <c r="J156" t="inlineStr">
-        <is>
-          <t>gap</t>
-        </is>
-      </c>
-      <c r="K156" t="inlineStr">
-        <is>
-          <t>backend_and_bullet</t>
-        </is>
-      </c>
-      <c r="L156" t="inlineStr">
-        <is>
-          <t>pending_add</t>
-        </is>
-      </c>
-      <c r="M156" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>ledsone_uk</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>B09JM3PLLH</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>LDSG125LOE274</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>B0DBTNQT8Z</t>
-        </is>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>zero_sales_6mo</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>edison bulb</t>
-        </is>
-      </c>
-      <c r="G157" t="n">
-        <v>133</v>
-      </c>
-      <c r="H157" t="b">
-        <v>1</v>
-      </c>
-      <c r="I157" t="b">
-        <v>1</v>
-      </c>
-      <c r="J157" t="inlineStr">
-        <is>
-          <t>present</t>
-        </is>
-      </c>
-      <c r="K157" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="L157" t="inlineStr">
-        <is>
-          <t>reviewed</t>
-        </is>
-      </c>
-      <c r="M157" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>ledsone_uk</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>B09JM3PLLH</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>LDSG125LOE274</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>B0DBTNQT8Z</t>
-        </is>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>zero_sales_6mo</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>love light bulb</t>
-        </is>
-      </c>
-      <c r="G158" t="n">
-        <v>74</v>
-      </c>
-      <c r="H158" t="b">
-        <v>1</v>
-      </c>
-      <c r="I158" t="b">
-        <v>1</v>
-      </c>
-      <c r="J158" t="inlineStr">
-        <is>
-          <t>present</t>
-        </is>
-      </c>
-      <c r="K158" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="L158" t="inlineStr">
-        <is>
-          <t>reviewed</t>
-        </is>
-      </c>
-      <c r="M158" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>ledsone_uk</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>B09JM3PLLH</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>LDSG125LOE274</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>B0DBTNQT8Z</t>
-        </is>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>zero_sales_6mo</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>e27 screw bulb decorative</t>
-        </is>
-      </c>
-      <c r="G159" t="n">
-        <v>55</v>
-      </c>
-      <c r="H159" t="b">
-        <v>1</v>
-      </c>
-      <c r="I159" t="b">
-        <v>0</v>
-      </c>
-      <c r="J159" t="inlineStr">
-        <is>
-          <t>gap</t>
-        </is>
-      </c>
-      <c r="K159" t="inlineStr">
-        <is>
-          <t>backend</t>
-        </is>
-      </c>
-      <c r="L159" t="inlineStr">
-        <is>
-          <t>pending_add</t>
-        </is>
-      </c>
-      <c r="M159" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>ledsone_uk</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>B09JM3PLLH</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>LDSG125LOE274</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>B0DBTNQT8Z</t>
-        </is>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>zero_sales_6mo</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>e27 large globe bulb</t>
-        </is>
-      </c>
-      <c r="G160" t="n">
-        <v>50</v>
-      </c>
-      <c r="H160" t="b">
-        <v>0</v>
-      </c>
-      <c r="I160" t="b">
-        <v>0</v>
-      </c>
-      <c r="J160" t="inlineStr">
-        <is>
-          <t>gap</t>
-        </is>
-      </c>
-      <c r="K160" t="inlineStr">
-        <is>
-          <t>backend_and_bullet</t>
-        </is>
-      </c>
-      <c r="L160" t="inlineStr">
-        <is>
-          <t>pending_add</t>
-        </is>
-      </c>
-      <c r="M160" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>ledsone_uk</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>B09JM3PLLH</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>LDSG125LOE274</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>B0DBTNQT8Z</t>
-        </is>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>zero_sales_6mo</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>extra large edison bulb</t>
-        </is>
-      </c>
-      <c r="G161" t="n">
-        <v>40</v>
-      </c>
-      <c r="H161" t="b">
-        <v>0</v>
-      </c>
-      <c r="I161" t="b">
-        <v>0</v>
-      </c>
-      <c r="J161" t="inlineStr">
-        <is>
-          <t>gap</t>
-        </is>
-      </c>
-      <c r="K161" t="inlineStr">
-        <is>
-          <t>backend_and_bullet</t>
-        </is>
-      </c>
-      <c r="L161" t="inlineStr">
-        <is>
-          <t>pending_add</t>
-        </is>
-      </c>
-      <c r="M161" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>ledsone_uk</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>B09JM3PLLH</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>LDSG125LOE274</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>B0DBTNQT8Z</t>
-        </is>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>zero_sales_6mo</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>big bulb</t>
-        </is>
-      </c>
-      <c r="G162" t="n">
-        <v>20</v>
-      </c>
-      <c r="H162" t="b">
-        <v>0</v>
-      </c>
-      <c r="I162" t="b">
-        <v>1</v>
-      </c>
-      <c r="J162" t="inlineStr">
-        <is>
-          <t>gap</t>
-        </is>
-      </c>
-      <c r="K162" t="inlineStr">
-        <is>
-          <t>bullet</t>
-        </is>
-      </c>
-      <c r="L162" t="inlineStr">
-        <is>
-          <t>pending_add</t>
-        </is>
-      </c>
-      <c r="M162" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>ledsone_uk</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>B09JM3PLLH</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>LDSG125LOE274</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>B0DBTNQT8Z</t>
-        </is>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>zero_sales_6mo</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>e27 screw bulb spiral</t>
-        </is>
-      </c>
-      <c r="G163" t="n">
-        <v>17</v>
-      </c>
-      <c r="H163" t="b">
-        <v>0</v>
-      </c>
-      <c r="I163" t="b">
-        <v>0</v>
-      </c>
-      <c r="J163" t="inlineStr">
-        <is>
-          <t>gap</t>
-        </is>
-      </c>
-      <c r="K163" t="inlineStr">
-        <is>
-          <t>backend_and_bullet</t>
-        </is>
-      </c>
-      <c r="L163" t="inlineStr">
-        <is>
-          <t>pending_add</t>
-        </is>
-      </c>
-      <c r="M163" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>ledsone_uk</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>B09JM3PLLH</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>LDSG125LOE274</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>B0DBTNQT8Z</t>
-        </is>
-      </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>zero_sales_6mo</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>warm white large screw light bulbs</t>
-        </is>
-      </c>
-      <c r="G164" t="n">
-        <v>16</v>
-      </c>
-      <c r="H164" t="b">
-        <v>0</v>
-      </c>
-      <c r="I164" t="b">
-        <v>0</v>
-      </c>
-      <c r="J164" t="inlineStr">
-        <is>
-          <t>gap</t>
-        </is>
-      </c>
-      <c r="K164" t="inlineStr">
-        <is>
-          <t>backend_and_bullet</t>
-        </is>
-      </c>
-      <c r="L164" t="inlineStr">
-        <is>
-          <t>pending_add</t>
-        </is>
-      </c>
-      <c r="M164" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>ledsone_uk</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>B09JM3PLLH</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>LDSG125LOE274</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>B0DBTNQT8Z</t>
-        </is>
-      </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>zero_sales_6mo</t>
-        </is>
-      </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>love bulb</t>
-        </is>
-      </c>
-      <c r="G165" t="n">
-        <v>14</v>
-      </c>
-      <c r="H165" t="b">
-        <v>1</v>
-      </c>
-      <c r="I165" t="b">
-        <v>1</v>
-      </c>
-      <c r="J165" t="inlineStr">
-        <is>
-          <t>present</t>
-        </is>
-      </c>
-      <c r="K165" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="L165" t="inlineStr">
-        <is>
-          <t>reviewed</t>
-        </is>
-      </c>
-      <c r="M165" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>ledsone_uk</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>B09JM3PLLH</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>LDSG125LOE274</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>B0DBTNQT8Z</t>
-        </is>
-      </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>zero_sales_6mo</t>
-        </is>
-      </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>g125 led bulb</t>
-        </is>
-      </c>
-      <c r="G166" t="n">
-        <v>6</v>
-      </c>
-      <c r="H166" t="b">
-        <v>1</v>
-      </c>
-      <c r="I166" t="b">
-        <v>1</v>
-      </c>
-      <c r="J166" t="inlineStr">
-        <is>
-          <t>present</t>
-        </is>
-      </c>
-      <c r="K166" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="L166" t="inlineStr">
-        <is>
-          <t>reviewed</t>
-        </is>
-      </c>
-      <c r="M166" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>ledsone_uk</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>B09JM3PLLH</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>LDSG125LOE274</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>B0DBTNQT8Z</t>
-        </is>
-      </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>zero_sales_6mo</t>
-        </is>
-      </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>screw e27 led light bulb, 4w globe large screw vintage edison led bulbs</t>
-        </is>
-      </c>
-      <c r="G167" t="n">
-        <v>6</v>
-      </c>
-      <c r="H167" t="b">
-        <v>0</v>
-      </c>
-      <c r="I167" t="b">
-        <v>0</v>
-      </c>
-      <c r="J167" t="inlineStr">
-        <is>
-          <t>gap</t>
-        </is>
-      </c>
-      <c r="K167" t="inlineStr">
-        <is>
-          <t>backend_and_bullet</t>
-        </is>
-      </c>
-      <c r="L167" t="inlineStr">
-        <is>
-          <t>pending_add</t>
-        </is>
-      </c>
-      <c r="M167" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>ledsone_uk</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>B09JM3PLLH</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>LDSG125LOE274</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>B0DBTNQT8Z</t>
-        </is>
-      </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>zero_sales_6mo</t>
-        </is>
-      </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>large edison screw bulb warm white</t>
-        </is>
-      </c>
-      <c r="G168" t="n">
-        <v>5</v>
-      </c>
-      <c r="H168" t="b">
-        <v>0</v>
-      </c>
-      <c r="I168" t="b">
-        <v>0</v>
-      </c>
-      <c r="J168" t="inlineStr">
-        <is>
-          <t>gap</t>
-        </is>
-      </c>
-      <c r="K168" t="inlineStr">
-        <is>
-          <t>backend_and_bullet</t>
-        </is>
-      </c>
-      <c r="L168" t="inlineStr">
-        <is>
-          <t>pending_add</t>
-        </is>
-      </c>
-      <c r="M168" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>ledsone_uk</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>B09JM3PLLH</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>LDSG125LOE274</t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr">
-        <is>
-          <t>B0DBTNQT8Z</t>
-        </is>
-      </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>zero_sales_6mo</t>
-        </is>
-      </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>light bulb with amber love</t>
-        </is>
-      </c>
-      <c r="G169" t="n">
-        <v>5</v>
-      </c>
-      <c r="H169" t="b">
-        <v>1</v>
-      </c>
-      <c r="I169" t="b">
-        <v>0</v>
-      </c>
-      <c r="J169" t="inlineStr">
-        <is>
-          <t>gap</t>
-        </is>
-      </c>
-      <c r="K169" t="inlineStr">
-        <is>
-          <t>backend</t>
-        </is>
-      </c>
-      <c r="L169" t="inlineStr">
-        <is>
-          <t>pending_add</t>
-        </is>
-      </c>
-      <c r="M169" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>ledsone_uk</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>B09JM3PLLH</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>LDSG125LOE274</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>B0DBTNQT8Z</t>
-        </is>
-      </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>zero_sales_6mo</t>
-        </is>
-      </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>es love light bulb</t>
-        </is>
-      </c>
-      <c r="G170" t="n">
-        <v>3</v>
-      </c>
-      <c r="H170" t="b">
-        <v>1</v>
-      </c>
-      <c r="I170" t="b">
-        <v>1</v>
-      </c>
-      <c r="J170" t="inlineStr">
-        <is>
-          <t>present</t>
-        </is>
-      </c>
-      <c r="K170" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="L170" t="inlineStr">
-        <is>
-          <t>reviewed</t>
-        </is>
-      </c>
-      <c r="M170" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>ledsone_uk</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>B09JM3PLLH</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>LDSG125LOE274</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>B0DBTNQT8Z</t>
-        </is>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>zero_sales_6mo</t>
-        </is>
-      </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>e27 love light balb</t>
-        </is>
-      </c>
-      <c r="G171" t="n">
-        <v>2</v>
-      </c>
-      <c r="H171" t="b">
-        <v>0</v>
-      </c>
-      <c r="I171" t="b">
-        <v>0</v>
-      </c>
-      <c r="J171" t="inlineStr">
-        <is>
-          <t>gap</t>
-        </is>
-      </c>
-      <c r="K171" t="inlineStr">
-        <is>
-          <t>backend_and_bullet</t>
-        </is>
-      </c>
-      <c r="L171" t="inlineStr">
-        <is>
-          <t>pending_add</t>
-        </is>
-      </c>
-      <c r="M171" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>ledsone_uk</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>B09JM3PLLH</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>LDSG125LOE274</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>B0DBTNQT8Z</t>
-        </is>
-      </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>zero_sales_6mo</t>
-        </is>
-      </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>bulb writing</t>
-        </is>
-      </c>
-      <c r="G172" t="n">
-        <v>1</v>
-      </c>
-      <c r="H172" t="b">
-        <v>0</v>
-      </c>
-      <c r="I172" t="b">
-        <v>0</v>
-      </c>
-      <c r="J172" t="inlineStr">
-        <is>
-          <t>gap</t>
-        </is>
-      </c>
-      <c r="K172" t="inlineStr">
-        <is>
-          <t>backend_and_bullet</t>
-        </is>
-      </c>
-      <c r="L172" t="inlineStr">
-        <is>
-          <t>pending_add</t>
-        </is>
-      </c>
-      <c r="M172" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>ledsone_uk</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>B0DCDSZ719</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>LDSG95DIE274</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>B0DCFP1CX8</t>
-        </is>
-      </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>sales_drop_3mo</t>
-        </is>
-      </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>vintage light bulb</t>
-        </is>
-      </c>
-      <c r="G173" t="n">
-        <v>394</v>
-      </c>
-      <c r="H173" t="b">
-        <v>1</v>
-      </c>
-      <c r="I173" t="b">
-        <v>1</v>
-      </c>
-      <c r="J173" t="inlineStr">
-        <is>
-          <t>present</t>
-        </is>
-      </c>
-      <c r="K173" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="L173" t="inlineStr">
-        <is>
-          <t>reviewed</t>
-        </is>
-      </c>
-      <c r="M173" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>ledsone_uk</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>B0DCDSZ719</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>LDSG95DIE274</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>B0DCFP1CX8</t>
-        </is>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>sales_drop_3mo</t>
-        </is>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>decorative light bulbs</t>
-        </is>
-      </c>
-      <c r="G174" t="n">
-        <v>213</v>
-      </c>
-      <c r="H174" t="b">
-        <v>1</v>
-      </c>
-      <c r="I174" t="b">
-        <v>0</v>
-      </c>
-      <c r="J174" t="inlineStr">
-        <is>
-          <t>gap</t>
-        </is>
-      </c>
-      <c r="K174" t="inlineStr">
-        <is>
-          <t>backend</t>
-        </is>
-      </c>
-      <c r="L174" t="inlineStr">
-        <is>
-          <t>pending_add</t>
-        </is>
-      </c>
-      <c r="M174" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>ledsone_uk</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>B0DCDSZ719</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>LDSG95DIE274</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>B0DCFP1CX8</t>
-        </is>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>sales_drop_3mo</t>
-        </is>
-      </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>e27 vintage light bulbs</t>
-        </is>
-      </c>
-      <c r="G175" t="n">
-        <v>177</v>
-      </c>
-      <c r="H175" t="b">
-        <v>1</v>
-      </c>
-      <c r="I175" t="b">
-        <v>0</v>
-      </c>
-      <c r="J175" t="inlineStr">
-        <is>
-          <t>gap</t>
-        </is>
-      </c>
-      <c r="K175" t="inlineStr">
-        <is>
-          <t>backend</t>
-        </is>
-      </c>
-      <c r="L175" t="inlineStr">
-        <is>
-          <t>pending_add</t>
-        </is>
-      </c>
-      <c r="M175" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>ledsone_uk</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>B0DCDSZ719</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>LDSG95DIE274</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>B0DCFP1CX8</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>sales_drop_3mo</t>
-        </is>
-      </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>e14 vintage bulb</t>
-        </is>
-      </c>
-      <c r="G176" t="n">
-        <v>132</v>
-      </c>
-      <c r="H176" t="b">
-        <v>0</v>
-      </c>
-      <c r="I176" t="b">
-        <v>0</v>
-      </c>
-      <c r="J176" t="inlineStr">
-        <is>
-          <t>gap</t>
-        </is>
-      </c>
-      <c r="K176" t="inlineStr">
-        <is>
-          <t>backend_and_bullet</t>
-        </is>
-      </c>
-      <c r="L176" t="inlineStr">
-        <is>
-          <t>pending_add</t>
-        </is>
-      </c>
-      <c r="M176" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>ledsone_uk</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>B0DCDSZ719</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>LDSG95DIE274</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>B0DCFP1CX8</t>
-        </is>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>sales_drop_3mo</t>
-        </is>
-      </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>fancy light bulbs</t>
-        </is>
-      </c>
-      <c r="G177" t="n">
-        <v>64</v>
-      </c>
-      <c r="H177" t="b">
-        <v>0</v>
-      </c>
-      <c r="I177" t="b">
-        <v>0</v>
-      </c>
-      <c r="J177" t="inlineStr">
-        <is>
-          <t>gap</t>
-        </is>
-      </c>
-      <c r="K177" t="inlineStr">
-        <is>
-          <t>backend_and_bullet</t>
-        </is>
-      </c>
-      <c r="L177" t="inlineStr">
-        <is>
-          <t>pending_add</t>
-        </is>
-      </c>
-      <c r="M177" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>ledsone_uk</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>B0DCDSZ719</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>LDSG95DIE274</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>B0DCFP1CX8</t>
-        </is>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>sales_drop_3mo</t>
-        </is>
-      </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>dimmable led vintage</t>
-        </is>
-      </c>
-      <c r="G178" t="n">
-        <v>16</v>
-      </c>
-      <c r="H178" t="b">
-        <v>1</v>
-      </c>
-      <c r="I178" t="b">
-        <v>1</v>
-      </c>
-      <c r="J178" t="inlineStr">
-        <is>
-          <t>present</t>
-        </is>
-      </c>
-      <c r="K178" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="L178" t="inlineStr">
-        <is>
-          <t>reviewed</t>
-        </is>
-      </c>
-      <c r="M178" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>ledsone_uk</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>B0DCDSZ719</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>LDSG95DIE274</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>B0DCFP1CX8</t>
-        </is>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>sales_drop_3mo</t>
-        </is>
-      </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>e14 2w diamond shaped bulb</t>
-        </is>
-      </c>
-      <c r="G179" t="n">
-        <v>11</v>
-      </c>
-      <c r="H179" t="b">
-        <v>0</v>
-      </c>
-      <c r="I179" t="b">
-        <v>0</v>
-      </c>
-      <c r="J179" t="inlineStr">
-        <is>
-          <t>gap</t>
-        </is>
-      </c>
-      <c r="K179" t="inlineStr">
-        <is>
-          <t>backend_and_bullet</t>
-        </is>
-      </c>
-      <c r="L179" t="inlineStr">
-        <is>
-          <t>pending_add</t>
-        </is>
-      </c>
-      <c r="M179" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>ledsone_uk</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>B0DCDSZ719</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>LDSG95DIE274</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>B0DCFP1CX8</t>
-        </is>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>sales_drop_3mo</t>
-        </is>
-      </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>fancy lightbulbs</t>
-        </is>
-      </c>
-      <c r="G180" t="n">
-        <v>10</v>
-      </c>
-      <c r="H180" t="b">
-        <v>0</v>
-      </c>
-      <c r="I180" t="b">
-        <v>0</v>
-      </c>
-      <c r="J180" t="inlineStr">
-        <is>
-          <t>gap</t>
-        </is>
-      </c>
-      <c r="K180" t="inlineStr">
-        <is>
-          <t>backend_and_bullet</t>
-        </is>
-      </c>
-      <c r="L180" t="inlineStr">
-        <is>
-          <t>pending_add</t>
-        </is>
-      </c>
-      <c r="M180" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>ledsone_uk</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>B0DCDSZ719</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>LDSG95DIE274</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>B0DCFP1CX8</t>
-        </is>
-      </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>sales_drop_3mo</t>
-        </is>
-      </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>e17 warm light bulb</t>
-        </is>
-      </c>
-      <c r="G181" t="n">
-        <v>4</v>
-      </c>
-      <c r="H181" t="b">
-        <v>0</v>
-      </c>
-      <c r="I181" t="b">
-        <v>0</v>
-      </c>
-      <c r="J181" t="inlineStr">
-        <is>
-          <t>gap</t>
-        </is>
-      </c>
-      <c r="K181" t="inlineStr">
-        <is>
-          <t>backend_and_bullet</t>
-        </is>
-      </c>
-      <c r="L181" t="inlineStr">
-        <is>
-          <t>pending_add</t>
-        </is>
-      </c>
-      <c r="M181" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>ledsone_uk</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>B0DCDSZ719</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>LDSG95DIE274</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>B0DCFP1CX8</t>
-        </is>
-      </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>sales_drop_3mo</t>
-        </is>
-      </c>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>decorative led bulb xxl</t>
-        </is>
-      </c>
-      <c r="G182" t="n">
-        <v>3</v>
-      </c>
-      <c r="H182" t="b">
-        <v>0</v>
-      </c>
-      <c r="I182" t="b">
-        <v>0</v>
-      </c>
-      <c r="J182" t="inlineStr">
-        <is>
-          <t>gap</t>
-        </is>
-      </c>
-      <c r="K182" t="inlineStr">
-        <is>
-          <t>backend_and_bullet</t>
-        </is>
-      </c>
-      <c r="L182" t="inlineStr">
-        <is>
-          <t>pending_add</t>
-        </is>
-      </c>
-      <c r="M182" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>ledsone_uk</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>B0DCDSZ719</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>LDSG95DIE274</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>B0DR1XY3R6</t>
-        </is>
-      </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>zero_sales_6mo</t>
-        </is>
-      </c>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>vintage light bulb</t>
-        </is>
-      </c>
-      <c r="G183" t="n">
-        <v>394</v>
-      </c>
-      <c r="H183" t="b">
-        <v>1</v>
-      </c>
-      <c r="I183" t="b">
-        <v>1</v>
-      </c>
-      <c r="J183" t="inlineStr">
-        <is>
-          <t>present</t>
-        </is>
-      </c>
-      <c r="K183" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="L183" t="inlineStr">
-        <is>
-          <t>reviewed</t>
-        </is>
-      </c>
-      <c r="M183" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>ledsone_uk</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>B0DCDSZ719</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>LDSG95DIE274</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>B0DR1XY3R6</t>
-        </is>
-      </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>zero_sales_6mo</t>
-        </is>
-      </c>
-      <c r="F184" t="inlineStr">
-        <is>
-          <t>decorative light bulbs</t>
-        </is>
-      </c>
-      <c r="G184" t="n">
-        <v>213</v>
-      </c>
-      <c r="H184" t="b">
-        <v>1</v>
-      </c>
-      <c r="I184" t="b">
-        <v>1</v>
-      </c>
-      <c r="J184" t="inlineStr">
-        <is>
-          <t>present</t>
-        </is>
-      </c>
-      <c r="K184" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="L184" t="inlineStr">
-        <is>
-          <t>reviewed</t>
-        </is>
-      </c>
-      <c r="M184" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>ledsone_uk</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>B0DCDSZ719</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>LDSG95DIE274</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>B0DR1XY3R6</t>
-        </is>
-      </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>zero_sales_6mo</t>
-        </is>
-      </c>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>e27 vintage light bulbs</t>
-        </is>
-      </c>
-      <c r="G185" t="n">
-        <v>177</v>
-      </c>
-      <c r="H185" t="b">
-        <v>1</v>
-      </c>
-      <c r="I185" t="b">
-        <v>1</v>
-      </c>
-      <c r="J185" t="inlineStr">
-        <is>
-          <t>present</t>
-        </is>
-      </c>
-      <c r="K185" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="L185" t="inlineStr">
-        <is>
-          <t>reviewed</t>
-        </is>
-      </c>
-      <c r="M185" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>ledsone_uk</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>B0DCDSZ719</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>LDSG95DIE274</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>B0DR1XY3R6</t>
-        </is>
-      </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>zero_sales_6mo</t>
-        </is>
-      </c>
-      <c r="F186" t="inlineStr">
-        <is>
-          <t>e14 vintage bulb</t>
-        </is>
-      </c>
-      <c r="G186" t="n">
-        <v>132</v>
-      </c>
-      <c r="H186" t="b">
-        <v>0</v>
-      </c>
-      <c r="I186" t="b">
-        <v>0</v>
-      </c>
-      <c r="J186" t="inlineStr">
-        <is>
-          <t>gap</t>
-        </is>
-      </c>
-      <c r="K186" t="inlineStr">
-        <is>
-          <t>backend_and_bullet</t>
-        </is>
-      </c>
-      <c r="L186" t="inlineStr">
-        <is>
-          <t>pending_add</t>
-        </is>
-      </c>
-      <c r="M186" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>ledsone_uk</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>B0DCDSZ719</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>LDSG95DIE274</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>B0DR1XY3R6</t>
-        </is>
-      </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>zero_sales_6mo</t>
-        </is>
-      </c>
-      <c r="F187" t="inlineStr">
-        <is>
-          <t>fancy light bulbs</t>
-        </is>
-      </c>
-      <c r="G187" t="n">
-        <v>64</v>
-      </c>
-      <c r="H187" t="b">
-        <v>1</v>
-      </c>
-      <c r="I187" t="b">
-        <v>1</v>
-      </c>
-      <c r="J187" t="inlineStr">
-        <is>
-          <t>present</t>
-        </is>
-      </c>
-      <c r="K187" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="L187" t="inlineStr">
-        <is>
-          <t>reviewed</t>
-        </is>
-      </c>
-      <c r="M187" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>ledsone_uk</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>B0DCDSZ719</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>LDSG95DIE274</t>
-        </is>
-      </c>
-      <c r="D188" t="inlineStr">
-        <is>
-          <t>B0DR1XY3R6</t>
-        </is>
-      </c>
-      <c r="E188" t="inlineStr">
-        <is>
-          <t>zero_sales_6mo</t>
-        </is>
-      </c>
-      <c r="F188" t="inlineStr">
-        <is>
-          <t>dimmable led vintage</t>
-        </is>
-      </c>
-      <c r="G188" t="n">
-        <v>16</v>
-      </c>
-      <c r="H188" t="b">
-        <v>1</v>
-      </c>
-      <c r="I188" t="b">
-        <v>1</v>
-      </c>
-      <c r="J188" t="inlineStr">
-        <is>
-          <t>present</t>
-        </is>
-      </c>
-      <c r="K188" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="L188" t="inlineStr">
-        <is>
-          <t>reviewed</t>
-        </is>
-      </c>
-      <c r="M188" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>ledsone_uk</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>B0DCDSZ719</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>LDSG95DIE274</t>
-        </is>
-      </c>
-      <c r="D189" t="inlineStr">
-        <is>
-          <t>B0DR1XY3R6</t>
-        </is>
-      </c>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>zero_sales_6mo</t>
-        </is>
-      </c>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t>e14 2w diamond shaped bulb</t>
-        </is>
-      </c>
-      <c r="G189" t="n">
-        <v>11</v>
-      </c>
-      <c r="H189" t="b">
-        <v>0</v>
-      </c>
-      <c r="I189" t="b">
-        <v>0</v>
-      </c>
-      <c r="J189" t="inlineStr">
-        <is>
-          <t>gap</t>
-        </is>
-      </c>
-      <c r="K189" t="inlineStr">
-        <is>
-          <t>backend_and_bullet</t>
-        </is>
-      </c>
-      <c r="L189" t="inlineStr">
-        <is>
-          <t>pending_add</t>
-        </is>
-      </c>
-      <c r="M189" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>ledsone_uk</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>B0DCDSZ719</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>LDSG95DIE274</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr">
-        <is>
-          <t>B0DR1XY3R6</t>
-        </is>
-      </c>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t>zero_sales_6mo</t>
-        </is>
-      </c>
-      <c r="F190" t="inlineStr">
-        <is>
-          <t>fancy lightbulbs</t>
-        </is>
-      </c>
-      <c r="G190" t="n">
-        <v>10</v>
-      </c>
-      <c r="H190" t="b">
-        <v>0</v>
-      </c>
-      <c r="I190" t="b">
-        <v>0</v>
-      </c>
-      <c r="J190" t="inlineStr">
-        <is>
-          <t>gap</t>
-        </is>
-      </c>
-      <c r="K190" t="inlineStr">
-        <is>
-          <t>backend_and_bullet</t>
-        </is>
-      </c>
-      <c r="L190" t="inlineStr">
-        <is>
-          <t>pending_add</t>
-        </is>
-      </c>
-      <c r="M190" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>ledsone_uk</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>B0DCDSZ719</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>LDSG95DIE274</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr">
-        <is>
-          <t>B0DR1XY3R6</t>
-        </is>
-      </c>
-      <c r="E191" t="inlineStr">
-        <is>
-          <t>zero_sales_6mo</t>
-        </is>
-      </c>
-      <c r="F191" t="inlineStr">
-        <is>
-          <t>e17 warm light bulb</t>
-        </is>
-      </c>
-      <c r="G191" t="n">
-        <v>4</v>
-      </c>
-      <c r="H191" t="b">
-        <v>0</v>
-      </c>
-      <c r="I191" t="b">
-        <v>1</v>
-      </c>
-      <c r="J191" t="inlineStr">
-        <is>
-          <t>gap</t>
-        </is>
-      </c>
-      <c r="K191" t="inlineStr">
-        <is>
-          <t>bullet</t>
-        </is>
-      </c>
-      <c r="L191" t="inlineStr">
-        <is>
-          <t>pending_add</t>
-        </is>
-      </c>
-      <c r="M191" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>ledsone_uk</t>
-        </is>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>B0DCDSZ719</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>LDSG95DIE274</t>
-        </is>
-      </c>
-      <c r="D192" t="inlineStr">
-        <is>
-          <t>B0DR1XY3R6</t>
-        </is>
-      </c>
-      <c r="E192" t="inlineStr">
-        <is>
-          <t>zero_sales_6mo</t>
-        </is>
-      </c>
-      <c r="F192" t="inlineStr">
-        <is>
-          <t>decorative led bulb xxl</t>
-        </is>
-      </c>
-      <c r="G192" t="n">
-        <v>3</v>
-      </c>
-      <c r="H192" t="b">
-        <v>0</v>
-      </c>
-      <c r="I192" t="b">
-        <v>0</v>
-      </c>
-      <c r="J192" t="inlineStr">
-        <is>
-          <t>gap</t>
-        </is>
-      </c>
-      <c r="K192" t="inlineStr">
-        <is>
-          <t>backend_and_bullet</t>
-        </is>
-      </c>
-      <c r="L192" t="inlineStr">
-        <is>
-          <t>pending_add</t>
-        </is>
-      </c>
-      <c r="M192" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:M192"/>
+  <autoFilter ref="A1:M151"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="8" max="8"/>
+    <col width="60" customWidth="1" min="9" max="9"/>
+    <col width="44" customWidth="1" min="10" max="10"/>
+    <col width="60" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>brand</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>top_asin</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>base_sku</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>duplicate_asin</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>duplicate_sku</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>duplicate_status</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>top_watts</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>duplicate_watts</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>issue</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>recommended_action</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>date_checked</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ledsone_uk</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>B09Z6P8H29</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>LDCWB223</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>B0D5CMBXK6</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>LDCWB2236PK</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>zero_sales_6mo</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>same base SKU but the listings state different wattage (7W vs 3W) - the stored SKU looks wrong</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Check and correct the SKU before using this pair</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>LEDSone B22 Bayonet LED Light Bulb, GLS B22 LED Bulbs Cool White 6000K, Energy Saver Bulb, 80lm/W Lumen, Non-Dimmable (6 Pack, 3W)</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ledsone_uk</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>B0B8P9BKXB</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>LDMG125E278</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>B0B8P75R4Y</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>LDMG125E2782PK</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>zero_sales_6mo</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>8</v>
+      </c>
+      <c r="H3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>same base SKU but the listings state different wattage (8W vs 4W) - the stored SKU looks wrong</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Check and correct the SKU before using this pair</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>LED G125 Vintage Non-Dimmable Edison Christmas Decorative Light Bulb 4W(40 Watts Equivalent), E27 Screw Warm White 2700K Energy-Saving Spiral Marry X-mas Filament Globe Home Pendant Lmap (PACK 2)S</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ledsone_uk</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>B0BLP1JSRK</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>LDMST64E278</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>B0D7HPWK2P</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>LDMST64E2786PK k</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>zero_sales_6mo</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>8</v>
+      </c>
+      <c r="H4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>same base SKU but the listings state different wattage (8W vs 4W) - the stored SKU looks wrong</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Check and correct the SKU before using this pair</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>LEDSone LED Edison Bulb, Vintage Light Bulb,4W/6W/8W E27 2700K Warm white ST64 LED Bulbs, Led Filament Bulbs, Dimmable Antique Style Retro Amber Glass Screw Lamp 220V (6 Pack, 8W)</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:L4"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/development/abiraj_mini_aios_workbench/projects/PRJ-2026-026_amazon-keyword-gap-sync/evidence/final_outputs/REQ-30_amazon-keyword-gap-sync/REQ-30-D02_keyword_gap_report.xlsx
+++ b/development/abiraj_mini_aios_workbench/projects/PRJ-2026-026_amazon-keyword-gap-sync/evidence/final_outputs/REQ-30_amazon-keyword-gap-sync/REQ-30-D02_keyword_gap_report.xlsx
@@ -15,8 +15,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Part A - No Content'!$A$1:$K$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Part B - Keyword Gaps'!$A$1:$M$151</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Part C - SKU mismatch'!$A$1:$L$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Part B - Keyword Gaps'!$A$1:$M$166</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Part C - SKU mismatch'!$A$1:$L$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Field Reference'!$A$1:$B$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -492,7 +492,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-19T11:52:27</t>
+          <t>2026-08-19T12:03:23</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>3 pairs REJECTED — same base SKU but the two listings state different wattage, so the stored SKU is wrong. Not keyword-checked; the SKU needs correcting first.</t>
+          <t>2 pairs REJECTED — same base SKU but the two listings state different wattage, so the stored SKU is wrong. Not keyword-checked; the SKU needs correcting first.</t>
         </is>
       </c>
     </row>
@@ -684,7 +684,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>150 keyword rows across listings that DO have content — 115 real, actionable gaps.</t>
+          <t>165 keyword rows across listings that DO have content — 130 real, actionable gaps.</t>
         </is>
       </c>
     </row>
@@ -1884,7 +1884,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M151"/>
+  <dimension ref="A1:M166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8870,17 +8870,17 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>B09JM3PLLH</t>
+          <t>B0BLP1JSRK</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>LDSG125LOE274</t>
+          <t>LDMST64E278</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>B0DBTNQT8Z</t>
+          <t>B0D7HPWK2P</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -8890,11 +8890,11 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>large e27 vintage light bulbs</t>
+          <t>e27 vintage bulb 60w</t>
         </is>
       </c>
       <c r="G115" t="n">
-        <v>150</v>
+        <v>11</v>
       </c>
       <c r="H115" t="b">
         <v>0</v>
@@ -8931,17 +8931,17 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>B09JM3PLLH</t>
+          <t>B0BLP1JSRK</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>LDSG125LOE274</t>
+          <t>LDMST64E278</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>B0DBTNQT8Z</t>
+          <t>B0D7HPWK2P</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -8951,31 +8951,31 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>edison bulb</t>
+          <t>e27 es dimmable bulb 8w squirrel cage</t>
         </is>
       </c>
       <c r="G116" t="n">
-        <v>133</v>
+        <v>4</v>
       </c>
       <c r="H116" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I116" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>present</t>
+          <t>gap</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>pending_add</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
@@ -8992,17 +8992,17 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>B09JM3PLLH</t>
+          <t>B0BLP1JSRK</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>LDSG125LOE274</t>
+          <t>LDMST64E278</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>B0DBTNQT8Z</t>
+          <t>B0D7HPWK2P</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -9012,31 +9012,31 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>love light bulb</t>
+          <t>bravo lighting bulbs 8w dimmable</t>
         </is>
       </c>
       <c r="G117" t="n">
-        <v>74</v>
+        <v>4</v>
       </c>
       <c r="H117" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I117" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>present</t>
+          <t>gap</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>pending_add</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
@@ -9053,17 +9053,17 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>B09JM3PLLH</t>
+          <t>B0BLP1JSRK</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>LDSG125LOE274</t>
+          <t>LDMST64E278</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>B0DBTNQT8Z</t>
+          <t>B0D7HPWK2P</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -9073,14 +9073,14 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>e27 screw bulb decorative</t>
+          <t>ledsone pack 3 | vintage led edison e27 light bulb, 8w (equivalent 60w) st64 dimmable 2700k warm white amber glass screw 806 lumens| energy saving bulb for squirrel cage lamp 220v [energy class a]</t>
         </is>
       </c>
       <c r="G118" t="n">
-        <v>55</v>
+        <v>4</v>
       </c>
       <c r="H118" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I118" t="b">
         <v>0</v>
@@ -9092,7 +9092,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>backend</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -9114,17 +9114,17 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>B09JM3PLLH</t>
+          <t>B0BLP1JSRK</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>LDSG125LOE274</t>
+          <t>LDMST64E278</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>B0DBTNQT8Z</t>
+          <t>B0D7HPWK2P</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -9134,14 +9134,14 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>e27 large globe bulb</t>
+          <t>e27 8w vintage light bulbs</t>
         </is>
       </c>
       <c r="G119" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="H119" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I119" t="b">
         <v>0</v>
@@ -9153,7 +9153,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>backend</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -9175,17 +9175,17 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>B09JM3PLLH</t>
+          <t>B0BLP1JSRK</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>LDSG125LOE274</t>
+          <t>LDMST64E278</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>B0DBTNQT8Z</t>
+          <t>B0D7HPWK2P</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -9195,17 +9195,17 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>extra large edison bulb</t>
+          <t>squirrel led cage dimmable</t>
         </is>
       </c>
       <c r="G120" t="n">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="H120" t="b">
         <v>0</v>
       </c>
       <c r="I120" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J120" t="inlineStr">
         <is>
@@ -9214,7 +9214,7 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>bullet</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -9236,17 +9236,17 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>B09JM3PLLH</t>
+          <t>B0BLP1JSRK</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>LDSG125LOE274</t>
+          <t>LDMST64E278</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>B0DBTNQT8Z</t>
+          <t>B0D7HPWK2P</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -9256,17 +9256,17 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>big bulb</t>
+          <t>bul-e27-rus-w1 bulb</t>
         </is>
       </c>
       <c r="G121" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="H121" t="b">
         <v>0</v>
       </c>
       <c r="I121" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J121" t="inlineStr">
         <is>
@@ -9275,7 +9275,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>bullet</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -9297,17 +9297,17 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>B09JM3PLLH</t>
+          <t>B0BLP1JSRK</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>LDSG125LOE274</t>
+          <t>LDMST64E278</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>B0DBTNQT8Z</t>
+          <t>B0D7HPWK2P</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -9317,11 +9317,11 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>e27 screw bulb spiral</t>
+          <t>e27 8w 2200k 720lumen</t>
         </is>
       </c>
       <c r="G122" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="H122" t="b">
         <v>0</v>
@@ -9358,17 +9358,17 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>B09JM3PLLH</t>
+          <t>B0BLP1JSRK</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>LDSG125LOE274</t>
+          <t>LDMST64E278</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>B0DBTNQT8Z</t>
+          <t>B0D7HPWK2P</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -9378,11 +9378,11 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>warm white large screw light bulbs</t>
+          <t>e27 dimmable bulb pack of six</t>
         </is>
       </c>
       <c r="G123" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="H123" t="b">
         <v>0</v>
@@ -9419,17 +9419,17 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>B09JM3PLLH</t>
+          <t>B0BLP1JSRK</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>LDSG125LOE274</t>
+          <t>LDMST64E278</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>B0DBTNQT8Z</t>
+          <t>B0D7HPWK2P</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -9439,31 +9439,31 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>love bulb</t>
+          <t>light bulbs screv wintage 8w</t>
         </is>
       </c>
       <c r="G124" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="H124" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I124" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>present</t>
+          <t>gap</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>pending_add</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -9480,17 +9480,17 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>B09JM3PLLH</t>
+          <t>B0BLP1JSRK</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>LDSG125LOE274</t>
+          <t>LDMST64E278</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>B0DBTNQT8Z</t>
+          <t>B0D7HPWK2P</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -9500,31 +9500,31 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>g125 led bulb</t>
+          <t>e27 2700k dimmable 8w amber 6 pack</t>
         </is>
       </c>
       <c r="G125" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H125" t="b">
         <v>1</v>
       </c>
       <c r="I125" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>present</t>
+          <t>gap</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>backend</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>pending_add</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -9541,17 +9541,17 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>B09JM3PLLH</t>
+          <t>B0BLP1JSRK</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>LDSG125LOE274</t>
+          <t>LDMST64E278</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>B0DBTNQT8Z</t>
+          <t>B0D7HPWK2P</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -9561,11 +9561,11 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>screw e27 led light bulb, 4w globe large screw vintage edison led bulbs</t>
+          <t>bulb warm yellliw pack 6</t>
         </is>
       </c>
       <c r="G126" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H126" t="b">
         <v>0</v>
@@ -9602,17 +9602,17 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>B09JM3PLLH</t>
+          <t>B0BLP1JSRK</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>LDSG125LOE274</t>
+          <t>LDMST64E278</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>B0DBTNQT8Z</t>
+          <t>B0D7HPWK2P</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -9622,11 +9622,11 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>large edison screw bulb warm white</t>
+          <t>squirrel cage vintage edison e27 screw bulb 8w clear</t>
         </is>
       </c>
       <c r="G127" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H127" t="b">
         <v>0</v>
@@ -9663,17 +9663,17 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>B09JM3PLLH</t>
+          <t>B0BLP1JSRK</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>LDSG125LOE274</t>
+          <t>LDMST64E278</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>B0DBTNQT8Z</t>
+          <t>B0D7HPWK2P</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -9683,14 +9683,14 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>light bulb with amber love</t>
+          <t>6 led e27 st64 8w 60 w dimmable warm white 2700k</t>
         </is>
       </c>
       <c r="G128" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H128" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I128" t="b">
         <v>0</v>
@@ -9702,7 +9702,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>backend</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -9724,17 +9724,17 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>B09JM3PLLH</t>
+          <t>B0BLP1JSRK</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>LDSG125LOE274</t>
+          <t>LDMST64E278</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>B0DBTNQT8Z</t>
+          <t>B0D7HPWK2P</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -9744,31 +9744,31 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>es love light bulb</t>
+          <t>vintage 60w es bulb pack not dimmable</t>
         </is>
       </c>
       <c r="G129" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H129" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I129" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>present</t>
+          <t>gap</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>pending_add</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -9805,11 +9805,11 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>e27 love light balb</t>
+          <t>large e27 vintage light bulbs</t>
         </is>
       </c>
       <c r="G130" t="n">
-        <v>2</v>
+        <v>150</v>
       </c>
       <c r="H130" t="b">
         <v>0</v>
@@ -9866,31 +9866,31 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>bulb writing</t>
+          <t>edison bulb</t>
         </is>
       </c>
       <c r="G131" t="n">
-        <v>1</v>
+        <v>133</v>
       </c>
       <c r="H131" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I131" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>gap</t>
+          <t>present</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>pending_add</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -9907,31 +9907,31 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>B0DCDSZ719</t>
+          <t>B09JM3PLLH</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>LDSG95DIE274</t>
+          <t>LDSG125LOE274</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>B0DCFP1CX8</t>
+          <t>B0DBTNQT8Z</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>sales_drop_3mo</t>
+          <t>zero_sales_6mo</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>vintage light bulb</t>
+          <t>love light bulb</t>
         </is>
       </c>
       <c r="G132" t="n">
-        <v>394</v>
+        <v>74</v>
       </c>
       <c r="H132" t="b">
         <v>1</v>
@@ -9968,31 +9968,31 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>B0DCDSZ719</t>
+          <t>B09JM3PLLH</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>LDSG95DIE274</t>
+          <t>LDSG125LOE274</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>B0DCFP1CX8</t>
+          <t>B0DBTNQT8Z</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>sales_drop_3mo</t>
+          <t>zero_sales_6mo</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>decorative light bulbs</t>
+          <t>e27 screw bulb decorative</t>
         </is>
       </c>
       <c r="G133" t="n">
-        <v>213</v>
+        <v>55</v>
       </c>
       <c r="H133" t="b">
         <v>1</v>
@@ -10029,34 +10029,34 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>B0DCDSZ719</t>
+          <t>B09JM3PLLH</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>LDSG95DIE274</t>
+          <t>LDSG125LOE274</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>B0DCFP1CX8</t>
+          <t>B0DBTNQT8Z</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>sales_drop_3mo</t>
+          <t>zero_sales_6mo</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>e27 vintage light bulbs</t>
+          <t>e27 large globe bulb</t>
         </is>
       </c>
       <c r="G134" t="n">
-        <v>177</v>
+        <v>50</v>
       </c>
       <c r="H134" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I134" t="b">
         <v>0</v>
@@ -10068,7 +10068,7 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>backend</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -10090,31 +10090,31 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>B0DCDSZ719</t>
+          <t>B09JM3PLLH</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>LDSG95DIE274</t>
+          <t>LDSG125LOE274</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>B0DCFP1CX8</t>
+          <t>B0DBTNQT8Z</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>sales_drop_3mo</t>
+          <t>zero_sales_6mo</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>e14 vintage bulb</t>
+          <t>extra large edison bulb</t>
         </is>
       </c>
       <c r="G135" t="n">
-        <v>132</v>
+        <v>40</v>
       </c>
       <c r="H135" t="b">
         <v>0</v>
@@ -10151,37 +10151,37 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>B0DCDSZ719</t>
+          <t>B09JM3PLLH</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>LDSG95DIE274</t>
+          <t>LDSG125LOE274</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>B0DCFP1CX8</t>
+          <t>B0DBTNQT8Z</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>sales_drop_3mo</t>
+          <t>zero_sales_6mo</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>fancy light bulbs</t>
+          <t>big bulb</t>
         </is>
       </c>
       <c r="G136" t="n">
-        <v>64</v>
+        <v>20</v>
       </c>
       <c r="H136" t="b">
         <v>0</v>
       </c>
       <c r="I136" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J136" t="inlineStr">
         <is>
@@ -10190,7 +10190,7 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>bullet</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -10212,51 +10212,51 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>B0DCDSZ719</t>
+          <t>B09JM3PLLH</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>LDSG95DIE274</t>
+          <t>LDSG125LOE274</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>B0DCFP1CX8</t>
+          <t>B0DBTNQT8Z</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>sales_drop_3mo</t>
+          <t>zero_sales_6mo</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>dimmable led vintage</t>
+          <t>e27 screw bulb spiral</t>
         </is>
       </c>
       <c r="G137" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H137" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I137" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>present</t>
+          <t>gap</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>pending_add</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
@@ -10273,31 +10273,31 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>B0DCDSZ719</t>
+          <t>B09JM3PLLH</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>LDSG95DIE274</t>
+          <t>LDSG125LOE274</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>B0DCFP1CX8</t>
+          <t>B0DBTNQT8Z</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>sales_drop_3mo</t>
+          <t>zero_sales_6mo</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>e14 2w diamond shaped bulb</t>
+          <t>warm white large screw light bulbs</t>
         </is>
       </c>
       <c r="G138" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H138" t="b">
         <v>0</v>
@@ -10334,51 +10334,51 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>B0DCDSZ719</t>
+          <t>B09JM3PLLH</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>LDSG95DIE274</t>
+          <t>LDSG125LOE274</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>B0DCFP1CX8</t>
+          <t>B0DBTNQT8Z</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>sales_drop_3mo</t>
+          <t>zero_sales_6mo</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>fancy lightbulbs</t>
+          <t>love bulb</t>
         </is>
       </c>
       <c r="G139" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H139" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I139" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>gap</t>
+          <t>present</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>pending_add</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
@@ -10395,51 +10395,51 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>B0DCDSZ719</t>
+          <t>B09JM3PLLH</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>LDSG95DIE274</t>
+          <t>LDSG125LOE274</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>B0DCFP1CX8</t>
+          <t>B0DBTNQT8Z</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>sales_drop_3mo</t>
+          <t>zero_sales_6mo</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>e17 warm light bulb</t>
+          <t>g125 led bulb</t>
         </is>
       </c>
       <c r="G140" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H140" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I140" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>gap</t>
+          <t>present</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>pending_add</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
@@ -10456,31 +10456,31 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>B0DCDSZ719</t>
+          <t>B09JM3PLLH</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>LDSG95DIE274</t>
+          <t>LDSG125LOE274</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>B0DCFP1CX8</t>
+          <t>B0DBTNQT8Z</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>sales_drop_3mo</t>
+          <t>zero_sales_6mo</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>decorative led bulb xxl</t>
+          <t>screw e27 led light bulb, 4w globe large screw vintage edison led bulbs</t>
         </is>
       </c>
       <c r="G141" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H141" t="b">
         <v>0</v>
@@ -10517,17 +10517,17 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>B0DCDSZ719</t>
+          <t>B09JM3PLLH</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>LDSG95DIE274</t>
+          <t>LDSG125LOE274</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>B0DR1XY3R6</t>
+          <t>B0DBTNQT8Z</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -10537,31 +10537,31 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>vintage light bulb</t>
+          <t>large edison screw bulb warm white</t>
         </is>
       </c>
       <c r="G142" t="n">
-        <v>394</v>
+        <v>5</v>
       </c>
       <c r="H142" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I142" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>present</t>
+          <t>gap</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>pending_add</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
@@ -10578,17 +10578,17 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>B0DCDSZ719</t>
+          <t>B09JM3PLLH</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>LDSG95DIE274</t>
+          <t>LDSG125LOE274</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>B0DR1XY3R6</t>
+          <t>B0DBTNQT8Z</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -10598,31 +10598,31 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>decorative light bulbs</t>
+          <t>light bulb with amber love</t>
         </is>
       </c>
       <c r="G143" t="n">
-        <v>213</v>
+        <v>5</v>
       </c>
       <c r="H143" t="b">
         <v>1</v>
       </c>
       <c r="I143" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>present</t>
+          <t>gap</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>backend</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>pending_add</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
@@ -10639,17 +10639,17 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>B0DCDSZ719</t>
+          <t>B09JM3PLLH</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>LDSG95DIE274</t>
+          <t>LDSG125LOE274</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>B0DR1XY3R6</t>
+          <t>B0DBTNQT8Z</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -10659,11 +10659,11 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>e27 vintage light bulbs</t>
+          <t>es love light bulb</t>
         </is>
       </c>
       <c r="G144" t="n">
-        <v>177</v>
+        <v>3</v>
       </c>
       <c r="H144" t="b">
         <v>1</v>
@@ -10700,17 +10700,17 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>B0DCDSZ719</t>
+          <t>B09JM3PLLH</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>LDSG95DIE274</t>
+          <t>LDSG125LOE274</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>B0DR1XY3R6</t>
+          <t>B0DBTNQT8Z</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -10720,11 +10720,11 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>e14 vintage bulb</t>
+          <t>e27 love light balb</t>
         </is>
       </c>
       <c r="G145" t="n">
-        <v>132</v>
+        <v>2</v>
       </c>
       <c r="H145" t="b">
         <v>0</v>
@@ -10761,17 +10761,17 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>B0DCDSZ719</t>
+          <t>B09JM3PLLH</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>LDSG95DIE274</t>
+          <t>LDSG125LOE274</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>B0DR1XY3R6</t>
+          <t>B0DBTNQT8Z</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -10781,31 +10781,31 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>fancy light bulbs</t>
+          <t>bulb writing</t>
         </is>
       </c>
       <c r="G146" t="n">
-        <v>64</v>
+        <v>1</v>
       </c>
       <c r="H146" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I146" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>present</t>
+          <t>gap</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>pending_add</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
@@ -10832,21 +10832,21 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>B0DR1XY3R6</t>
+          <t>B0DCFP1CX8</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>zero_sales_6mo</t>
+          <t>sales_drop_3mo</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>dimmable led vintage</t>
+          <t>vintage light bulb</t>
         </is>
       </c>
       <c r="G147" t="n">
-        <v>16</v>
+        <v>394</v>
       </c>
       <c r="H147" t="b">
         <v>1</v>
@@ -10893,24 +10893,24 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>B0DR1XY3R6</t>
+          <t>B0DCFP1CX8</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>zero_sales_6mo</t>
+          <t>sales_drop_3mo</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>e14 2w diamond shaped bulb</t>
+          <t>decorative light bulbs</t>
         </is>
       </c>
       <c r="G148" t="n">
-        <v>11</v>
+        <v>213</v>
       </c>
       <c r="H148" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I148" t="b">
         <v>0</v>
@@ -10922,7 +10922,7 @@
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>backend</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -10954,24 +10954,24 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>B0DR1XY3R6</t>
+          <t>B0DCFP1CX8</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>zero_sales_6mo</t>
+          <t>sales_drop_3mo</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>fancy lightbulbs</t>
+          <t>e27 vintage light bulbs</t>
         </is>
       </c>
       <c r="G149" t="n">
-        <v>10</v>
+        <v>177</v>
       </c>
       <c r="H149" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I149" t="b">
         <v>0</v>
@@ -10983,7 +10983,7 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>backend</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -11015,27 +11015,27 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>B0DR1XY3R6</t>
+          <t>B0DCFP1CX8</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>zero_sales_6mo</t>
+          <t>sales_drop_3mo</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>e17 warm light bulb</t>
+          <t>e14 vintage bulb</t>
         </is>
       </c>
       <c r="G150" t="n">
-        <v>4</v>
+        <v>132</v>
       </c>
       <c r="H150" t="b">
         <v>0</v>
       </c>
       <c r="I150" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J150" t="inlineStr">
         <is>
@@ -11044,7 +11044,7 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>bullet</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -11076,51 +11076,966 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
+          <t>B0DCFP1CX8</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>sales_drop_3mo</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>fancy light bulbs</t>
+        </is>
+      </c>
+      <c r="G151" t="n">
+        <v>64</v>
+      </c>
+      <c r="H151" t="b">
+        <v>0</v>
+      </c>
+      <c r="I151" t="b">
+        <v>0</v>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>backend_and_bullet</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>pending_add</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>ledsone_uk</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>B0DCDSZ719</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>LDSG95DIE274</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>B0DCFP1CX8</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>sales_drop_3mo</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>dimmable led vintage</t>
+        </is>
+      </c>
+      <c r="G152" t="n">
+        <v>16</v>
+      </c>
+      <c r="H152" t="b">
+        <v>1</v>
+      </c>
+      <c r="I152" t="b">
+        <v>1</v>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>present</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>ledsone_uk</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>B0DCDSZ719</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>LDSG95DIE274</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>B0DCFP1CX8</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>sales_drop_3mo</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>e14 2w diamond shaped bulb</t>
+        </is>
+      </c>
+      <c r="G153" t="n">
+        <v>11</v>
+      </c>
+      <c r="H153" t="b">
+        <v>0</v>
+      </c>
+      <c r="I153" t="b">
+        <v>0</v>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>backend_and_bullet</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>pending_add</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>ledsone_uk</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>B0DCDSZ719</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>LDSG95DIE274</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>B0DCFP1CX8</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>sales_drop_3mo</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>fancy lightbulbs</t>
+        </is>
+      </c>
+      <c r="G154" t="n">
+        <v>10</v>
+      </c>
+      <c r="H154" t="b">
+        <v>0</v>
+      </c>
+      <c r="I154" t="b">
+        <v>0</v>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>backend_and_bullet</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>pending_add</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>ledsone_uk</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>B0DCDSZ719</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>LDSG95DIE274</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>B0DCFP1CX8</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>sales_drop_3mo</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>e17 warm light bulb</t>
+        </is>
+      </c>
+      <c r="G155" t="n">
+        <v>4</v>
+      </c>
+      <c r="H155" t="b">
+        <v>0</v>
+      </c>
+      <c r="I155" t="b">
+        <v>0</v>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>backend_and_bullet</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>pending_add</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>ledsone_uk</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>B0DCDSZ719</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>LDSG95DIE274</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>B0DCFP1CX8</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>sales_drop_3mo</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>decorative led bulb xxl</t>
+        </is>
+      </c>
+      <c r="G156" t="n">
+        <v>3</v>
+      </c>
+      <c r="H156" t="b">
+        <v>0</v>
+      </c>
+      <c r="I156" t="b">
+        <v>0</v>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>backend_and_bullet</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>pending_add</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>ledsone_uk</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>B0DCDSZ719</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>LDSG95DIE274</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
           <t>B0DR1XY3R6</t>
         </is>
       </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>zero_sales_6mo</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>zero_sales_6mo</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>vintage light bulb</t>
+        </is>
+      </c>
+      <c r="G157" t="n">
+        <v>394</v>
+      </c>
+      <c r="H157" t="b">
+        <v>1</v>
+      </c>
+      <c r="I157" t="b">
+        <v>1</v>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>present</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>ledsone_uk</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>B0DCDSZ719</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>LDSG95DIE274</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>B0DR1XY3R6</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>zero_sales_6mo</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>decorative light bulbs</t>
+        </is>
+      </c>
+      <c r="G158" t="n">
+        <v>213</v>
+      </c>
+      <c r="H158" t="b">
+        <v>1</v>
+      </c>
+      <c r="I158" t="b">
+        <v>1</v>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>present</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>ledsone_uk</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>B0DCDSZ719</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>LDSG95DIE274</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>B0DR1XY3R6</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>zero_sales_6mo</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>e27 vintage light bulbs</t>
+        </is>
+      </c>
+      <c r="G159" t="n">
+        <v>177</v>
+      </c>
+      <c r="H159" t="b">
+        <v>1</v>
+      </c>
+      <c r="I159" t="b">
+        <v>1</v>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>present</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>ledsone_uk</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>B0DCDSZ719</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>LDSG95DIE274</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>B0DR1XY3R6</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>zero_sales_6mo</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>e14 vintage bulb</t>
+        </is>
+      </c>
+      <c r="G160" t="n">
+        <v>132</v>
+      </c>
+      <c r="H160" t="b">
+        <v>0</v>
+      </c>
+      <c r="I160" t="b">
+        <v>0</v>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>backend_and_bullet</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>pending_add</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>ledsone_uk</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>B0DCDSZ719</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>LDSG95DIE274</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>B0DR1XY3R6</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>zero_sales_6mo</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>fancy light bulbs</t>
+        </is>
+      </c>
+      <c r="G161" t="n">
+        <v>64</v>
+      </c>
+      <c r="H161" t="b">
+        <v>1</v>
+      </c>
+      <c r="I161" t="b">
+        <v>1</v>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>present</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>ledsone_uk</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>B0DCDSZ719</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>LDSG95DIE274</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>B0DR1XY3R6</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>zero_sales_6mo</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>dimmable led vintage</t>
+        </is>
+      </c>
+      <c r="G162" t="n">
+        <v>16</v>
+      </c>
+      <c r="H162" t="b">
+        <v>1</v>
+      </c>
+      <c r="I162" t="b">
+        <v>1</v>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>present</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>ledsone_uk</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>B0DCDSZ719</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>LDSG95DIE274</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>B0DR1XY3R6</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>zero_sales_6mo</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>e14 2w diamond shaped bulb</t>
+        </is>
+      </c>
+      <c r="G163" t="n">
+        <v>11</v>
+      </c>
+      <c r="H163" t="b">
+        <v>0</v>
+      </c>
+      <c r="I163" t="b">
+        <v>0</v>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>backend_and_bullet</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>pending_add</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>ledsone_uk</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>B0DCDSZ719</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>LDSG95DIE274</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>B0DR1XY3R6</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>zero_sales_6mo</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>fancy lightbulbs</t>
+        </is>
+      </c>
+      <c r="G164" t="n">
+        <v>10</v>
+      </c>
+      <c r="H164" t="b">
+        <v>0</v>
+      </c>
+      <c r="I164" t="b">
+        <v>0</v>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>backend_and_bullet</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>pending_add</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>ledsone_uk</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>B0DCDSZ719</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>LDSG95DIE274</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>B0DR1XY3R6</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>zero_sales_6mo</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>e17 warm light bulb</t>
+        </is>
+      </c>
+      <c r="G165" t="n">
+        <v>4</v>
+      </c>
+      <c r="H165" t="b">
+        <v>0</v>
+      </c>
+      <c r="I165" t="b">
+        <v>1</v>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>bullet</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>pending_add</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>ledsone_uk</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>B0DCDSZ719</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>LDSG95DIE274</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>B0DR1XY3R6</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>zero_sales_6mo</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
         <is>
           <t>decorative led bulb xxl</t>
         </is>
       </c>
-      <c r="G151" t="n">
+      <c r="G166" t="n">
         <v>3</v>
       </c>
-      <c r="H151" t="b">
-        <v>0</v>
-      </c>
-      <c r="I151" t="b">
-        <v>0</v>
-      </c>
-      <c r="J151" t="inlineStr">
-        <is>
-          <t>gap</t>
-        </is>
-      </c>
-      <c r="K151" t="inlineStr">
+      <c r="H166" t="b">
+        <v>0</v>
+      </c>
+      <c r="I166" t="b">
+        <v>0</v>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
         <is>
           <t>backend_and_bullet</t>
         </is>
       </c>
-      <c r="L151" t="inlineStr">
-        <is>
-          <t>pending_add</t>
-        </is>
-      </c>
-      <c r="M151" t="inlineStr">
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>pending_add</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M151"/>
+  <autoFilter ref="A1:M166"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11131,7 +12046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11241,15 +12156,19 @@
           <t>zero_sales_6mo</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>7</v>
-      </c>
-      <c r="H2" t="n">
-        <v>3</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>7W</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>3W</t>
+        </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>same base SKU but the listings state different wattage (7W vs 3W) - the stored SKU looks wrong</t>
+          <t>same base SKU but the listings share no wattage (7W vs 3W) - the stored SKU looks wrong</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -11299,15 +12218,19 @@
           <t>zero_sales_6mo</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>8</v>
-      </c>
-      <c r="H3" t="n">
-        <v>4</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>8W</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>4W</t>
+        </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>same base SKU but the listings state different wattage (8W vs 4W) - the stored SKU looks wrong</t>
+          <t>same base SKU but the listings share no wattage (8W vs 4W) - the stored SKU looks wrong</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -11326,66 +12249,8 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>ledsone_uk</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>B0BLP1JSRK</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>LDMST64E278</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>B0D7HPWK2P</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>LDMST64E2786PK k</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>zero_sales_6mo</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>8</v>
-      </c>
-      <c r="H4" t="n">
-        <v>4</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>same base SKU but the listings state different wattage (8W vs 4W) - the stored SKU looks wrong</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Check and correct the SKU before using this pair</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>LEDSone LED Edison Bulb, Vintage Light Bulb,4W/6W/8W E27 2700K Warm white ST64 LED Bulbs, Led Filament Bulbs, Dimmable Antique Style Retro Amber Glass Screw Lamp 220V (6 Pack, 8W)</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:L4"/>
+  <autoFilter ref="A1:L3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/development/abiraj_mini_aios_workbench/projects/PRJ-2026-026_amazon-keyword-gap-sync/evidence/final_outputs/REQ-30_amazon-keyword-gap-sync/REQ-30-D02_keyword_gap_report.xlsx
+++ b/development/abiraj_mini_aios_workbench/projects/PRJ-2026-026_amazon-keyword-gap-sync/evidence/final_outputs/REQ-30_amazon-keyword-gap-sync/REQ-30-D02_keyword_gap_report.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -492,7 +492,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-19T12:26:43</t>
+          <t>2026-08-19T13:42:26</t>
         </is>
       </c>
     </row>
@@ -600,89 +600,113 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>top 50 by search volume, zero-conversion terms dropped (source Step 6)</t>
+          <t>top 50 by search volume PER MONTH, zero-conversion terms dropped (source Step 6)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>SCOPE BOUNDARY</t>
+          <t>Months kept separate</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>This system NEVER writes to Amazon. Section 2.7's automatic SP-API push is out of workbench scope. add_target is a recommendation; a person applies it.</t>
+          <t>Source Step 4: the last 3 months are checked one month at a time, never combined. Each weekly row is assigned to the month containing its start_date. Phase 2 audits the de-duplicated union of the confirmed terms across those months.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Deviation from source</t>
+          <t>Rate denominators</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Zero-sales is anchored on the product catalogue, not the sales report: that report only lists an ASIN on days it had traffic, so 27% of ASINs — the deadest ones — never appear in it.</t>
+          <t>Verified against Amazon's own stored columns: asin_share = ASIN impressions / total query impressions · click_rate = total clicks / SEARCH VOLUME (not impressions) · asin_click_share = ASIN clicks / total clicks. Recomputed from summed numerator and denominator, never averaged across weeks.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>QA (source 2.10)</t>
+          <t>SCOPE BOUNDARY</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>1_account_separation=PASS; 2_sku_mismatch_never_paired=PASS; 3_one_place_is_enough=PASS; 4_dual_method_independent=PASS; 5_directional_add_logic=PASS; 6_zero_manual_lookup=PASS; 7_monthly_cadence=PASS</t>
+          <t>This system NEVER writes to Amazon. Section 2.7's automatic SP-API push is out of workbench scope. add_target is a recommendation; a person applies it.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Deviation from source</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>DRAFT — not validated, not published, not automated. Business confirmation from Thuwaraga still outstanding; rules confirmed by Abiraj 2026-08-19.</t>
+          <t>Zero-sales is anchored on the product catalogue, not the sales report: that report only lists an ASIN on days it had traffic, so 27% of ASINs — the deadest ones — never appear in it.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Part A</t>
+          <t>QA (source 2.10)</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>22 listings with NO CONTENT — empty backend keyword field and/or no bullet points. Every keyword would show as 'missing' because there is nothing to search. These need a rewrite, not keyword edits (rule Q12).</t>
+          <t>1_account_separation=PASS; 2_sku_mismatch_never_paired=PASS; 3_one_place_is_enough=PASS; 4_dual_method_independent=PASS; 5_directional_add_logic=PASS; 6_zero_manual_lookup=PASS; 7_monthly_cadence=PASS</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Part C</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>3 pairs REJECTED — same base SKU but the two listings state different wattage, so the stored SKU is wrong. Not keyword-checked; the SKU needs correcting first.</t>
+          <t>DRAFT — not validated, not published, not automated. Business confirmation from Thuwaraga still outstanding; rules confirmed by Abiraj 2026-08-19.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>Part A</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>22 listings with NO CONTENT — empty backend keyword field and/or no bullet points. Every keyword would show as 'missing' because there is nothing to search. These need a rewrite, not keyword edits (rule Q12).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Part C</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>3 pairs REJECTED — same base SKU but the two listings state different wattage, so the stored SKU is wrong. Not keyword-checked; the SKU needs correcting first.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
           <t>Part B</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>275 keyword rows across listings that DO have content — 204 real, actionable gaps.</t>
         </is>
@@ -2290,31 +2314,31 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>g125 bulb</t>
+          <t>e27 low watt bulb</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="H5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>present</t>
+          <t>gap</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>pending_add</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2351,31 +2375,31 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>e27 low watt bulb</t>
+          <t>g125 bulb</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="H6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>gap</t>
+          <t>present</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>pending_add</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2839,7 +2863,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>g125 e27 led bulb</t>
+          <t>edison e27 led g125</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2900,7 +2924,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>bulbs g125</t>
+          <t>g125 e27 led bulb</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2961,7 +2985,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>edison e27 led g125</t>
+          <t>bulbs g125</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3022,14 +3046,14 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>vintage led e27 bulb, edison g125</t>
+          <t>8w gls large screw e27</t>
         </is>
       </c>
       <c r="G17" t="n">
         <v>2</v>
       </c>
       <c r="H17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I17" t="b">
         <v>0</v>
@@ -3041,7 +3065,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>backend</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -3144,31 +3168,31 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>large glibe filament bulb</t>
+          <t>large edison screw g125 bulb</t>
         </is>
       </c>
       <c r="G19" t="n">
         <v>2</v>
       </c>
       <c r="H19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>gap</t>
+          <t>present</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>pending_add</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -3205,7 +3229,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>edison g125</t>
+          <t>vintage led e27 bulb, edison g125</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3215,21 +3239,21 @@
         <v>1</v>
       </c>
       <c r="I20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>present</t>
+          <t>gap</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>backend</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>pending_add</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -3266,7 +3290,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>8w gls large screw e27</t>
+          <t>large glibe filament bulb</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3327,7 +3351,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>large edison screw g125 bulb</t>
+          <t>edison g125</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3571,31 +3595,31 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>g125 bulb</t>
+          <t>e27 low watt bulb</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="H26" t="b">
         <v>1</v>
       </c>
       <c r="I26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>present</t>
+          <t>gap</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>backend</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>pending_add</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -3632,31 +3656,31 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>e27 low watt bulb</t>
+          <t>g125 bulb</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="H27" t="b">
         <v>1</v>
       </c>
       <c r="I27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>gap</t>
+          <t>present</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>backend</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>pending_add</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -4120,7 +4144,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>g125 e27 led bulb</t>
+          <t>edison e27 led g125</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4181,7 +4205,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>bulbs g125</t>
+          <t>g125 e27 led bulb</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4242,7 +4266,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>edison e27 led g125</t>
+          <t>bulbs g125</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4303,31 +4327,31 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>vintage led e27 bulb, edison g125</t>
+          <t>8w gls large screw e27</t>
         </is>
       </c>
       <c r="G38" t="n">
         <v>2</v>
       </c>
       <c r="H38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>present</t>
+          <t>gap</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>pending_add</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -4425,7 +4449,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>large glibe filament bulb</t>
+          <t>large edison screw g125 bulb</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -4486,7 +4510,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>edison g125</t>
+          <t>vintage led e27 bulb, edison g125</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -4547,7 +4571,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>8w gls large screw e27</t>
+          <t>large glibe filament bulb</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -4608,31 +4632,31 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>large edison screw g125 bulb</t>
+          <t>edison g125</t>
         </is>
       </c>
       <c r="G43" t="n">
         <v>2</v>
       </c>
       <c r="H43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>gap</t>
+          <t>present</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>pending_add</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -5035,7 +5059,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>dc voltage vintage amber led bulb e27 edison screw st64 4w dimmable,</t>
+          <t>outdoor bulb for pendant light</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -5096,7 +5120,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>outdoor bulb for pendant light</t>
+          <t>dc voltage vintage amber led bulb e27 edison screw st64 4w dimmable,</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -5279,7 +5303,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>dc voltage vintage amber led bulb e27 edison screw st64 4w dimmable,</t>
+          <t>outdoor bulb for pendant light</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -5340,7 +5364,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>outdoor bulb for pendant light</t>
+          <t>dc voltage vintage amber led bulb e27 edison screw st64 4w dimmable,</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -5523,7 +5547,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>dc voltage vintage amber led bulb e27 edison screw st64 4w dimmable,</t>
+          <t>outdoor bulb for pendant light</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -5584,7 +5608,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>outdoor bulb for pendant light</t>
+          <t>dc voltage vintage amber led bulb e27 edison screw st64 4w dimmable,</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -5767,14 +5791,14 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>dc voltage vintage amber led bulb e27 edison screw st64 4w dimmable,</t>
+          <t>outdoor bulb for pendant light</t>
         </is>
       </c>
       <c r="G62" t="n">
         <v>1</v>
       </c>
       <c r="H62" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I62" t="b">
         <v>0</v>
@@ -5786,7 +5810,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>backend</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -5828,14 +5852,14 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>outdoor bulb for pendant light</t>
+          <t>dc voltage vintage amber led bulb e27 edison screw st64 4w dimmable,</t>
         </is>
       </c>
       <c r="G63" t="n">
         <v>1</v>
       </c>
       <c r="H63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I63" t="b">
         <v>0</v>
@@ -5847,7 +5871,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>backend</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -6011,14 +6035,14 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>dc voltage vintage amber led bulb e27 edison screw st64 4w dimmable,</t>
+          <t>outdoor bulb for pendant light</t>
         </is>
       </c>
       <c r="G66" t="n">
         <v>1</v>
       </c>
       <c r="H66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I66" t="b">
         <v>0</v>
@@ -6030,7 +6054,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>backend</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -6072,14 +6096,14 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>outdoor bulb for pendant light</t>
+          <t>dc voltage vintage amber led bulb e27 edison screw st64 4w dimmable,</t>
         </is>
       </c>
       <c r="G67" t="n">
         <v>1</v>
       </c>
       <c r="H67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I67" t="b">
         <v>0</v>
@@ -6091,7 +6115,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>backend</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -6255,7 +6279,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>dc voltage vintage amber led bulb e27 edison screw st64 4w dimmable,</t>
+          <t>outdoor bulb for pendant light</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -6316,7 +6340,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>outdoor bulb for pendant light</t>
+          <t>dc voltage vintage amber led bulb e27 edison screw st64 4w dimmable,</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -7475,7 +7499,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>es 8w led bulb</t>
+          <t>g125 e27</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -7485,21 +7509,21 @@
         <v>1</v>
       </c>
       <c r="I90" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>gap</t>
+          <t>present</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>backend</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>pending_add</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -7536,7 +7560,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>g125 e27</t>
+          <t>es 8w led bulb</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -7546,21 +7570,21 @@
         <v>1</v>
       </c>
       <c r="I91" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>present</t>
+          <t>gap</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>backend</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>pending_add</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -7719,14 +7743,14 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>e27 large bulb dimmable</t>
+          <t>led bulb light large 120 mm x 160mm</t>
         </is>
       </c>
       <c r="G94" t="n">
         <v>8</v>
       </c>
       <c r="H94" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I94" t="b">
         <v>0</v>
@@ -7738,7 +7762,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>backend</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -7780,14 +7804,14 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>led bulb light large 120 mm x 160mm</t>
+          <t>e27 large bulb dimmable</t>
         </is>
       </c>
       <c r="G95" t="n">
         <v>8</v>
       </c>
       <c r="H95" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I95" t="b">
         <v>0</v>
@@ -7799,7 +7823,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>backend</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -8024,14 +8048,14 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>dimmable retro large 8w</t>
+          <t>vintage led e27 g125 8w dimmable, amber glass, 2700k, 806 lumen</t>
         </is>
       </c>
       <c r="G99" t="n">
         <v>5</v>
       </c>
       <c r="H99" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I99" t="b">
         <v>0</v>
@@ -8043,7 +8067,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>backend</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -8085,14 +8109,14 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>vintage led e27 g125 8w dimmable, amber glass, 2700k, 806 lumen</t>
+          <t>dimmable retro large 8w</t>
         </is>
       </c>
       <c r="G100" t="n">
         <v>5</v>
       </c>
       <c r="H100" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I100" t="b">
         <v>0</v>
@@ -8104,7 +8128,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>backend</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -8268,31 +8292,31 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>edison g125</t>
+          <t>g125 led filament bulb smoked e27 warm</t>
         </is>
       </c>
       <c r="G103" t="n">
         <v>2</v>
       </c>
       <c r="H103" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I103" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>present</t>
+          <t>gap</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>pending_add</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -8329,7 +8353,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>e27 g125 vintage</t>
+          <t>edison g125</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -8390,31 +8414,31 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>g125 led filament bulb smoked e27 warm</t>
+          <t>e27 g125 vintage</t>
         </is>
       </c>
       <c r="G105" t="n">
         <v>2</v>
       </c>
       <c r="H105" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I105" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>gap</t>
+          <t>present</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>pending_add</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -8451,31 +8475,31 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>led bulb dimmable filament amber e27 8w</t>
+          <t>diall g125 e27 5.5w 470lm 330° amber globe warm white led filament light bulb</t>
         </is>
       </c>
       <c r="G106" t="n">
         <v>1</v>
       </c>
       <c r="H106" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I106" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>present</t>
+          <t>gap</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>pending_add</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -8512,31 +8536,31 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>diall g125 e27 5.5w 470lm 330° amber globe warm white led filament light bulb</t>
+          <t>led bulb dimmable filament amber e27 8w</t>
         </is>
       </c>
       <c r="G107" t="n">
         <v>1</v>
       </c>
       <c r="H107" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I107" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>gap</t>
+          <t>present</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>pending_add</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -9061,7 +9085,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>es 8w led bulb</t>
+          <t>g125 e27</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -9071,21 +9095,21 @@
         <v>1</v>
       </c>
       <c r="I116" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>gap</t>
+          <t>present</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>backend</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>pending_add</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
@@ -9122,7 +9146,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>g125 e27</t>
+          <t>es 8w led bulb</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -9132,21 +9156,21 @@
         <v>1</v>
       </c>
       <c r="I117" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>present</t>
+          <t>gap</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>backend</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>pending_add</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
@@ -9305,7 +9329,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>e27 large bulb dimmable</t>
+          <t>led bulb light large 120 mm x 160mm</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -9366,7 +9390,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>led bulb light large 120 mm x 160mm</t>
+          <t>e27 large bulb dimmable</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -9610,14 +9634,14 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>dimmable retro large 8w</t>
+          <t>vintage led e27 g125 8w dimmable, amber glass, 2700k, 806 lumen</t>
         </is>
       </c>
       <c r="G125" t="n">
         <v>5</v>
       </c>
       <c r="H125" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I125" t="b">
         <v>0</v>
@@ -9629,7 +9653,7 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>backend</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -9671,14 +9695,14 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>vintage led e27 g125 8w dimmable, amber glass, 2700k, 806 lumen</t>
+          <t>dimmable retro large 8w</t>
         </is>
       </c>
       <c r="G126" t="n">
         <v>5</v>
       </c>
       <c r="H126" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I126" t="b">
         <v>0</v>
@@ -9690,7 +9714,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>backend</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -9854,31 +9878,31 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>edison g125</t>
+          <t>g125 led filament bulb smoked e27 warm</t>
         </is>
       </c>
       <c r="G129" t="n">
         <v>2</v>
       </c>
       <c r="H129" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I129" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>present</t>
+          <t>gap</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>pending_add</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -9915,7 +9939,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>e27 g125 vintage</t>
+          <t>edison g125</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -9976,31 +10000,31 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>g125 led filament bulb smoked e27 warm</t>
+          <t>e27 g125 vintage</t>
         </is>
       </c>
       <c r="G131" t="n">
         <v>2</v>
       </c>
       <c r="H131" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I131" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>gap</t>
+          <t>present</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>pending_add</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -10037,14 +10061,14 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>led bulb dimmable filament amber e27 8w</t>
+          <t>diall g125 e27 5.5w 470lm 330° amber globe warm white led filament light bulb</t>
         </is>
       </c>
       <c r="G132" t="n">
         <v>1</v>
       </c>
       <c r="H132" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I132" t="b">
         <v>0</v>
@@ -10056,7 +10080,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>backend</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -10098,14 +10122,14 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>diall g125 e27 5.5w 470lm 330° amber globe warm white led filament light bulb</t>
+          <t>led bulb dimmable filament amber e27 8w</t>
         </is>
       </c>
       <c r="G133" t="n">
         <v>1</v>
       </c>
       <c r="H133" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I133" t="b">
         <v>0</v>
@@ -10117,7 +10141,7 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>backend</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -10163,7 +10187,7 @@
         </is>
       </c>
       <c r="G134" t="n">
-        <v>11481</v>
+        <v>6135</v>
       </c>
       <c r="H134" t="b">
         <v>1</v>
@@ -10403,17 +10427,17 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>g95 bulbs</t>
+          <t>4000k e27 bulb</t>
         </is>
       </c>
       <c r="G138" t="n">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="H138" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I138" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J138" t="inlineStr">
         <is>
@@ -10422,7 +10446,7 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>backend</t>
+          <t>bullet</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -10464,17 +10488,17 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>4000k e27 bulb</t>
+          <t>g95 bulbs</t>
         </is>
       </c>
       <c r="G139" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H139" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I139" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J139" t="inlineStr">
         <is>
@@ -10483,7 +10507,7 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>bullet</t>
+          <t>backend</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -10586,7 +10610,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>sklum e27 g95</t>
+          <t>pack of 6 e27 globe bulbs</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -10647,31 +10671,31 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>pack of 6 e27 globe bulbs</t>
+          <t>e27 globe dimmable led</t>
         </is>
       </c>
       <c r="G142" t="n">
         <v>4</v>
       </c>
       <c r="H142" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I142" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>gap</t>
+          <t>present</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>pending_add</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
@@ -10708,31 +10732,31 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>e27 globe dimmable led</t>
+          <t>sklum e27 g95</t>
         </is>
       </c>
       <c r="G143" t="n">
         <v>4</v>
       </c>
       <c r="H143" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I143" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>present</t>
+          <t>gap</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>pending_add</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
@@ -10895,7 +10919,7 @@
         </is>
       </c>
       <c r="G146" t="n">
-        <v>11481</v>
+        <v>6135</v>
       </c>
       <c r="H146" t="b">
         <v>1</v>
@@ -11135,31 +11159,31 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>g95 bulbs</t>
+          <t>4000k e27 bulb</t>
         </is>
       </c>
       <c r="G150" t="n">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="H150" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I150" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>present</t>
+          <t>gap</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>pending_add</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -11196,31 +11220,31 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>4000k e27 bulb</t>
+          <t>g95 bulbs</t>
         </is>
       </c>
       <c r="G151" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H151" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I151" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>gap</t>
+          <t>present</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>pending_add</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -11318,7 +11342,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>sklum e27 g95</t>
+          <t>pack of 6 e27 globe bulbs</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -11379,31 +11403,31 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>pack of 6 e27 globe bulbs</t>
+          <t>e27 globe dimmable led</t>
         </is>
       </c>
       <c r="G154" t="n">
         <v>4</v>
       </c>
       <c r="H154" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I154" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>gap</t>
+          <t>present</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>pending_add</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
@@ -11440,31 +11464,31 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>e27 globe dimmable led</t>
+          <t>sklum e27 g95</t>
         </is>
       </c>
       <c r="G155" t="n">
         <v>4</v>
       </c>
       <c r="H155" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I155" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>present</t>
+          <t>gap</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>pending_add</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
@@ -11684,14 +11708,14 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>e27 es dimmable bulb 8w squirrel cage</t>
+          <t>ledsone pack 3 | vintage led edison e27 light bulb, 8w (equivalent 60w) st64 dimmable 2700k warm white amber glass screw 806 lumens| energy saving bulb for squirrel cage lamp 220v [energy class a]</t>
         </is>
       </c>
       <c r="G159" t="n">
         <v>4</v>
       </c>
       <c r="H159" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I159" t="b">
         <v>0</v>
@@ -11703,7 +11727,7 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>backend</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
@@ -11745,31 +11769,31 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>bravo lighting bulbs 8w dimmable</t>
+          <t>e27 8w vintage light bulbs</t>
         </is>
       </c>
       <c r="G160" t="n">
         <v>4</v>
       </c>
       <c r="H160" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I160" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>gap</t>
+          <t>present</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>pending_add</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
@@ -11806,14 +11830,14 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>ledsone pack 3 | vintage led edison e27 light bulb, 8w (equivalent 60w) st64 dimmable 2700k warm white amber glass screw 806 lumens| energy saving bulb for squirrel cage lamp 220v [energy class a]</t>
+          <t>e27 es dimmable bulb 8w squirrel cage</t>
         </is>
       </c>
       <c r="G161" t="n">
         <v>4</v>
       </c>
       <c r="H161" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I161" t="b">
         <v>0</v>
@@ -11825,7 +11849,7 @@
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>backend</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
@@ -11867,31 +11891,31 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>e27 8w vintage light bulbs</t>
+          <t>bravo lighting bulbs 8w dimmable</t>
         </is>
       </c>
       <c r="G162" t="n">
         <v>4</v>
       </c>
       <c r="H162" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I162" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>present</t>
+          <t>gap</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>pending_add</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
@@ -12050,7 +12074,7 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>e27 8w 2200k 720lumen</t>
+          <t>e27 dimmable bulb pack of six</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -12111,7 +12135,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>e27 dimmable bulb pack of six</t>
+          <t>light bulbs screv wintage 8w</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -12172,7 +12196,7 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>light bulbs screv wintage 8w</t>
+          <t>e27 8w 2200k 720lumen</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -12233,31 +12257,31 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>e27 2700k dimmable 8w amber 6 pack</t>
+          <t>squirrel cage vintage edison e27 screw bulb 8w clear</t>
         </is>
       </c>
       <c r="G168" t="n">
         <v>1</v>
       </c>
       <c r="H168" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I168" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>present</t>
+          <t>gap</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>pending_add</t>
         </is>
       </c>
       <c r="M168" t="inlineStr">
@@ -12294,14 +12318,14 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>bulb warm yellliw pack 6</t>
+          <t>vintage 60w es bulb pack not dimmable</t>
         </is>
       </c>
       <c r="G169" t="n">
         <v>1</v>
       </c>
       <c r="H169" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I169" t="b">
         <v>0</v>
@@ -12313,7 +12337,7 @@
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>backend</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
@@ -12355,31 +12379,31 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>squirrel cage vintage edison e27 screw bulb 8w clear</t>
+          <t>6 led e27 st64 8w 60 w dimmable warm white 2700k</t>
         </is>
       </c>
       <c r="G170" t="n">
         <v>1</v>
       </c>
       <c r="H170" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I170" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>gap</t>
+          <t>present</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>pending_add</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
@@ -12416,7 +12440,7 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>6 led e27 st64 8w 60 w dimmable warm white 2700k</t>
+          <t>e27 2700k dimmable 8w amber 6 pack</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -12477,14 +12501,14 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>vintage 60w es bulb pack not dimmable</t>
+          <t>bulb warm yellliw pack 6</t>
         </is>
       </c>
       <c r="G172" t="n">
         <v>1</v>
       </c>
       <c r="H172" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I172" t="b">
         <v>0</v>
@@ -12496,7 +12520,7 @@
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>backend</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
@@ -12599,7 +12623,7 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>e27 es dimmable bulb 8w squirrel cage</t>
+          <t>ledsone pack 3 | vintage led edison e27 light bulb, 8w (equivalent 60w) st64 dimmable 2700k warm white amber glass screw 806 lumens| energy saving bulb for squirrel cage lamp 220v [energy class a]</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -12660,14 +12684,14 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>bravo lighting bulbs 8w dimmable</t>
+          <t>e27 8w vintage light bulbs</t>
         </is>
       </c>
       <c r="G175" t="n">
         <v>4</v>
       </c>
       <c r="H175" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I175" t="b">
         <v>0</v>
@@ -12679,7 +12703,7 @@
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>backend</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
@@ -12721,7 +12745,7 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>ledsone pack 3 | vintage led edison e27 light bulb, 8w (equivalent 60w) st64 dimmable 2700k warm white amber glass screw 806 lumens| energy saving bulb for squirrel cage lamp 220v [energy class a]</t>
+          <t>e27 es dimmable bulb 8w squirrel cage</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -12782,14 +12806,14 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>e27 8w vintage light bulbs</t>
+          <t>bravo lighting bulbs 8w dimmable</t>
         </is>
       </c>
       <c r="G177" t="n">
         <v>4</v>
       </c>
       <c r="H177" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I177" t="b">
         <v>0</v>
@@ -12801,7 +12825,7 @@
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>backend</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
@@ -12965,7 +12989,7 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>e27 8w 2200k 720lumen</t>
+          <t>e27 dimmable bulb pack of six</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -13026,7 +13050,7 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>e27 dimmable bulb pack of six</t>
+          <t>light bulbs screv wintage 8w</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -13087,7 +13111,7 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>light bulbs screv wintage 8w</t>
+          <t>e27 8w 2200k 720lumen</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -13148,14 +13172,14 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>e27 2700k dimmable 8w amber 6 pack</t>
+          <t>squirrel cage vintage edison e27 screw bulb 8w clear</t>
         </is>
       </c>
       <c r="G183" t="n">
         <v>1</v>
       </c>
       <c r="H183" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I183" t="b">
         <v>0</v>
@@ -13167,7 +13191,7 @@
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>backend</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
@@ -13209,7 +13233,7 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>bulb warm yellliw pack 6</t>
+          <t>vintage 60w es bulb pack not dimmable</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -13270,14 +13294,14 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>squirrel cage vintage edison e27 screw bulb 8w clear</t>
+          <t>6 led e27 st64 8w 60 w dimmable warm white 2700k</t>
         </is>
       </c>
       <c r="G185" t="n">
         <v>1</v>
       </c>
       <c r="H185" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I185" t="b">
         <v>0</v>
@@ -13289,7 +13313,7 @@
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>backend</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
@@ -13331,7 +13355,7 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>6 led e27 st64 8w 60 w dimmable warm white 2700k</t>
+          <t>e27 2700k dimmable 8w amber 6 pack</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -13392,7 +13416,7 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>vintage 60w es bulb pack not dimmable</t>
+          <t>bulb warm yellliw pack 6</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -13514,7 +13538,7 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>e27 es dimmable bulb 8w squirrel cage</t>
+          <t>ledsone pack 3 | vintage led edison e27 light bulb, 8w (equivalent 60w) st64 dimmable 2700k warm white amber glass screw 806 lumens| energy saving bulb for squirrel cage lamp 220v [energy class a]</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -13575,14 +13599,14 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>bravo lighting bulbs 8w dimmable</t>
+          <t>e27 8w vintage light bulbs</t>
         </is>
       </c>
       <c r="G190" t="n">
         <v>4</v>
       </c>
       <c r="H190" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I190" t="b">
         <v>0</v>
@@ -13594,7 +13618,7 @@
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>backend</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
@@ -13636,7 +13660,7 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>ledsone pack 3 | vintage led edison e27 light bulb, 8w (equivalent 60w) st64 dimmable 2700k warm white amber glass screw 806 lumens| energy saving bulb for squirrel cage lamp 220v [energy class a]</t>
+          <t>e27 es dimmable bulb 8w squirrel cage</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -13697,14 +13721,14 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>e27 8w vintage light bulbs</t>
+          <t>bravo lighting bulbs 8w dimmable</t>
         </is>
       </c>
       <c r="G192" t="n">
         <v>4</v>
       </c>
       <c r="H192" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I192" t="b">
         <v>0</v>
@@ -13716,7 +13740,7 @@
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>backend</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
@@ -13880,7 +13904,7 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>e27 8w 2200k 720lumen</t>
+          <t>e27 dimmable bulb pack of six</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -13941,7 +13965,7 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>e27 dimmable bulb pack of six</t>
+          <t>light bulbs screv wintage 8w</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -14002,7 +14026,7 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>light bulbs screv wintage 8w</t>
+          <t>e27 8w 2200k 720lumen</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -14063,14 +14087,14 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>e27 2700k dimmable 8w amber 6 pack</t>
+          <t>squirrel cage vintage edison e27 screw bulb 8w clear</t>
         </is>
       </c>
       <c r="G198" t="n">
         <v>1</v>
       </c>
       <c r="H198" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I198" t="b">
         <v>0</v>
@@ -14082,7 +14106,7 @@
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>backend</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
@@ -14124,7 +14148,7 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>bulb warm yellliw pack 6</t>
+          <t>vintage 60w es bulb pack not dimmable</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -14185,14 +14209,14 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>squirrel cage vintage edison e27 screw bulb 8w clear</t>
+          <t>6 led e27 st64 8w 60 w dimmable warm white 2700k</t>
         </is>
       </c>
       <c r="G200" t="n">
         <v>1</v>
       </c>
       <c r="H200" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I200" t="b">
         <v>0</v>
@@ -14204,7 +14228,7 @@
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>backend</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
@@ -14246,7 +14270,7 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>6 led e27 st64 8w 60 w dimmable warm white 2700k</t>
+          <t>e27 2700k dimmable 8w amber 6 pack</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -14307,7 +14331,7 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>vintage 60w es bulb pack not dimmable</t>
+          <t>bulb warm yellliw pack 6</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -14429,7 +14453,7 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>e27 es dimmable bulb 8w squirrel cage</t>
+          <t>ledsone pack 3 | vintage led edison e27 light bulb, 8w (equivalent 60w) st64 dimmable 2700k warm white amber glass screw 806 lumens| energy saving bulb for squirrel cage lamp 220v [energy class a]</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -14490,14 +14514,14 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>bravo lighting bulbs 8w dimmable</t>
+          <t>e27 8w vintage light bulbs</t>
         </is>
       </c>
       <c r="G205" t="n">
         <v>4</v>
       </c>
       <c r="H205" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I205" t="b">
         <v>0</v>
@@ -14509,7 +14533,7 @@
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>backend</t>
         </is>
       </c>
       <c r="L205" t="inlineStr">
@@ -14551,7 +14575,7 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>ledsone pack 3 | vintage led edison e27 light bulb, 8w (equivalent 60w) st64 dimmable 2700k warm white amber glass screw 806 lumens| energy saving bulb for squirrel cage lamp 220v [energy class a]</t>
+          <t>e27 es dimmable bulb 8w squirrel cage</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -14612,14 +14636,14 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>e27 8w vintage light bulbs</t>
+          <t>bravo lighting bulbs 8w dimmable</t>
         </is>
       </c>
       <c r="G207" t="n">
         <v>4</v>
       </c>
       <c r="H207" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I207" t="b">
         <v>0</v>
@@ -14631,7 +14655,7 @@
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t>backend</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
@@ -14795,7 +14819,7 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>e27 8w 2200k 720lumen</t>
+          <t>e27 dimmable bulb pack of six</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -14856,7 +14880,7 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>e27 dimmable bulb pack of six</t>
+          <t>light bulbs screv wintage 8w</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -14917,7 +14941,7 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>light bulbs screv wintage 8w</t>
+          <t>e27 8w 2200k 720lumen</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -14978,14 +15002,14 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>e27 2700k dimmable 8w amber 6 pack</t>
+          <t>squirrel cage vintage edison e27 screw bulb 8w clear</t>
         </is>
       </c>
       <c r="G213" t="n">
         <v>1</v>
       </c>
       <c r="H213" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I213" t="b">
         <v>0</v>
@@ -14997,7 +15021,7 @@
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t>backend</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
@@ -15039,7 +15063,7 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>bulb warm yellliw pack 6</t>
+          <t>vintage 60w es bulb pack not dimmable</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -15100,7 +15124,7 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>squirrel cage vintage edison e27 screw bulb 8w clear</t>
+          <t>6 led e27 st64 8w 60 w dimmable warm white 2700k</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -15161,14 +15185,14 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>6 led e27 st64 8w 60 w dimmable warm white 2700k</t>
+          <t>e27 2700k dimmable 8w amber 6 pack</t>
         </is>
       </c>
       <c r="G216" t="n">
         <v>1</v>
       </c>
       <c r="H216" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I216" t="b">
         <v>0</v>
@@ -15180,7 +15204,7 @@
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>backend</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
@@ -15222,7 +15246,7 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>vintage 60w es bulb pack not dimmable</t>
+          <t>bulb warm yellliw pack 6</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -15470,7 +15494,7 @@
         </is>
       </c>
       <c r="G221" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="H221" t="b">
         <v>1</v>
@@ -16141,7 +16165,7 @@
         </is>
       </c>
       <c r="G232" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="H232" t="b">
         <v>1</v>
@@ -16625,31 +16649,31 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>large e27 vintage light bulbs</t>
+          <t>edison bulb</t>
         </is>
       </c>
       <c r="G240" t="n">
-        <v>150</v>
+        <v>133</v>
       </c>
       <c r="H240" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I240" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>gap</t>
+          <t>present</t>
         </is>
       </c>
       <c r="K240" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L240" t="inlineStr">
         <is>
-          <t>pending_add</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="M240" t="inlineStr">
@@ -16686,31 +16710,31 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>edison bulb</t>
+          <t>large e27 vintage light bulbs</t>
         </is>
       </c>
       <c r="G241" t="n">
-        <v>133</v>
+        <v>91</v>
       </c>
       <c r="H241" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I241" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>present</t>
+          <t>gap</t>
         </is>
       </c>
       <c r="K241" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L241" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>pending_add</t>
         </is>
       </c>
       <c r="M241" t="inlineStr">
@@ -16747,31 +16771,31 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>love light bulb</t>
+          <t>e27 large globe bulb</t>
         </is>
       </c>
       <c r="G242" t="n">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="H242" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I242" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>present</t>
+          <t>gap</t>
         </is>
       </c>
       <c r="K242" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L242" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>pending_add</t>
         </is>
       </c>
       <c r="M242" t="inlineStr">
@@ -16808,31 +16832,31 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>e27 screw bulb decorative</t>
+          <t>love light bulb</t>
         </is>
       </c>
       <c r="G243" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="H243" t="b">
         <v>1</v>
       </c>
       <c r="I243" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>gap</t>
+          <t>present</t>
         </is>
       </c>
       <c r="K243" t="inlineStr">
         <is>
-          <t>backend</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L243" t="inlineStr">
         <is>
-          <t>pending_add</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="M243" t="inlineStr">
@@ -16869,11 +16893,11 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>e27 large globe bulb</t>
+          <t>extra large edison bulb</t>
         </is>
       </c>
       <c r="G244" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H244" t="b">
         <v>0</v>
@@ -16930,14 +16954,14 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>extra large edison bulb</t>
+          <t>e27 screw bulb decorative</t>
         </is>
       </c>
       <c r="G245" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="H245" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I245" t="b">
         <v>0</v>
@@ -16949,7 +16973,7 @@
       </c>
       <c r="K245" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>backend</t>
         </is>
       </c>
       <c r="L245" t="inlineStr">
@@ -17235,31 +17259,31 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>g125 led bulb</t>
+          <t>screw e27 led light bulb, 4w globe large screw vintage edison led bulbs</t>
         </is>
       </c>
       <c r="G250" t="n">
         <v>6</v>
       </c>
       <c r="H250" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I250" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>present</t>
+          <t>gap</t>
         </is>
       </c>
       <c r="K250" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L250" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>pending_add</t>
         </is>
       </c>
       <c r="M250" t="inlineStr">
@@ -17296,31 +17320,31 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>screw e27 led light bulb, 4w globe large screw vintage edison led bulbs</t>
+          <t>g125 led bulb</t>
         </is>
       </c>
       <c r="G251" t="n">
         <v>6</v>
       </c>
       <c r="H251" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I251" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>gap</t>
+          <t>present</t>
         </is>
       </c>
       <c r="K251" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L251" t="inlineStr">
         <is>
-          <t>pending_add</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="M251" t="inlineStr">
@@ -17357,14 +17381,14 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>large edison screw bulb warm white</t>
+          <t>light bulb with amber love</t>
         </is>
       </c>
       <c r="G252" t="n">
         <v>5</v>
       </c>
       <c r="H252" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I252" t="b">
         <v>0</v>
@@ -17376,7 +17400,7 @@
       </c>
       <c r="K252" t="inlineStr">
         <is>
-          <t>backend_and_bullet</t>
+          <t>backend</t>
         </is>
       </c>
       <c r="L252" t="inlineStr">
@@ -17418,14 +17442,14 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>light bulb with amber love</t>
+          <t>large edison screw bulb warm white</t>
         </is>
       </c>
       <c r="G253" t="n">
         <v>5</v>
       </c>
       <c r="H253" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I253" t="b">
         <v>0</v>
@@ -17437,7 +17461,7 @@
       </c>
       <c r="K253" t="inlineStr">
         <is>
-          <t>backend</t>
+          <t>backend_and_bullet</t>
         </is>
       </c>
       <c r="L253" t="inlineStr">

--- a/development/abiraj_mini_aios_workbench/projects/PRJ-2026-026_amazon-keyword-gap-sync/evidence/final_outputs/REQ-30_amazon-keyword-gap-sync/REQ-30-D02_keyword_gap_report.xlsx
+++ b/development/abiraj_mini_aios_workbench/projects/PRJ-2026-026_amazon-keyword-gap-sync/evidence/final_outputs/REQ-30_amazon-keyword-gap-sync/REQ-30-D02_keyword_gap_report.xlsx
@@ -17,7 +17,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Part A - No Content'!$A$1:$K$23</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Part B - Keyword Gaps'!$A$1:$M$276</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Part C - SKU mismatch'!$A$1:$L$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Field Reference'!$A$1:$B$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Field Reference'!$A$1:$B$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -492,7 +492,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-19T13:42:26</t>
+          <t>2026-08-19T14:02:40</t>
         </is>
       </c>
     </row>
@@ -734,7 +734,7 @@
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
     <col width="48" customWidth="1" min="8" max="8"/>
-    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
@@ -782,7 +782,7 @@
       </c>
       <c r="I1" s="4" t="inlineStr">
         <is>
-          <t>terms_available</t>
+          <t>keywords_ready_to_use</t>
         </is>
       </c>
       <c r="J1" s="4" t="inlineStr">
@@ -19167,7 +19167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -19189,149 +19189,161 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>brand</t>
+          <t>keywords_ready_to_use</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>dcvoltage_uk / ledsone_uk — accounts never merged</t>
+          <t>Part A only — how many proven search terms already exist on the good-selling twin, ready for whoever rewrites this empty listing. 0 means the twin has none either.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>top_asin</t>
+          <t>brand</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Top-Moving ASIN — the source of the proven search terms</t>
+          <t>dcvoltage_uk / ledsone_uk — accounts never merged</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>base_sku</t>
+          <t>top_asin</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Normalised SKU — pack suffixes stripped, bundles kept whole</t>
+          <t>Top-Moving ASIN — the source of the proven search terms</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>duplicate_asin</t>
+          <t>base_sku</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Underperforming listing sharing the same base SKU</t>
+          <t>Normalised SKU — pack suffixes stripped, bundles kept whole</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>duplicate_status</t>
+          <t>duplicate_asin</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>sales_drop_3mo / zero_sales_6mo</t>
+          <t>Underperforming listing sharing the same base SKU</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>keyword</t>
+          <t>duplicate_status</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Top search term being audited (from the Phase 1 export)</t>
+          <t>sales_drop_3mo / zero_sales_6mo</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>in_frontend</t>
+          <t>keyword</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>TRUE if found in title, bullets or description (any one is enough)</t>
+          <t>Top search term being audited (from the Phase 1 export)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>in_backend</t>
+          <t>in_frontend</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>TRUE if found in the backend / generic keyword field</t>
+          <t>TRUE if found in title, bullets or description (any one is enough)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>in_backend</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>present / gap</t>
+          <t>TRUE if found in the backend / generic keyword field</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>add_target</t>
+          <t>status</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>backend / bullet / backend_and_bullet / none — where the term should be added</t>
+          <t>present / gap</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>action_state</t>
+          <t>add_target</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>reviewed / pending_add / added</t>
+          <t>backend / bullet / backend_and_bullet / none — where the term should be added</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>action_state</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>reviewed / pending_add / added</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>date_checked</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>ISO date of this monthly run</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B13"/>
+  <autoFilter ref="A1:B14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/development/abiraj_mini_aios_workbench/projects/PRJ-2026-026_amazon-keyword-gap-sync/evidence/final_outputs/REQ-30_amazon-keyword-gap-sync/REQ-30-D02_keyword_gap_report.xlsx
+++ b/development/abiraj_mini_aios_workbench/projects/PRJ-2026-026_amazon-keyword-gap-sync/evidence/final_outputs/REQ-30_amazon-keyword-gap-sync/REQ-30-D02_keyword_gap_report.xlsx
@@ -492,7 +492,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-19T15:18:23</t>
+          <t>2026-08-19T15:55:01</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>1_account_separation=PASS; 2_sku_mismatch_never_paired=PASS; 3_one_place_is_enough=PASS; 4_dual_method_independent=PASS; 5_directional_add_logic=PASS; 6_zero_manual_lookup=PASS; 7_monthly_cadence=PASS</t>
+          <t>1_account_separation=PASS; 2_sku_mismatch_never_paired=PASS; 3_one_place_is_enough=PASS; 4_dual_method_independent=PASS; 5_directional_add_logic=PASS; 6_zero_manual_lookup=PASS; 8_every_asin_accounted_for=PASS; 7_monthly_cadence=PASS</t>
         </is>
       </c>
     </row>

--- a/development/abiraj_mini_aios_workbench/projects/PRJ-2026-026_amazon-keyword-gap-sync/evidence/final_outputs/REQ-30_amazon-keyword-gap-sync/REQ-30-D02_keyword_gap_report.xlsx
+++ b/development/abiraj_mini_aios_workbench/projects/PRJ-2026-026_amazon-keyword-gap-sync/evidence/final_outputs/REQ-30_amazon-keyword-gap-sync/REQ-30-D02_keyword_gap_report.xlsx
@@ -492,7 +492,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-19T15:55:01</t>
+          <t>2026-08-19T16:06:04</t>
         </is>
       </c>
     </row>

--- a/development/abiraj_mini_aios_workbench/projects/PRJ-2026-026_amazon-keyword-gap-sync/evidence/final_outputs/REQ-30_amazon-keyword-gap-sync/REQ-30-D02_keyword_gap_report.xlsx
+++ b/development/abiraj_mini_aios_workbench/projects/PRJ-2026-026_amazon-keyword-gap-sync/evidence/final_outputs/REQ-30_amazon-keyword-gap-sync/REQ-30-D02_keyword_gap_report.xlsx
@@ -15,9 +15,9 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Part A - No Content'!$A$1:$K$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Part B - Keyword Gaps'!$A$1:$M$229</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Part B - Keyword Gaps'!$A$1:$O$229</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Part C - SKU mismatch'!$A$1:$L$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Field Reference'!$A$1:$B$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Field Reference'!$A$1:$B$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -492,7 +492,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-19T16:06:04</t>
+          <t>2026-08-19T16:20:33</t>
         </is>
       </c>
     </row>
@@ -875,7 +875,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M229"/>
+  <dimension ref="A1:O229"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -889,8 +889,10 @@
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
+    <col width="30" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -951,10 +953,20 @@
       </c>
       <c r="L1" s="4" t="inlineStr">
         <is>
+          <t>missing_words_backend</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>missing_words_frontend</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
           <t>action_state</t>
         </is>
       </c>
-      <c r="M1" s="4" t="inlineStr">
+      <c r="O1" s="4" t="inlineStr">
         <is>
           <t>date_checked</t>
         </is>
@@ -1010,12 +1022,14 @@
           <t>none</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
         <is>
           <t>reviewed</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -1071,12 +1085,14 @@
           <t>none</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
         <is>
           <t>reviewed</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -1134,10 +1150,20 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
+          <t>10w</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>10w</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -1195,10 +1221,20 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
+          <t>low watt</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -1254,12 +1290,14 @@
           <t>none</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
         <is>
           <t>reviewed</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -1315,12 +1353,18 @@
           <t>bullet</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>g80</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
         <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -1378,10 +1422,16 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
+          <t>vintage</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -1439,10 +1489,20 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
+          <t>lucide</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lucide</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -1500,10 +1560,16 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
+          <t>amber</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -1559,12 +1625,14 @@
           <t>none</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
         <is>
           <t>reviewed</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -1622,10 +1690,20 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -1683,10 +1761,20 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
+          <t>10w warm white</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>10w</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -1744,10 +1832,16 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
+          <t>low watt</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -1803,12 +1897,14 @@
           <t>none</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
         <is>
           <t>reviewed</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -1866,10 +1962,20 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
+          <t>g80</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>g80</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -1927,10 +2033,20 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
+          <t>globe warm white</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>globe</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -1988,10 +2104,20 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
+          <t>lucide dimmable</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>lucide dimmable</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -2049,10 +2175,20 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
+          <t>globe dimmable</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>globe dimmable</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -2108,12 +2244,14 @@
           <t>none</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
         <is>
           <t>reviewed</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -2169,12 +2307,14 @@
           <t>none</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
         <is>
           <t>reviewed</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -2230,12 +2370,14 @@
           <t>none</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
         <is>
           <t>reviewed</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -2293,10 +2435,20 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
+          <t>outdoor</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>outdoor</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -2354,10 +2506,20 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
+          <t>outdoor</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>outdoor</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -2415,10 +2577,20 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
+          <t>outdoor bulbs</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>outdoor</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -2476,10 +2648,20 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
+          <t>outdoor</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>outdoor</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -2537,10 +2719,20 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
+          <t>outdoor bulbs</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>outdoor</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -2598,10 +2790,20 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
+          <t>outdoor</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>outdoor</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -2657,12 +2859,14 @@
           <t>none</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
         <is>
           <t>reviewed</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -2720,10 +2924,16 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
+          <t>100w</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -2781,10 +2991,16 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
+          <t>100w</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -2842,10 +3058,20 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
+          <t>e27 screw</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>screw cool</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -2903,10 +3129,20 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
+          <t>e27 100w equivalent</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>100w</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -2964,10 +3200,20 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
+          <t>e27 screw 100w</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>screw cool 100w</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -3025,10 +3271,20 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -3086,10 +3342,20 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="O36" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -3147,10 +3413,20 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="O37" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -3206,12 +3482,14 @@
           <t>none</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
         <is>
           <t>reviewed</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr">
+      <c r="O38" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -3269,10 +3547,20 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr">
+      <c r="O39" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -3330,10 +3618,20 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr">
+      <c r="O40" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -3391,10 +3689,20 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr">
+      <c r="O41" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -3450,12 +3758,18 @@
           <t>bullet</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>bayonet</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
         <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
+      <c r="O42" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -3511,12 +3825,14 @@
           <t>none</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
         <is>
           <t>reviewed</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr">
+      <c r="O43" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -3572,12 +3888,14 @@
           <t>none</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
         <is>
           <t>reviewed</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr">
+      <c r="O44" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -3633,12 +3951,14 @@
           <t>none</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
         <is>
           <t>reviewed</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr">
+      <c r="O45" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -3696,10 +4016,16 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
+          <t>large bulbs</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
+      <c r="O46" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -3757,10 +4083,16 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr">
+      <c r="O47" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -3818,10 +4150,16 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr">
+      <c r="O48" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -3877,12 +4215,14 @@
           <t>none</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
         <is>
           <t>reviewed</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr">
+      <c r="O49" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -3940,10 +4280,16 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr">
+      <c r="O50" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -4001,10 +4347,16 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr">
+      <c r="O51" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -4062,10 +4414,16 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr">
+      <c r="O52" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -4123,10 +4481,20 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
+          <t>bulbs bayonet</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>bayonet</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr">
+      <c r="O53" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -4182,12 +4550,14 @@
           <t>none</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
         <is>
           <t>reviewed</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr">
+      <c r="O54" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -4245,10 +4615,16 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
+          <t>8w</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr">
+      <c r="O55" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -4304,12 +4680,14 @@
           <t>none</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
         <is>
           <t>reviewed</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr">
+      <c r="O56" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -4365,12 +4743,18 @@
           <t>bullet</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr">
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
         <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr">
+      <c r="O57" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -4426,12 +4810,18 @@
           <t>bullet</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr">
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
         <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M58" t="inlineStr">
+      <c r="O58" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -4487,12 +4877,18 @@
           <t>bullet</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr">
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>large globe</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
         <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M59" t="inlineStr">
+      <c r="O59" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -4548,12 +4944,18 @@
           <t>bullet</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr">
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>globe</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
         <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr">
+      <c r="O60" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -4609,12 +5011,18 @@
           <t>bullet</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>large globe</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
         <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr">
+      <c r="O61" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -4670,12 +5078,18 @@
           <t>bullet</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr">
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
         <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M62" t="inlineStr">
+      <c r="O62" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -4731,12 +5145,18 @@
           <t>bullet</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr">
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
         <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M63" t="inlineStr">
+      <c r="O63" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -4792,12 +5212,18 @@
           <t>bullet</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr">
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>decorative bayonet</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
         <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M64" t="inlineStr">
+      <c r="O64" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -4853,12 +5279,14 @@
           <t>none</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr">
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr">
         <is>
           <t>reviewed</t>
         </is>
       </c>
-      <c r="M65" t="inlineStr">
+      <c r="O65" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -4914,12 +5342,14 @@
           <t>none</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr">
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr">
         <is>
           <t>reviewed</t>
         </is>
       </c>
-      <c r="M66" t="inlineStr">
+      <c r="O66" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -4975,12 +5405,18 @@
           <t>bullet</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr">
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>globe</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
         <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M67" t="inlineStr">
+      <c r="O67" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -5038,10 +5474,20 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M68" t="inlineStr">
+      <c r="O68" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -5099,10 +5545,20 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M69" t="inlineStr">
+      <c r="O69" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -5160,10 +5616,20 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
+          <t>large globe</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M70" t="inlineStr">
+      <c r="O70" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -5221,10 +5687,16 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
+          <t>globe</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M71" t="inlineStr">
+      <c r="O71" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -5282,10 +5754,20 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
+          <t>large globe edison</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M72" t="inlineStr">
+      <c r="O72" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -5343,10 +5825,20 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M73" t="inlineStr">
+      <c r="O73" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -5404,10 +5896,20 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M74" t="inlineStr">
+      <c r="O74" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -5465,10 +5967,16 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
+          <t>decorative</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M75" t="inlineStr">
+      <c r="O75" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -5524,12 +6032,14 @@
           <t>none</t>
         </is>
       </c>
-      <c r="L76" t="inlineStr">
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr">
         <is>
           <t>reviewed</t>
         </is>
       </c>
-      <c r="M76" t="inlineStr">
+      <c r="O76" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -5587,10 +6097,16 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M77" t="inlineStr">
+      <c r="O77" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -5648,10 +6164,16 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
+          <t>amber filament globe</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M78" t="inlineStr">
+      <c r="O78" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -5709,10 +6231,16 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M79" t="inlineStr">
+      <c r="O79" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -5770,10 +6298,16 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M80" t="inlineStr">
+      <c r="O80" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -5831,10 +6365,16 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M81" t="inlineStr">
+      <c r="O81" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -5890,12 +6430,14 @@
           <t>none</t>
         </is>
       </c>
-      <c r="L82" t="inlineStr">
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr">
         <is>
           <t>reviewed</t>
         </is>
       </c>
-      <c r="M82" t="inlineStr">
+      <c r="O82" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -5953,10 +6495,16 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M83" t="inlineStr">
+      <c r="O83" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -6014,10 +6562,16 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M84" t="inlineStr">
+      <c r="O84" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -6075,10 +6629,16 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M85" t="inlineStr">
+      <c r="O85" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -6136,10 +6696,20 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
+          <t>bayonet</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>decorative bayonet</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M86" t="inlineStr">
+      <c r="O86" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -6195,12 +6765,14 @@
           <t>none</t>
         </is>
       </c>
-      <c r="L87" t="inlineStr">
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr">
         <is>
           <t>reviewed</t>
         </is>
       </c>
-      <c r="M87" t="inlineStr">
+      <c r="O87" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -6258,10 +6830,16 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M88" t="inlineStr">
+      <c r="O88" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -6317,12 +6895,14 @@
           <t>none</t>
         </is>
       </c>
-      <c r="L89" t="inlineStr">
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr">
         <is>
           <t>reviewed</t>
         </is>
       </c>
-      <c r="M89" t="inlineStr">
+      <c r="O89" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -6378,12 +6958,14 @@
           <t>none</t>
         </is>
       </c>
-      <c r="L90" t="inlineStr">
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr">
         <is>
           <t>reviewed</t>
         </is>
       </c>
-      <c r="M90" t="inlineStr">
+      <c r="O90" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -6439,12 +7021,14 @@
           <t>none</t>
         </is>
       </c>
-      <c r="L91" t="inlineStr">
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr">
         <is>
           <t>reviewed</t>
         </is>
       </c>
-      <c r="M91" t="inlineStr">
+      <c r="O91" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -6500,12 +7084,14 @@
           <t>none</t>
         </is>
       </c>
-      <c r="L92" t="inlineStr">
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr"/>
+      <c r="N92" t="inlineStr">
         <is>
           <t>reviewed</t>
         </is>
       </c>
-      <c r="M92" t="inlineStr">
+      <c r="O92" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -6561,12 +7147,14 @@
           <t>none</t>
         </is>
       </c>
-      <c r="L93" t="inlineStr">
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr"/>
+      <c r="N93" t="inlineStr">
         <is>
           <t>reviewed</t>
         </is>
       </c>
-      <c r="M93" t="inlineStr">
+      <c r="O93" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -6622,12 +7210,14 @@
           <t>none</t>
         </is>
       </c>
-      <c r="L94" t="inlineStr">
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr"/>
+      <c r="N94" t="inlineStr">
         <is>
           <t>reviewed</t>
         </is>
       </c>
-      <c r="M94" t="inlineStr">
+      <c r="O94" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -6683,12 +7273,14 @@
           <t>none</t>
         </is>
       </c>
-      <c r="L95" t="inlineStr">
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr">
         <is>
           <t>reviewed</t>
         </is>
       </c>
-      <c r="M95" t="inlineStr">
+      <c r="O95" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -6744,12 +7336,14 @@
           <t>none</t>
         </is>
       </c>
-      <c r="L96" t="inlineStr">
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr"/>
+      <c r="N96" t="inlineStr">
         <is>
           <t>reviewed</t>
         </is>
       </c>
-      <c r="M96" t="inlineStr">
+      <c r="O96" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -6805,12 +7399,14 @@
           <t>none</t>
         </is>
       </c>
-      <c r="L97" t="inlineStr">
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr"/>
+      <c r="N97" t="inlineStr">
         <is>
           <t>reviewed</t>
         </is>
       </c>
-      <c r="M97" t="inlineStr">
+      <c r="O97" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -6866,12 +7462,14 @@
           <t>none</t>
         </is>
       </c>
-      <c r="L98" t="inlineStr">
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr"/>
+      <c r="N98" t="inlineStr">
         <is>
           <t>reviewed</t>
         </is>
       </c>
-      <c r="M98" t="inlineStr">
+      <c r="O98" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -6927,12 +7525,14 @@
           <t>none</t>
         </is>
       </c>
-      <c r="L99" t="inlineStr">
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr"/>
+      <c r="N99" t="inlineStr">
         <is>
           <t>reviewed</t>
         </is>
       </c>
-      <c r="M99" t="inlineStr">
+      <c r="O99" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -6988,12 +7588,14 @@
           <t>none</t>
         </is>
       </c>
-      <c r="L100" t="inlineStr">
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr"/>
+      <c r="N100" t="inlineStr">
         <is>
           <t>reviewed</t>
         </is>
       </c>
-      <c r="M100" t="inlineStr">
+      <c r="O100" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -7049,12 +7651,18 @@
           <t>bullet</t>
         </is>
       </c>
-      <c r="L101" t="inlineStr">
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
         <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M101" t="inlineStr">
+      <c r="O101" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -7110,12 +7718,18 @@
           <t>bullet</t>
         </is>
       </c>
-      <c r="L102" t="inlineStr">
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
         <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M102" t="inlineStr">
+      <c r="O102" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -7171,12 +7785,18 @@
           <t>bullet</t>
         </is>
       </c>
-      <c r="L103" t="inlineStr">
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
         <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M103" t="inlineStr">
+      <c r="O103" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -7232,12 +7852,14 @@
           <t>none</t>
         </is>
       </c>
-      <c r="L104" t="inlineStr">
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr"/>
+      <c r="N104" t="inlineStr">
         <is>
           <t>reviewed</t>
         </is>
       </c>
-      <c r="M104" t="inlineStr">
+      <c r="O104" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -7293,12 +7915,18 @@
           <t>bullet</t>
         </is>
       </c>
-      <c r="L105" t="inlineStr">
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
         <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M105" t="inlineStr">
+      <c r="O105" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -7354,12 +7982,18 @@
           <t>bullet</t>
         </is>
       </c>
-      <c r="L106" t="inlineStr">
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
         <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M106" t="inlineStr">
+      <c r="O106" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -7415,12 +8049,18 @@
           <t>bullet</t>
         </is>
       </c>
-      <c r="L107" t="inlineStr">
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
         <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M107" t="inlineStr">
+      <c r="O107" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -7478,10 +8118,16 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
+          <t>bayonet</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr"/>
+      <c r="N108" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M108" t="inlineStr">
+      <c r="O108" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -7537,12 +8183,14 @@
           <t>none</t>
         </is>
       </c>
-      <c r="L109" t="inlineStr">
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr"/>
+      <c r="N109" t="inlineStr">
         <is>
           <t>reviewed</t>
         </is>
       </c>
-      <c r="M109" t="inlineStr">
+      <c r="O109" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -7598,12 +8246,14 @@
           <t>none</t>
         </is>
       </c>
-      <c r="L110" t="inlineStr">
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr"/>
+      <c r="N110" t="inlineStr">
         <is>
           <t>reviewed</t>
         </is>
       </c>
-      <c r="M110" t="inlineStr">
+      <c r="O110" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -7659,12 +8309,14 @@
           <t>none</t>
         </is>
       </c>
-      <c r="L111" t="inlineStr">
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr"/>
+      <c r="N111" t="inlineStr">
         <is>
           <t>reviewed</t>
         </is>
       </c>
-      <c r="M111" t="inlineStr">
+      <c r="O111" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -7720,12 +8372,14 @@
           <t>none</t>
         </is>
       </c>
-      <c r="L112" t="inlineStr">
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr"/>
+      <c r="N112" t="inlineStr">
         <is>
           <t>reviewed</t>
         </is>
       </c>
-      <c r="M112" t="inlineStr">
+      <c r="O112" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -7781,12 +8435,14 @@
           <t>none</t>
         </is>
       </c>
-      <c r="L113" t="inlineStr">
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr"/>
+      <c r="N113" t="inlineStr">
         <is>
           <t>reviewed</t>
         </is>
       </c>
-      <c r="M113" t="inlineStr">
+      <c r="O113" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -7842,12 +8498,14 @@
           <t>none</t>
         </is>
       </c>
-      <c r="L114" t="inlineStr">
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr"/>
+      <c r="N114" t="inlineStr">
         <is>
           <t>reviewed</t>
         </is>
       </c>
-      <c r="M114" t="inlineStr">
+      <c r="O114" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -7903,12 +8561,14 @@
           <t>none</t>
         </is>
       </c>
-      <c r="L115" t="inlineStr">
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr"/>
+      <c r="N115" t="inlineStr">
         <is>
           <t>reviewed</t>
         </is>
       </c>
-      <c r="M115" t="inlineStr">
+      <c r="O115" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -7966,10 +8626,20 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
+          <t>10w</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>10w gls</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M116" t="inlineStr">
+      <c r="O116" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -8025,12 +8695,14 @@
           <t>none</t>
         </is>
       </c>
-      <c r="L117" t="inlineStr">
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr"/>
+      <c r="N117" t="inlineStr">
         <is>
           <t>reviewed</t>
         </is>
       </c>
-      <c r="M117" t="inlineStr">
+      <c r="O117" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -8088,10 +8760,20 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M118" t="inlineStr">
+      <c r="O118" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -8147,12 +8829,14 @@
           <t>none</t>
         </is>
       </c>
-      <c r="L119" t="inlineStr">
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr"/>
+      <c r="N119" t="inlineStr">
         <is>
           <t>reviewed</t>
         </is>
       </c>
-      <c r="M119" t="inlineStr">
+      <c r="O119" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -8208,12 +8892,14 @@
           <t>none</t>
         </is>
       </c>
-      <c r="L120" t="inlineStr">
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr"/>
+      <c r="N120" t="inlineStr">
         <is>
           <t>reviewed</t>
         </is>
       </c>
-      <c r="M120" t="inlineStr">
+      <c r="O120" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -8271,10 +8957,20 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
+          <t>10w gls</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>10w gls</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M121" t="inlineStr">
+      <c r="O121" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -8330,12 +9026,14 @@
           <t>none</t>
         </is>
       </c>
-      <c r="L122" t="inlineStr">
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr"/>
+      <c r="N122" t="inlineStr">
         <is>
           <t>reviewed</t>
         </is>
       </c>
-      <c r="M122" t="inlineStr">
+      <c r="O122" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -8391,12 +9089,14 @@
           <t>none</t>
         </is>
       </c>
-      <c r="L123" t="inlineStr">
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr"/>
+      <c r="N123" t="inlineStr">
         <is>
           <t>reviewed</t>
         </is>
       </c>
-      <c r="M123" t="inlineStr">
+      <c r="O123" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -8454,10 +9154,16 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
+          <t>edison</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr"/>
+      <c r="N124" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M124" t="inlineStr">
+      <c r="O124" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -8515,10 +9221,16 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
+          <t>60w</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr"/>
+      <c r="N125" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M125" t="inlineStr">
+      <c r="O125" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -8574,12 +9286,18 @@
           <t>bullet</t>
         </is>
       </c>
-      <c r="L126" t="inlineStr">
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>4000k</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr">
         <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M126" t="inlineStr">
+      <c r="O126" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -8637,10 +9355,16 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
+          <t>bulbs</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr"/>
+      <c r="N127" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M127" t="inlineStr">
+      <c r="O127" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -8696,12 +9420,14 @@
           <t>none</t>
         </is>
       </c>
-      <c r="L128" t="inlineStr">
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr"/>
+      <c r="N128" t="inlineStr">
         <is>
           <t>reviewed</t>
         </is>
       </c>
-      <c r="M128" t="inlineStr">
+      <c r="O128" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -8757,12 +9483,14 @@
           <t>none</t>
         </is>
       </c>
-      <c r="L129" t="inlineStr">
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="inlineStr"/>
+      <c r="N129" t="inlineStr">
         <is>
           <t>reviewed</t>
         </is>
       </c>
-      <c r="M129" t="inlineStr">
+      <c r="O129" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -8818,12 +9546,14 @@
           <t>none</t>
         </is>
       </c>
-      <c r="L130" t="inlineStr">
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" t="inlineStr"/>
+      <c r="N130" t="inlineStr">
         <is>
           <t>reviewed</t>
         </is>
       </c>
-      <c r="M130" t="inlineStr">
+      <c r="O130" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -8879,12 +9609,18 @@
           <t>bullet</t>
         </is>
       </c>
-      <c r="L131" t="inlineStr">
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>60w</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr">
         <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M131" t="inlineStr">
+      <c r="O131" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -8942,10 +9678,20 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
+          <t>4000k</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>4000k</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M132" t="inlineStr">
+      <c r="O132" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -9001,12 +9747,14 @@
           <t>none</t>
         </is>
       </c>
-      <c r="L133" t="inlineStr">
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="inlineStr"/>
+      <c r="N133" t="inlineStr">
         <is>
           <t>reviewed</t>
         </is>
       </c>
-      <c r="M133" t="inlineStr">
+      <c r="O133" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -9062,12 +9810,14 @@
           <t>none</t>
         </is>
       </c>
-      <c r="L134" t="inlineStr">
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" t="inlineStr"/>
+      <c r="N134" t="inlineStr">
         <is>
           <t>reviewed</t>
         </is>
       </c>
-      <c r="M134" t="inlineStr">
+      <c r="O134" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -9123,12 +9873,14 @@
           <t>none</t>
         </is>
       </c>
-      <c r="L135" t="inlineStr">
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr"/>
+      <c r="N135" t="inlineStr">
         <is>
           <t>reviewed</t>
         </is>
       </c>
-      <c r="M135" t="inlineStr">
+      <c r="O135" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -9184,12 +9936,14 @@
           <t>none</t>
         </is>
       </c>
-      <c r="L136" t="inlineStr">
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" t="inlineStr"/>
+      <c r="N136" t="inlineStr">
         <is>
           <t>reviewed</t>
         </is>
       </c>
-      <c r="M136" t="inlineStr">
+      <c r="O136" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -9247,10 +10001,20 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
+          <t>60w</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>60w</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M137" t="inlineStr">
+      <c r="O137" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -9308,10 +10072,20 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
+          <t>4000k</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>4000k</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M138" t="inlineStr">
+      <c r="O138" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -9367,12 +10141,14 @@
           <t>none</t>
         </is>
       </c>
-      <c r="L139" t="inlineStr">
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="inlineStr"/>
+      <c r="N139" t="inlineStr">
         <is>
           <t>reviewed</t>
         </is>
       </c>
-      <c r="M139" t="inlineStr">
+      <c r="O139" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -9428,12 +10204,14 @@
           <t>none</t>
         </is>
       </c>
-      <c r="L140" t="inlineStr">
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" t="inlineStr"/>
+      <c r="N140" t="inlineStr">
         <is>
           <t>reviewed</t>
         </is>
       </c>
-      <c r="M140" t="inlineStr">
+      <c r="O140" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -9489,12 +10267,14 @@
           <t>none</t>
         </is>
       </c>
-      <c r="L141" t="inlineStr">
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" t="inlineStr"/>
+      <c r="N141" t="inlineStr">
         <is>
           <t>reviewed</t>
         </is>
       </c>
-      <c r="M141" t="inlineStr">
+      <c r="O141" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -9550,12 +10330,14 @@
           <t>none</t>
         </is>
       </c>
-      <c r="L142" t="inlineStr">
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" t="inlineStr"/>
+      <c r="N142" t="inlineStr">
         <is>
           <t>reviewed</t>
         </is>
       </c>
-      <c r="M142" t="inlineStr">
+      <c r="O142" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -9613,10 +10395,20 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
+          <t>60w</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>60w</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M143" t="inlineStr">
+      <c r="O143" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -9674,10 +10466,20 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
+          <t>4000k</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>4000k</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M144" t="inlineStr">
+      <c r="O144" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -9733,12 +10535,14 @@
           <t>none</t>
         </is>
       </c>
-      <c r="L145" t="inlineStr">
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" t="inlineStr"/>
+      <c r="N145" t="inlineStr">
         <is>
           <t>reviewed</t>
         </is>
       </c>
-      <c r="M145" t="inlineStr">
+      <c r="O145" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -9794,12 +10598,14 @@
           <t>none</t>
         </is>
       </c>
-      <c r="L146" t="inlineStr">
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" t="inlineStr"/>
+      <c r="N146" t="inlineStr">
         <is>
           <t>reviewed</t>
         </is>
       </c>
-      <c r="M146" t="inlineStr">
+      <c r="O146" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -9855,12 +10661,14 @@
           <t>none</t>
         </is>
       </c>
-      <c r="L147" t="inlineStr">
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" t="inlineStr"/>
+      <c r="N147" t="inlineStr">
         <is>
           <t>reviewed</t>
         </is>
       </c>
-      <c r="M147" t="inlineStr">
+      <c r="O147" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -9916,12 +10724,14 @@
           <t>none</t>
         </is>
       </c>
-      <c r="L148" t="inlineStr">
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" t="inlineStr"/>
+      <c r="N148" t="inlineStr">
         <is>
           <t>reviewed</t>
         </is>
       </c>
-      <c r="M148" t="inlineStr">
+      <c r="O148" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -9977,12 +10787,18 @@
           <t>bullet</t>
         </is>
       </c>
-      <c r="L149" t="inlineStr">
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>60w</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr">
         <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M149" t="inlineStr">
+      <c r="O149" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -10040,10 +10856,20 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
+          <t>4000k</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>4000k</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M150" t="inlineStr">
+      <c r="O150" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -10101,10 +10927,16 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
+          <t>bulbs</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr"/>
+      <c r="N151" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M151" t="inlineStr">
+      <c r="O151" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -10160,12 +10992,14 @@
           <t>none</t>
         </is>
       </c>
-      <c r="L152" t="inlineStr">
+      <c r="L152" t="inlineStr"/>
+      <c r="M152" t="inlineStr"/>
+      <c r="N152" t="inlineStr">
         <is>
           <t>reviewed</t>
         </is>
       </c>
-      <c r="M152" t="inlineStr">
+      <c r="O152" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -10221,12 +11055,14 @@
           <t>none</t>
         </is>
       </c>
-      <c r="L153" t="inlineStr">
+      <c r="L153" t="inlineStr"/>
+      <c r="M153" t="inlineStr"/>
+      <c r="N153" t="inlineStr">
         <is>
           <t>reviewed</t>
         </is>
       </c>
-      <c r="M153" t="inlineStr">
+      <c r="O153" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -10282,12 +11118,14 @@
           <t>none</t>
         </is>
       </c>
-      <c r="L154" t="inlineStr">
+      <c r="L154" t="inlineStr"/>
+      <c r="M154" t="inlineStr"/>
+      <c r="N154" t="inlineStr">
         <is>
           <t>reviewed</t>
         </is>
       </c>
-      <c r="M154" t="inlineStr">
+      <c r="O154" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -10345,10 +11183,16 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
+          <t>60w</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr"/>
+      <c r="N155" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M155" t="inlineStr">
+      <c r="O155" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -10406,10 +11250,20 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
+          <t>4000k</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>4000k</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M156" t="inlineStr">
+      <c r="O156" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -10465,12 +11319,14 @@
           <t>none</t>
         </is>
       </c>
-      <c r="L157" t="inlineStr">
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" t="inlineStr"/>
+      <c r="N157" t="inlineStr">
         <is>
           <t>reviewed</t>
         </is>
       </c>
-      <c r="M157" t="inlineStr">
+      <c r="O157" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -10528,10 +11384,16 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
+          <t>screw</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr"/>
+      <c r="N158" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M158" t="inlineStr">
+      <c r="O158" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -10589,10 +11451,16 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
+          <t>dimmable</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr"/>
+      <c r="N159" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M159" t="inlineStr">
+      <c r="O159" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -10650,10 +11518,16 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
+          <t>screw</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr"/>
+      <c r="N160" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M160" t="inlineStr">
+      <c r="O160" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -10711,10 +11585,20 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
+          <t>60w</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>60w</t>
+        </is>
+      </c>
+      <c r="N161" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M161" t="inlineStr">
+      <c r="O161" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -10772,10 +11656,20 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
+          <t>4000k</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>4000k</t>
+        </is>
+      </c>
+      <c r="N162" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M162" t="inlineStr">
+      <c r="O162" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -10831,12 +11725,14 @@
           <t>none</t>
         </is>
       </c>
-      <c r="L163" t="inlineStr">
+      <c r="L163" t="inlineStr"/>
+      <c r="M163" t="inlineStr"/>
+      <c r="N163" t="inlineStr">
         <is>
           <t>reviewed</t>
         </is>
       </c>
-      <c r="M163" t="inlineStr">
+      <c r="O163" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -10894,10 +11790,16 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
+          <t>60w</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr"/>
+      <c r="N164" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M164" t="inlineStr">
+      <c r="O164" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -10955,10 +11857,16 @@
       </c>
       <c r="L165" t="inlineStr">
         <is>
+          <t>60w</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr"/>
+      <c r="N165" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M165" t="inlineStr">
+      <c r="O165" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -11016,10 +11924,16 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
+          <t>60w</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr"/>
+      <c r="N166" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M166" t="inlineStr">
+      <c r="O166" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -11077,10 +11991,16 @@
       </c>
       <c r="L167" t="inlineStr">
         <is>
+          <t>60w</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr"/>
+      <c r="N167" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M167" t="inlineStr">
+      <c r="O167" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -11136,12 +12056,14 @@
           <t>none</t>
         </is>
       </c>
-      <c r="L168" t="inlineStr">
+      <c r="L168" t="inlineStr"/>
+      <c r="M168" t="inlineStr"/>
+      <c r="N168" t="inlineStr">
         <is>
           <t>reviewed</t>
         </is>
       </c>
-      <c r="M168" t="inlineStr">
+      <c r="O168" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -11199,10 +12121,20 @@
       </c>
       <c r="L169" t="inlineStr">
         <is>
+          <t>60w</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>60w</t>
+        </is>
+      </c>
+      <c r="N169" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M169" t="inlineStr">
+      <c r="O169" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -11260,10 +12192,20 @@
       </c>
       <c r="L170" t="inlineStr">
         <is>
+          <t>60w</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>60w</t>
+        </is>
+      </c>
+      <c r="N170" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M170" t="inlineStr">
+      <c r="O170" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -11319,12 +12261,14 @@
           <t>none</t>
         </is>
       </c>
-      <c r="L171" t="inlineStr">
+      <c r="L171" t="inlineStr"/>
+      <c r="M171" t="inlineStr"/>
+      <c r="N171" t="inlineStr">
         <is>
           <t>reviewed</t>
         </is>
       </c>
-      <c r="M171" t="inlineStr">
+      <c r="O171" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -11380,12 +12324,14 @@
           <t>none</t>
         </is>
       </c>
-      <c r="L172" t="inlineStr">
+      <c r="L172" t="inlineStr"/>
+      <c r="M172" t="inlineStr"/>
+      <c r="N172" t="inlineStr">
         <is>
           <t>reviewed</t>
         </is>
       </c>
-      <c r="M172" t="inlineStr">
+      <c r="O172" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -11443,10 +12389,20 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
+          <t>24v</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>24v</t>
+        </is>
+      </c>
+      <c r="N173" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M173" t="inlineStr">
+      <c r="O173" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -11502,12 +12458,14 @@
           <t>none</t>
         </is>
       </c>
-      <c r="L174" t="inlineStr">
+      <c r="L174" t="inlineStr"/>
+      <c r="M174" t="inlineStr"/>
+      <c r="N174" t="inlineStr">
         <is>
           <t>reviewed</t>
         </is>
       </c>
-      <c r="M174" t="inlineStr">
+      <c r="O174" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -11565,10 +12523,20 @@
       </c>
       <c r="L175" t="inlineStr">
         <is>
+          <t>8w</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>8w</t>
+        </is>
+      </c>
+      <c r="N175" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M175" t="inlineStr">
+      <c r="O175" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -11624,12 +12592,14 @@
           <t>none</t>
         </is>
       </c>
-      <c r="L176" t="inlineStr">
+      <c r="L176" t="inlineStr"/>
+      <c r="M176" t="inlineStr"/>
+      <c r="N176" t="inlineStr">
         <is>
           <t>reviewed</t>
         </is>
       </c>
-      <c r="M176" t="inlineStr">
+      <c r="O176" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -11685,12 +12655,14 @@
           <t>none</t>
         </is>
       </c>
-      <c r="L177" t="inlineStr">
+      <c r="L177" t="inlineStr"/>
+      <c r="M177" t="inlineStr"/>
+      <c r="N177" t="inlineStr">
         <is>
           <t>reviewed</t>
         </is>
       </c>
-      <c r="M177" t="inlineStr">
+      <c r="O177" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -11748,10 +12720,20 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
+          <t>24v</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>24v</t>
+        </is>
+      </c>
+      <c r="N178" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M178" t="inlineStr">
+      <c r="O178" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -11809,10 +12791,16 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
+          <t>bulbs</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr"/>
+      <c r="N179" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M179" t="inlineStr">
+      <c r="O179" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -11868,12 +12856,18 @@
           <t>bullet</t>
         </is>
       </c>
-      <c r="L180" t="inlineStr">
+      <c r="L180" t="inlineStr"/>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>8w</t>
+        </is>
+      </c>
+      <c r="N180" t="inlineStr">
         <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M180" t="inlineStr">
+      <c r="O180" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -11931,10 +12925,16 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
+          <t>screw</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr"/>
+      <c r="N181" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M181" t="inlineStr">
+      <c r="O181" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -11990,12 +12990,14 @@
           <t>none</t>
         </is>
       </c>
-      <c r="L182" t="inlineStr">
+      <c r="L182" t="inlineStr"/>
+      <c r="M182" t="inlineStr"/>
+      <c r="N182" t="inlineStr">
         <is>
           <t>reviewed</t>
         </is>
       </c>
-      <c r="M182" t="inlineStr">
+      <c r="O182" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -12053,10 +13055,20 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
+          <t>24v</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>24v</t>
+        </is>
+      </c>
+      <c r="N183" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M183" t="inlineStr">
+      <c r="O183" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -12112,12 +13124,14 @@
           <t>none</t>
         </is>
       </c>
-      <c r="L184" t="inlineStr">
+      <c r="L184" t="inlineStr"/>
+      <c r="M184" t="inlineStr"/>
+      <c r="N184" t="inlineStr">
         <is>
           <t>reviewed</t>
         </is>
       </c>
-      <c r="M184" t="inlineStr">
+      <c r="O184" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -12175,10 +13189,20 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
+          <t>screw</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>8w</t>
+        </is>
+      </c>
+      <c r="N185" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M185" t="inlineStr">
+      <c r="O185" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -12234,12 +13258,14 @@
           <t>none</t>
         </is>
       </c>
-      <c r="L186" t="inlineStr">
+      <c r="L186" t="inlineStr"/>
+      <c r="M186" t="inlineStr"/>
+      <c r="N186" t="inlineStr">
         <is>
           <t>reviewed</t>
         </is>
       </c>
-      <c r="M186" t="inlineStr">
+      <c r="O186" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -12295,12 +13321,14 @@
           <t>none</t>
         </is>
       </c>
-      <c r="L187" t="inlineStr">
+      <c r="L187" t="inlineStr"/>
+      <c r="M187" t="inlineStr"/>
+      <c r="N187" t="inlineStr">
         <is>
           <t>reviewed</t>
         </is>
       </c>
-      <c r="M187" t="inlineStr">
+      <c r="O187" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -12358,10 +13386,20 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
+          <t>24v</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>24v</t>
+        </is>
+      </c>
+      <c r="N188" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M188" t="inlineStr">
+      <c r="O188" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -12417,12 +13455,14 @@
           <t>none</t>
         </is>
       </c>
-      <c r="L189" t="inlineStr">
+      <c r="L189" t="inlineStr"/>
+      <c r="M189" t="inlineStr"/>
+      <c r="N189" t="inlineStr">
         <is>
           <t>reviewed</t>
         </is>
       </c>
-      <c r="M189" t="inlineStr">
+      <c r="O189" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -12480,10 +13520,20 @@
       </c>
       <c r="L190" t="inlineStr">
         <is>
+          <t>8w</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>8w</t>
+        </is>
+      </c>
+      <c r="N190" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M190" t="inlineStr">
+      <c r="O190" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -12541,10 +13591,16 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
+          <t>screw</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr"/>
+      <c r="N191" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M191" t="inlineStr">
+      <c r="O191" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -12600,12 +13656,14 @@
           <t>none</t>
         </is>
       </c>
-      <c r="L192" t="inlineStr">
+      <c r="L192" t="inlineStr"/>
+      <c r="M192" t="inlineStr"/>
+      <c r="N192" t="inlineStr">
         <is>
           <t>reviewed</t>
         </is>
       </c>
-      <c r="M192" t="inlineStr">
+      <c r="O192" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -12663,10 +13721,20 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
+          <t>24v</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>24v</t>
+        </is>
+      </c>
+      <c r="N193" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M193" t="inlineStr">
+      <c r="O193" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -12724,10 +13792,16 @@
       </c>
       <c r="L194" t="inlineStr">
         <is>
+          <t>bulbs</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr"/>
+      <c r="N194" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M194" t="inlineStr">
+      <c r="O194" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -12785,10 +13859,20 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
+          <t>8w screw</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>8w</t>
+        </is>
+      </c>
+      <c r="N195" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M195" t="inlineStr">
+      <c r="O195" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -12844,12 +13928,14 @@
           <t>none</t>
         </is>
       </c>
-      <c r="L196" t="inlineStr">
+      <c r="L196" t="inlineStr"/>
+      <c r="M196" t="inlineStr"/>
+      <c r="N196" t="inlineStr">
         <is>
           <t>reviewed</t>
         </is>
       </c>
-      <c r="M196" t="inlineStr">
+      <c r="O196" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -12907,10 +13993,20 @@
       </c>
       <c r="L197" t="inlineStr">
         <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="N197" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M197" t="inlineStr">
+      <c r="O197" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -12968,10 +14064,20 @@
       </c>
       <c r="L198" t="inlineStr">
         <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="N198" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M198" t="inlineStr">
+      <c r="O198" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -13027,12 +14133,14 @@
           <t>none</t>
         </is>
       </c>
-      <c r="L199" t="inlineStr">
+      <c r="L199" t="inlineStr"/>
+      <c r="M199" t="inlineStr"/>
+      <c r="N199" t="inlineStr">
         <is>
           <t>reviewed</t>
         </is>
       </c>
-      <c r="M199" t="inlineStr">
+      <c r="O199" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -13090,10 +14198,20 @@
       </c>
       <c r="L200" t="inlineStr">
         <is>
+          <t>extra large</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>extra large</t>
+        </is>
+      </c>
+      <c r="N200" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M200" t="inlineStr">
+      <c r="O200" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -13151,10 +14269,16 @@
       </c>
       <c r="L201" t="inlineStr">
         <is>
+          <t>screw</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr"/>
+      <c r="N201" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M201" t="inlineStr">
+      <c r="O201" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -13210,12 +14334,18 @@
           <t>bullet</t>
         </is>
       </c>
-      <c r="L202" t="inlineStr">
+      <c r="L202" t="inlineStr"/>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>big</t>
+        </is>
+      </c>
+      <c r="N202" t="inlineStr">
         <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M202" t="inlineStr">
+      <c r="O202" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -13273,10 +14403,20 @@
       </c>
       <c r="L203" t="inlineStr">
         <is>
+          <t>screw spiral</t>
+        </is>
+      </c>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>spiral</t>
+        </is>
+      </c>
+      <c r="N203" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M203" t="inlineStr">
+      <c r="O203" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -13334,10 +14474,20 @@
       </c>
       <c r="L204" t="inlineStr">
         <is>
+          <t>white large screw</t>
+        </is>
+      </c>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="N204" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M204" t="inlineStr">
+      <c r="O204" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -13393,12 +14543,14 @@
           <t>none</t>
         </is>
       </c>
-      <c r="L205" t="inlineStr">
+      <c r="L205" t="inlineStr"/>
+      <c r="M205" t="inlineStr"/>
+      <c r="N205" t="inlineStr">
         <is>
           <t>reviewed</t>
         </is>
       </c>
-      <c r="M205" t="inlineStr">
+      <c r="O205" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -13454,12 +14606,14 @@
           <t>none</t>
         </is>
       </c>
-      <c r="L206" t="inlineStr">
+      <c r="L206" t="inlineStr"/>
+      <c r="M206" t="inlineStr"/>
+      <c r="N206" t="inlineStr">
         <is>
           <t>reviewed</t>
         </is>
       </c>
-      <c r="M206" t="inlineStr">
+      <c r="O206" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -13515,12 +14669,14 @@
           <t>none</t>
         </is>
       </c>
-      <c r="L207" t="inlineStr">
+      <c r="L207" t="inlineStr"/>
+      <c r="M207" t="inlineStr"/>
+      <c r="N207" t="inlineStr">
         <is>
           <t>reviewed</t>
         </is>
       </c>
-      <c r="M207" t="inlineStr">
+      <c r="O207" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -13576,12 +14732,14 @@
           <t>none</t>
         </is>
       </c>
-      <c r="L208" t="inlineStr">
+      <c r="L208" t="inlineStr"/>
+      <c r="M208" t="inlineStr"/>
+      <c r="N208" t="inlineStr">
         <is>
           <t>reviewed</t>
         </is>
       </c>
-      <c r="M208" t="inlineStr">
+      <c r="O208" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -13639,10 +14797,20 @@
       </c>
       <c r="L209" t="inlineStr">
         <is>
+          <t>e14</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>e14</t>
+        </is>
+      </c>
+      <c r="N209" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M209" t="inlineStr">
+      <c r="O209" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -13698,12 +14866,18 @@
           <t>bullet</t>
         </is>
       </c>
-      <c r="L210" t="inlineStr">
+      <c r="L210" t="inlineStr"/>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>fancy</t>
+        </is>
+      </c>
+      <c r="N210" t="inlineStr">
         <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M210" t="inlineStr">
+      <c r="O210" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -13759,12 +14933,14 @@
           <t>none</t>
         </is>
       </c>
-      <c r="L211" t="inlineStr">
+      <c r="L211" t="inlineStr"/>
+      <c r="M211" t="inlineStr"/>
+      <c r="N211" t="inlineStr">
         <is>
           <t>reviewed</t>
         </is>
       </c>
-      <c r="M211" t="inlineStr">
+      <c r="O211" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -13822,10 +14998,20 @@
       </c>
       <c r="L212" t="inlineStr">
         <is>
+          <t>e14 2w shaped</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>e14 2w</t>
+        </is>
+      </c>
+      <c r="N212" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M212" t="inlineStr">
+      <c r="O212" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -13883,10 +15069,20 @@
       </c>
       <c r="L213" t="inlineStr">
         <is>
+          <t>lightbulbs</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>fancy lightbulbs</t>
+        </is>
+      </c>
+      <c r="N213" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M213" t="inlineStr">
+      <c r="O213" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -13942,12 +15138,14 @@
           <t>none</t>
         </is>
       </c>
-      <c r="L214" t="inlineStr">
+      <c r="L214" t="inlineStr"/>
+      <c r="M214" t="inlineStr"/>
+      <c r="N214" t="inlineStr">
         <is>
           <t>reviewed</t>
         </is>
       </c>
-      <c r="M214" t="inlineStr">
+      <c r="O214" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -14005,10 +15203,16 @@
       </c>
       <c r="L215" t="inlineStr">
         <is>
+          <t>bulbs</t>
+        </is>
+      </c>
+      <c r="M215" t="inlineStr"/>
+      <c r="N215" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M215" t="inlineStr">
+      <c r="O215" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -14066,10 +15270,16 @@
       </c>
       <c r="L216" t="inlineStr">
         <is>
+          <t>bulbs</t>
+        </is>
+      </c>
+      <c r="M216" t="inlineStr"/>
+      <c r="N216" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M216" t="inlineStr">
+      <c r="O216" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -14127,10 +15337,20 @@
       </c>
       <c r="L217" t="inlineStr">
         <is>
+          <t>e14</t>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>e14</t>
+        </is>
+      </c>
+      <c r="N217" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M217" t="inlineStr">
+      <c r="O217" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -14188,10 +15408,20 @@
       </c>
       <c r="L218" t="inlineStr">
         <is>
+          <t>fancy bulbs</t>
+        </is>
+      </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>fancy</t>
+        </is>
+      </c>
+      <c r="N218" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M218" t="inlineStr">
+      <c r="O218" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -14247,12 +15477,14 @@
           <t>none</t>
         </is>
       </c>
-      <c r="L219" t="inlineStr">
+      <c r="L219" t="inlineStr"/>
+      <c r="M219" t="inlineStr"/>
+      <c r="N219" t="inlineStr">
         <is>
           <t>reviewed</t>
         </is>
       </c>
-      <c r="M219" t="inlineStr">
+      <c r="O219" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -14310,10 +15542,20 @@
       </c>
       <c r="L220" t="inlineStr">
         <is>
+          <t>e14 2w shaped</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>e14 2w shaped</t>
+        </is>
+      </c>
+      <c r="N220" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M220" t="inlineStr">
+      <c r="O220" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -14371,10 +15613,20 @@
       </c>
       <c r="L221" t="inlineStr">
         <is>
+          <t>fancy lightbulbs</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>fancy lightbulbs</t>
+        </is>
+      </c>
+      <c r="N221" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M221" t="inlineStr">
+      <c r="O221" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -14430,12 +15682,14 @@
           <t>none</t>
         </is>
       </c>
-      <c r="L222" t="inlineStr">
+      <c r="L222" t="inlineStr"/>
+      <c r="M222" t="inlineStr"/>
+      <c r="N222" t="inlineStr">
         <is>
           <t>reviewed</t>
         </is>
       </c>
-      <c r="M222" t="inlineStr">
+      <c r="O222" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -14491,12 +15745,14 @@
           <t>none</t>
         </is>
       </c>
-      <c r="L223" t="inlineStr">
+      <c r="L223" t="inlineStr"/>
+      <c r="M223" t="inlineStr"/>
+      <c r="N223" t="inlineStr">
         <is>
           <t>reviewed</t>
         </is>
       </c>
-      <c r="M223" t="inlineStr">
+      <c r="O223" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -14552,12 +15808,14 @@
           <t>none</t>
         </is>
       </c>
-      <c r="L224" t="inlineStr">
+      <c r="L224" t="inlineStr"/>
+      <c r="M224" t="inlineStr"/>
+      <c r="N224" t="inlineStr">
         <is>
           <t>reviewed</t>
         </is>
       </c>
-      <c r="M224" t="inlineStr">
+      <c r="O224" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -14615,10 +15873,20 @@
       </c>
       <c r="L225" t="inlineStr">
         <is>
+          <t>e14</t>
+        </is>
+      </c>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>e14</t>
+        </is>
+      </c>
+      <c r="N225" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M225" t="inlineStr">
+      <c r="O225" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -14674,12 +15942,14 @@
           <t>none</t>
         </is>
       </c>
-      <c r="L226" t="inlineStr">
+      <c r="L226" t="inlineStr"/>
+      <c r="M226" t="inlineStr"/>
+      <c r="N226" t="inlineStr">
         <is>
           <t>reviewed</t>
         </is>
       </c>
-      <c r="M226" t="inlineStr">
+      <c r="O226" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -14735,12 +16005,14 @@
           <t>none</t>
         </is>
       </c>
-      <c r="L227" t="inlineStr">
+      <c r="L227" t="inlineStr"/>
+      <c r="M227" t="inlineStr"/>
+      <c r="N227" t="inlineStr">
         <is>
           <t>reviewed</t>
         </is>
       </c>
-      <c r="M227" t="inlineStr">
+      <c r="O227" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -14798,10 +16070,20 @@
       </c>
       <c r="L228" t="inlineStr">
         <is>
+          <t>e14 2w</t>
+        </is>
+      </c>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>e14 2w shaped</t>
+        </is>
+      </c>
+      <c r="N228" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M228" t="inlineStr">
+      <c r="O228" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -14859,17 +16141,27 @@
       </c>
       <c r="L229" t="inlineStr">
         <is>
+          <t>lightbulbs</t>
+        </is>
+      </c>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>lightbulbs</t>
+        </is>
+      </c>
+      <c r="N229" t="inlineStr">
+        <is>
           <t>pending_add</t>
         </is>
       </c>
-      <c r="M229" t="inlineStr">
+      <c r="O229" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M229"/>
+  <autoFilter ref="A1:O229"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -15157,7 +16449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -15311,29 +16603,53 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>action_state</t>
+          <t>missing_words_backend</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>reviewed / pending_add / added</t>
+          <t>THE WORDS TO ACTUALLY TYPE into the backend keyword field — only the words not already there. If the keyword is 'e27 screw bulb' and the field already holds 'e27' and 'bulb', this reads just 'screw'. The backend field has a size limit and Amazon does not reward repeating a word it has already indexed.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>missing_words_frontend</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Same idea for the title / bullets / description text.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>action_state</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>reviewed / pending_add / added</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>date_checked</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>ISO date of this monthly run</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B14"/>
+  <autoFilter ref="A1:B16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/development/abiraj_mini_aios_workbench/projects/PRJ-2026-026_amazon-keyword-gap-sync/evidence/final_outputs/REQ-30_amazon-keyword-gap-sync/REQ-30-D02_keyword_gap_report.xlsx
+++ b/development/abiraj_mini_aios_workbench/projects/PRJ-2026-026_amazon-keyword-gap-sync/evidence/final_outputs/REQ-30_amazon-keyword-gap-sync/REQ-30-D02_keyword_gap_report.xlsx
@@ -492,7 +492,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-19T16:20:33</t>
+          <t>2026-08-19T16:40:50</t>
         </is>
       </c>
     </row>

--- a/development/abiraj_mini_aios_workbench/projects/PRJ-2026-026_amazon-keyword-gap-sync/evidence/final_outputs/REQ-30_amazon-keyword-gap-sync/REQ-30-D02_keyword_gap_report.xlsx
+++ b/development/abiraj_mini_aios_workbench/projects/PRJ-2026-026_amazon-keyword-gap-sync/evidence/final_outputs/REQ-30_amazon-keyword-gap-sync/REQ-30-D02_keyword_gap_report.xlsx
@@ -492,7 +492,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-19T16:40:50</t>
+          <t>2026-08-19T17:22:10</t>
         </is>
       </c>
     </row>

--- a/development/abiraj_mini_aios_workbench/projects/PRJ-2026-026_amazon-keyword-gap-sync/evidence/final_outputs/REQ-30_amazon-keyword-gap-sync/REQ-30-D02_keyword_gap_report.xlsx
+++ b/development/abiraj_mini_aios_workbench/projects/PRJ-2026-026_amazon-keyword-gap-sync/evidence/final_outputs/REQ-30_amazon-keyword-gap-sync/REQ-30-D02_keyword_gap_report.xlsx
@@ -492,7 +492,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-19T17:22:10</t>
+          <t>2026-08-19T17:36:04</t>
         </is>
       </c>
     </row>
